--- a/GourmetProject/GameConfig/Datas/reward.xlsx
+++ b/GourmetProject/GameConfig/Datas/reward.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H11"/>
+  <dimension ref="A1:H18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -774,6 +774,209 @@
       </c>
       <c r="H11" t="n">
         <v>100</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>reward_food_gold</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>22</v>
+      </c>
+      <c r="D12" t="n">
+        <v>36</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>main_gold</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>extra_mixed</t>
+        </is>
+      </c>
+      <c r="G12" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H12" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>reward_food_dish</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>28</v>
+      </c>
+      <c r="D13" t="n">
+        <v>44</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>main_dish</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>extra_mixed</t>
+        </is>
+      </c>
+      <c r="G13" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="H13" t="n">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>reward_food_passive</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>30</v>
+      </c>
+      <c r="D14" t="n">
+        <v>48</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>main_passive</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>extra_mixed</t>
+        </is>
+      </c>
+      <c r="G14" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="H14" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>reward_food_fragment</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>32</v>
+      </c>
+      <c r="D15" t="n">
+        <v>52</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>main_fragment</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>extra_mixed</t>
+        </is>
+      </c>
+      <c r="G15" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="H15" t="n">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>reward_food_hard_dish</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>46</v>
+      </c>
+      <c r="D16" t="n">
+        <v>72</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>main_dish</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>extra_mixed</t>
+        </is>
+      </c>
+      <c r="G16" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="H16" t="n">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>reward_food_hard_passive</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>50</v>
+      </c>
+      <c r="D17" t="n">
+        <v>78</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>main_passive</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>extra_mixed</t>
+        </is>
+      </c>
+      <c r="G17" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="H17" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>reward_food_hard_fragment</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>52</v>
+      </c>
+      <c r="D18" t="n">
+        <v>82</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>main_fragment</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>extra_mixed</t>
+        </is>
+      </c>
+      <c r="G18" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="H18" t="n">
+        <v>65</v>
       </c>
     </row>
   </sheetData>
@@ -787,7 +990,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I12"/>
+  <dimension ref="A1:I13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1230,6 +1433,36 @@
       </c>
       <c r="I12" t="n">
         <v>30</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>slot_main_gold</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>main_gold</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F13" t="n">
+        <v>1</v>
+      </c>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" t="n">
+        <v>35</v>
       </c>
     </row>
   </sheetData>

--- a/GourmetProject/GameConfig/Datas/reward.xlsx
+++ b/GourmetProject/GameConfig/Datas/reward.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I13"/>
+  <dimension ref="A1:I14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -886,6 +886,40 @@
       </c>
       <c r="I13" t="n">
         <v>35</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>slot_main_active</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>main_active</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>ActiveItemGrant</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>1</v>
+      </c>
+      <c r="F14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>pool_active</t>
+        </is>
+      </c>
+      <c r="H14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" t="n">
+        <v>45</v>
       </c>
     </row>
   </sheetData>

--- a/GourmetProject/GameConfig/Datas/reward.xlsx
+++ b/GourmetProject/GameConfig/Datas/reward.xlsx
@@ -7,8 +7,9 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="reward_slot" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="reward_pool" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="reward_package" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="reward_slot" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="reward_pool" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -18,10 +19,17 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
@@ -47,8 +55,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -414,512 +423,682 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I14"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:H21"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8"/>
+  <cols>
+    <col width="13.0769230769231" customWidth="1" min="1" max="1"/>
+    <col width="73.92307692307691" customWidth="1" min="2" max="2"/>
+    <col width="64.8461538461538" customWidth="1" min="3" max="3"/>
+    <col width="57.9230769230769" customWidth="1" min="5" max="5"/>
+    <col width="52.5384615384615" customWidth="1" min="6" max="6"/>
+    <col width="28.1538461538462" customWidth="1" min="7" max="7"/>
+    <col width="44.2307692307692" customWidth="1" min="8" max="8"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>##var</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>groupId</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>kind</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>choiceCount</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>weight</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>poolId</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>hiddenOffset</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>goldMin</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>goldMax</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>mainSlotGroupId</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>extraSlotGroupId</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>extraChance</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>fallbackGold</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="1" t="inlineStr">
         <is>
           <t>##comment</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>奖励槽ID</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>槽组ID</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>奖励类型</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>候选数量</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>槽权重</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>使用的奖励池ID</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>隐藏分偏移</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>兜底金币数量</t>
+      <c r="B2" s="1" t="inlineStr">
+        <is>
+          <t>奖励包 id；Week.rewardPackageId 或 Action.rewardPackageId 引用它。</t>
+        </is>
+      </c>
+      <c r="C2" s="1" t="inlineStr">
+        <is>
+          <t>基础金币奖励下限；实际奖励会结合隐藏分/行动曲线派生。</t>
+        </is>
+      </c>
+      <c r="D2" s="1" t="inlineStr">
+        <is>
+          <t>基础金币奖励上限；实际奖励会结合隐藏分/行动曲线派生。</t>
+        </is>
+      </c>
+      <c r="E2" s="1" t="inlineStr">
+        <is>
+          <t>主奖励槽组 id，对应 reward.xlsx/reward_slot.groupId。</t>
+        </is>
+      </c>
+      <c r="F2" s="1" t="inlineStr">
+        <is>
+          <t>额外奖励槽组 id；extraChance 命中时额外抽取。</t>
+        </is>
+      </c>
+      <c r="G2" s="1" t="inlineStr">
+        <is>
+          <t>额外奖励出现概率，0..1。</t>
+        </is>
+      </c>
+      <c r="H2" s="1" t="inlineStr">
+        <is>
+          <t>奖励候选无法生成或溢出时的兜底金币。</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="1" t="inlineStr">
         <is>
           <t>##type</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B3" s="1" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C3" s="1" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="D3" s="1" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="E3" s="1" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>RewardKind</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
+      <c r="F3" s="1" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="G3" s="1" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="H3" s="1" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
     </row>
     <row r="4">
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>slot_main_dish</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
+      <c r="A4" s="1" t="n"/>
+      <c r="B4" s="1" t="inlineStr">
+        <is>
+          <t>reward_w1</t>
+        </is>
+      </c>
+      <c r="C4" s="1" t="n">
+        <v>45</v>
+      </c>
+      <c r="D4" s="1" t="n">
+        <v>60</v>
+      </c>
+      <c r="E4" s="1" t="inlineStr">
         <is>
           <t>main_dish</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>DishChoice</t>
-        </is>
-      </c>
-      <c r="E4" t="n">
-        <v>3</v>
-      </c>
-      <c r="F4" t="n">
-        <v>1</v>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>pool_dish</t>
-        </is>
-      </c>
-      <c r="H4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I4" t="n">
+      <c r="F4" s="1" t="inlineStr">
+        <is>
+          <t>extra_mixed</t>
+        </is>
+      </c>
+      <c r="G4" s="1" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="H4" s="1" t="n">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="1" t="inlineStr">
+        <is>
+          <t>reward_w2</t>
+        </is>
+      </c>
+      <c r="C5" s="1" t="n">
+        <v>55</v>
+      </c>
+      <c r="D5" s="1" t="n">
+        <v>75</v>
+      </c>
+      <c r="E5" s="1" t="inlineStr">
+        <is>
+          <t>main_passive</t>
+        </is>
+      </c>
+      <c r="F5" s="1" t="inlineStr">
+        <is>
+          <t>extra_mixed</t>
+        </is>
+      </c>
+      <c r="G5" s="1" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H5" s="1" t="n">
         <v>40</v>
       </c>
     </row>
-    <row r="5">
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>slot_main_passive</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="1" t="inlineStr">
+        <is>
+          <t>reward_w3</t>
+        </is>
+      </c>
+      <c r="C6" s="1" t="n">
+        <v>65</v>
+      </c>
+      <c r="D6" s="1" t="n">
+        <v>85</v>
+      </c>
+      <c r="E6" s="1" t="inlineStr">
+        <is>
+          <t>main_dish</t>
+        </is>
+      </c>
+      <c r="F6" s="1" t="inlineStr">
+        <is>
+          <t>extra_mixed</t>
+        </is>
+      </c>
+      <c r="G6" s="1" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="H6" s="1" t="n">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="n"/>
+      <c r="B7" s="1" t="inlineStr">
+        <is>
+          <t>reward_w4_boss</t>
+        </is>
+      </c>
+      <c r="C7" s="1" t="n">
+        <v>90</v>
+      </c>
+      <c r="D7" s="1" t="n">
+        <v>125</v>
+      </c>
+      <c r="E7" s="1" t="inlineStr">
+        <is>
+          <t>main_boss</t>
+        </is>
+      </c>
+      <c r="F7" s="1" t="inlineStr">
+        <is>
+          <t>extra_mixed</t>
+        </is>
+      </c>
+      <c r="G7" s="1" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H7" s="1" t="n">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="1" t="inlineStr">
+        <is>
+          <t>reward_w5</t>
+        </is>
+      </c>
+      <c r="C8" s="1" t="n">
+        <v>85</v>
+      </c>
+      <c r="D8" s="1" t="n">
+        <v>115</v>
+      </c>
+      <c r="E8" s="1" t="inlineStr">
+        <is>
+          <t>main_fragment</t>
+        </is>
+      </c>
+      <c r="F8" s="1" t="inlineStr">
+        <is>
+          <t>extra_mixed</t>
+        </is>
+      </c>
+      <c r="G8" s="1" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="H8" s="1" t="n">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="1" t="inlineStr">
+        <is>
+          <t>reward_w6</t>
+        </is>
+      </c>
+      <c r="C9" s="1" t="n">
+        <v>95</v>
+      </c>
+      <c r="D9" s="1" t="n">
+        <v>130</v>
+      </c>
+      <c r="E9" s="1" t="inlineStr">
         <is>
           <t>main_passive</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>PassiveItemChoice</t>
-        </is>
-      </c>
-      <c r="E5" t="n">
-        <v>3</v>
-      </c>
-      <c r="F5" t="n">
-        <v>1</v>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>pool_passive</t>
-        </is>
-      </c>
-      <c r="H5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I5" t="n">
+      <c r="F9" s="1" t="inlineStr">
+        <is>
+          <t>extra_mixed</t>
+        </is>
+      </c>
+      <c r="G9" s="1" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="H9" s="1" t="n">
         <v>60</v>
       </c>
     </row>
-    <row r="6">
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>slot_main_fragment</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
+    <row r="10">
+      <c r="A10" s="1" t="n"/>
+      <c r="B10" s="1" t="inlineStr">
+        <is>
+          <t>reward_w7</t>
+        </is>
+      </c>
+      <c r="C10" s="1" t="n">
+        <v>110</v>
+      </c>
+      <c r="D10" s="1" t="n">
+        <v>145</v>
+      </c>
+      <c r="E10" s="1" t="inlineStr">
+        <is>
+          <t>main_dish_or_passive</t>
+        </is>
+      </c>
+      <c r="F10" s="1" t="inlineStr">
+        <is>
+          <t>extra_mixed</t>
+        </is>
+      </c>
+      <c r="G10" s="1" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="H10" s="1" t="n">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="1" t="inlineStr">
+        <is>
+          <t>reward_w8_boss</t>
+        </is>
+      </c>
+      <c r="C11" s="1" t="n">
+        <v>140</v>
+      </c>
+      <c r="D11" s="1" t="n">
+        <v>185</v>
+      </c>
+      <c r="E11" s="1" t="inlineStr">
+        <is>
+          <t>main_boss</t>
+        </is>
+      </c>
+      <c r="F11" s="1" t="inlineStr">
+        <is>
+          <t>extra_mixed</t>
+        </is>
+      </c>
+      <c r="G11" s="1" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="H11" s="1" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="1" t="inlineStr">
+        <is>
+          <t>reward_food_gold</t>
+        </is>
+      </c>
+      <c r="C12" s="1" t="n">
+        <v>22</v>
+      </c>
+      <c r="D12" s="1" t="n">
+        <v>36</v>
+      </c>
+      <c r="E12" s="1" t="inlineStr">
+        <is>
+          <t>main_gold</t>
+        </is>
+      </c>
+      <c r="F12" s="1" t="inlineStr">
+        <is>
+          <t>extra_mixed</t>
+        </is>
+      </c>
+      <c r="G12" s="1" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H12" s="1" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="n"/>
+      <c r="B13" s="1" t="inlineStr">
+        <is>
+          <t>reward_food_dish</t>
+        </is>
+      </c>
+      <c r="C13" s="1" t="n">
+        <v>28</v>
+      </c>
+      <c r="D13" s="1" t="n">
+        <v>44</v>
+      </c>
+      <c r="E13" s="1" t="inlineStr">
+        <is>
+          <t>main_dish</t>
+        </is>
+      </c>
+      <c r="F13" s="1" t="inlineStr">
+        <is>
+          <t>extra_mixed</t>
+        </is>
+      </c>
+      <c r="G13" s="1" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="H13" s="1" t="n">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="1" t="inlineStr">
+        <is>
+          <t>reward_food_passive</t>
+        </is>
+      </c>
+      <c r="C14" s="1" t="n">
+        <v>30</v>
+      </c>
+      <c r="D14" s="1" t="n">
+        <v>48</v>
+      </c>
+      <c r="E14" s="1" t="inlineStr">
+        <is>
+          <t>main_passive</t>
+        </is>
+      </c>
+      <c r="F14" s="1" t="inlineStr">
+        <is>
+          <t>extra_mixed</t>
+        </is>
+      </c>
+      <c r="G14" s="1" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="H14" s="1" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="1" t="inlineStr">
+        <is>
+          <t>reward_food_active</t>
+        </is>
+      </c>
+      <c r="C15" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="D15" s="1" t="n">
+        <v>40</v>
+      </c>
+      <c r="E15" s="1" t="inlineStr">
+        <is>
+          <t>main_active</t>
+        </is>
+      </c>
+      <c r="F15" s="1" t="inlineStr">
+        <is>
+          <t>extra_mixed</t>
+        </is>
+      </c>
+      <c r="G15" s="1" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="H15" s="1" t="n">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="n"/>
+      <c r="B16" s="1" t="inlineStr">
+        <is>
+          <t>reward_food_fragment</t>
+        </is>
+      </c>
+      <c r="C16" s="1" t="n">
+        <v>32</v>
+      </c>
+      <c r="D16" s="1" t="n">
+        <v>52</v>
+      </c>
+      <c r="E16" s="1" t="inlineStr">
         <is>
           <t>main_fragment</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>FragmentChoice</t>
-        </is>
-      </c>
-      <c r="E6" t="n">
-        <v>3</v>
-      </c>
-      <c r="F6" t="n">
-        <v>1</v>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>pool_fragment</t>
-        </is>
-      </c>
-      <c r="H6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I6" t="n">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>slot_main_dish_late</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>main_dish_or_passive</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>DishChoice</t>
-        </is>
-      </c>
-      <c r="E7" t="n">
-        <v>3</v>
-      </c>
-      <c r="F7" t="n">
+      <c r="F16" s="1" t="inlineStr">
+        <is>
+          <t>extra_mixed</t>
+        </is>
+      </c>
+      <c r="G16" s="1" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="H16" s="1" t="n">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="1" t="inlineStr">
+        <is>
+          <t>reward_food_hard_gold</t>
+        </is>
+      </c>
+      <c r="C17" s="1" t="n">
+        <v>40</v>
+      </c>
+      <c r="D17" s="1" t="n">
+        <v>66</v>
+      </c>
+      <c r="E17" s="1" t="inlineStr">
+        <is>
+          <t>main_gold</t>
+        </is>
+      </c>
+      <c r="F17" s="1" t="inlineStr">
+        <is>
+          <t>extra_mixed</t>
+        </is>
+      </c>
+      <c r="G17" s="1" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="H17" s="1" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="1" t="inlineStr">
+        <is>
+          <t>reward_food_hard_dish</t>
+        </is>
+      </c>
+      <c r="C18" s="1" t="n">
+        <v>46</v>
+      </c>
+      <c r="D18" s="1" t="n">
+        <v>72</v>
+      </c>
+      <c r="E18" s="1" t="inlineStr">
+        <is>
+          <t>main_dish</t>
+        </is>
+      </c>
+      <c r="F18" s="1" t="inlineStr">
+        <is>
+          <t>extra_mixed</t>
+        </is>
+      </c>
+      <c r="G18" s="1" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="H18" s="1" t="n">
         <v>55</v>
       </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>pool_dish</t>
-        </is>
-      </c>
-      <c r="H7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I7" t="n">
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="n"/>
+      <c r="B19" s="1" t="inlineStr">
+        <is>
+          <t>reward_food_hard_passive</t>
+        </is>
+      </c>
+      <c r="C19" s="1" t="n">
+        <v>50</v>
+      </c>
+      <c r="D19" s="1" t="n">
+        <v>78</v>
+      </c>
+      <c r="E19" s="1" t="inlineStr">
+        <is>
+          <t>main_passive</t>
+        </is>
+      </c>
+      <c r="F19" s="1" t="inlineStr">
+        <is>
+          <t>extra_mixed</t>
+        </is>
+      </c>
+      <c r="G19" s="1" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="H19" s="1" t="n">
         <v>60</v>
       </c>
     </row>
-    <row r="8">
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>slot_main_passive_late</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>main_dish_or_passive</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>PassiveItemChoice</t>
-        </is>
-      </c>
-      <c r="E8" t="n">
-        <v>3</v>
-      </c>
-      <c r="F8" t="n">
-        <v>45</v>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>pool_passive</t>
-        </is>
-      </c>
-      <c r="H8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I8" t="n">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>slot_boss_passive</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>main_boss</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>PassiveItemChoice</t>
-        </is>
-      </c>
-      <c r="E9" t="n">
-        <v>3</v>
-      </c>
-      <c r="F9" t="n">
-        <v>60</v>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>pool_passive_boss</t>
-        </is>
-      </c>
-      <c r="H9" t="n">
-        <v>5</v>
-      </c>
-      <c r="I9" t="n">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>slot_boss_active</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>main_boss</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>ActiveItemGrant</t>
-        </is>
-      </c>
-      <c r="E10" t="n">
-        <v>1</v>
-      </c>
-      <c r="F10" t="n">
-        <v>40</v>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>pool_active</t>
-        </is>
-      </c>
-      <c r="H10" t="n">
-        <v>0</v>
-      </c>
-      <c r="I10" t="n">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>slot_extra_active</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>extra_mixed</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>ActiveItemGrant</t>
-        </is>
-      </c>
-      <c r="E11" t="n">
-        <v>1</v>
-      </c>
-      <c r="F11" t="n">
-        <v>45</v>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>pool_active</t>
-        </is>
-      </c>
-      <c r="H11" t="n">
-        <v>0</v>
-      </c>
-      <c r="I11" t="n">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>slot_extra_gold</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>extra_mixed</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="E12" t="n">
-        <v>1</v>
-      </c>
-      <c r="F12" t="n">
+    <row r="20">
+      <c r="A20" s="1" t="n"/>
+      <c r="B20" s="1" t="inlineStr">
+        <is>
+          <t>reward_food_hard_active</t>
+        </is>
+      </c>
+      <c r="C20" s="1" t="n">
+        <v>42</v>
+      </c>
+      <c r="D20" s="1" t="n">
+        <v>68</v>
+      </c>
+      <c r="E20" s="1" t="inlineStr">
+        <is>
+          <t>main_active</t>
+        </is>
+      </c>
+      <c r="F20" s="1" t="inlineStr">
+        <is>
+          <t>extra_mixed</t>
+        </is>
+      </c>
+      <c r="G20" s="1" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="H20" s="1" t="n">
         <v>55</v>
       </c>
-      <c r="H12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I12" t="n">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>slot_main_gold</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>main_gold</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="E13" t="n">
-        <v>1</v>
-      </c>
-      <c r="F13" t="n">
-        <v>1</v>
-      </c>
-      <c r="H13" t="n">
-        <v>0</v>
-      </c>
-      <c r="I13" t="n">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>slot_main_active</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>main_active</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>ActiveItemGrant</t>
-        </is>
-      </c>
-      <c r="E14" t="n">
-        <v>1</v>
-      </c>
-      <c r="F14" t="n">
-        <v>1</v>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>pool_active</t>
-        </is>
-      </c>
-      <c r="H14" t="n">
-        <v>0</v>
-      </c>
-      <c r="I14" t="n">
-        <v>45</v>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="1" t="inlineStr">
+        <is>
+          <t>reward_food_hard_fragment</t>
+        </is>
+      </c>
+      <c r="C21" s="1" t="n">
+        <v>52</v>
+      </c>
+      <c r="D21" s="1" t="n">
+        <v>82</v>
+      </c>
+      <c r="E21" s="1" t="inlineStr">
+        <is>
+          <t>main_fragment</t>
+        </is>
+      </c>
+      <c r="F21" s="1" t="inlineStr">
+        <is>
+          <t>extra_mixed</t>
+        </is>
+      </c>
+      <c r="G21" s="1" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="H21" s="1" t="n">
+        <v>65</v>
       </c>
     </row>
   </sheetData>
@@ -933,6 +1112,525 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:I14"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>##var</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>groupId</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>kind</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>choiceCount</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>weight</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>poolId</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>hiddenOffset</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>fallbackGold</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>##comment</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>奖励槽ID</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>槽组ID</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>奖励类型</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>候选数量</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>槽权重</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>使用的奖励池ID</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>隐藏分偏移</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>兜底金币数量</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>##type</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>RewardKind</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>slot_main_dish</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>main_dish</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>DishChoice</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>3</v>
+      </c>
+      <c r="F4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>pool_dish</t>
+        </is>
+      </c>
+      <c r="H4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>slot_main_passive</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>main_passive</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>PassiveItemChoice</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>3</v>
+      </c>
+      <c r="F5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>pool_passive</t>
+        </is>
+      </c>
+      <c r="H5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>slot_main_fragment</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>main_fragment</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>FragmentChoice</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>3</v>
+      </c>
+      <c r="F6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>pool_fragment</t>
+        </is>
+      </c>
+      <c r="H6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" t="n">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>slot_main_dish_late</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>main_dish_or_passive</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>DishChoice</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>3</v>
+      </c>
+      <c r="F7" t="n">
+        <v>55</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>pool_dish</t>
+        </is>
+      </c>
+      <c r="H7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>slot_main_passive_late</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>main_dish_or_passive</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>PassiveItemChoice</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>3</v>
+      </c>
+      <c r="F8" t="n">
+        <v>45</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>pool_passive</t>
+        </is>
+      </c>
+      <c r="H8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" t="n">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>slot_boss_passive</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>main_boss</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>PassiveItemChoice</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>3</v>
+      </c>
+      <c r="F9" t="n">
+        <v>60</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>pool_passive_boss</t>
+        </is>
+      </c>
+      <c r="H9" t="n">
+        <v>5</v>
+      </c>
+      <c r="I9" t="n">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>slot_boss_active</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>main_boss</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>ActiveItemGrant</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F10" t="n">
+        <v>40</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>pool_active</t>
+        </is>
+      </c>
+      <c r="H10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>slot_extra_active</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>extra_mixed</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>ActiveItemGrant</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F11" t="n">
+        <v>45</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>pool_active</t>
+        </is>
+      </c>
+      <c r="H11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>slot_extra_gold</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>extra_mixed</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F12" t="n">
+        <v>55</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>slot_main_gold</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>main_gold</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F13" t="n">
+        <v>1</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" t="n">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>slot_main_active</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>main_active</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>ActiveItemGrant</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>1</v>
+      </c>
+      <c r="F14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>pool_active</t>
+        </is>
+      </c>
+      <c r="H14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" t="n">
+        <v>45</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:G8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>

--- a/GourmetProject/GameConfig/Datas/reward.xlsx
+++ b/GourmetProject/GameConfig/Datas/reward.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="187" uniqueCount="104">
   <si>
     <t>##var</t>
   </si>
@@ -168,6 +168,12 @@
     <t>hiddenOffset</t>
   </si>
   <si>
+    <t>goldMultiplierMin</t>
+  </si>
+  <si>
+    <t>goldMultiplierMax</t>
+  </si>
+  <si>
     <t>奖励槽ID</t>
   </si>
   <si>
@@ -187,6 +193,12 @@
   </si>
   <si>
     <t>隐藏分偏移</t>
+  </si>
+  <si>
+    <t>金币下限(基于基础金币)</t>
+  </si>
+  <si>
+    <t>金币上限</t>
   </si>
   <si>
     <t>RewardKind</t>
@@ -328,14 +340,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="21">
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
+  <fonts count="20">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -791,154 +796,154 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1752,8 +1757,8 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H14"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="7"/>
+  <dimension ref="A1:J14"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
     <col min="1" max="1" width="13.0769230769231" customWidth="1"/>
     <col min="2" max="2" width="23.6923076923077" customWidth="1"/>
@@ -1763,9 +1768,11 @@
     <col min="6" max="6" width="8.15384615384615" customWidth="1"/>
     <col min="7" max="7" width="18.7692307692308" customWidth="1"/>
     <col min="8" max="8" width="13.5384615384615" customWidth="1"/>
+    <col min="9" max="9" width="26.2307692307692" customWidth="1"/>
+    <col min="10" max="10" width="19.3846153846154" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:10">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1790,34 +1797,46 @@
       <c r="H1" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="2" spans="1:8">
+      <c r="I1" t="s">
+        <v>50</v>
+      </c>
+      <c r="J1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10">
       <c r="A2" t="s">
         <v>7</v>
       </c>
       <c r="B2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C2" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="D2" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="E2" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="G2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="H2" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8">
+        <v>58</v>
+      </c>
+      <c r="I2" t="s">
+        <v>59</v>
+      </c>
+      <c r="J2" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10">
       <c r="A3" t="s">
         <v>14</v>
       </c>
@@ -1828,7 +1847,7 @@
         <v>15</v>
       </c>
       <c r="D3" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="E3" t="s">
         <v>16</v>
@@ -1842,16 +1861,22 @@
       <c r="H3" t="s">
         <v>16</v>
       </c>
+      <c r="I3" t="s">
+        <v>17</v>
+      </c>
+      <c r="J3" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="4" spans="2:8">
       <c r="B4" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="C4" t="s">
         <v>19</v>
       </c>
       <c r="D4" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="E4">
         <v>3</v>
@@ -1860,7 +1885,7 @@
         <v>1</v>
       </c>
       <c r="G4" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="H4">
         <v>0</v>
@@ -1868,13 +1893,13 @@
     </row>
     <row r="5" spans="2:8">
       <c r="B5" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="C5" t="s">
         <v>22</v>
       </c>
       <c r="D5" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="E5">
         <v>3</v>
@@ -1883,7 +1908,7 @@
         <v>1</v>
       </c>
       <c r="G5" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="H5">
         <v>0</v>
@@ -1891,13 +1916,13 @@
     </row>
     <row r="6" spans="2:8">
       <c r="B6" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="C6" t="s">
         <v>27</v>
       </c>
       <c r="D6" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="E6">
         <v>3</v>
@@ -1906,7 +1931,7 @@
         <v>1</v>
       </c>
       <c r="G6" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="H6">
         <v>0</v>
@@ -1914,13 +1939,13 @@
     </row>
     <row r="7" spans="2:8">
       <c r="B7" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="C7" t="s">
         <v>30</v>
       </c>
       <c r="D7" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="E7">
         <v>3</v>
@@ -1929,7 +1954,7 @@
         <v>55</v>
       </c>
       <c r="G7" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="H7">
         <v>0</v>
@@ -1937,13 +1962,13 @@
     </row>
     <row r="8" spans="2:8">
       <c r="B8" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="C8" t="s">
         <v>30</v>
       </c>
       <c r="D8" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="E8">
         <v>3</v>
@@ -1952,7 +1977,7 @@
         <v>45</v>
       </c>
       <c r="G8" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="H8">
         <v>0</v>
@@ -1960,13 +1985,13 @@
     </row>
     <row r="9" spans="2:8">
       <c r="B9" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="C9" t="s">
         <v>25</v>
       </c>
       <c r="D9" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="E9">
         <v>3</v>
@@ -1975,7 +2000,7 @@
         <v>60</v>
       </c>
       <c r="G9" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="H9">
         <v>5</v>
@@ -1983,13 +2008,13 @@
     </row>
     <row r="10" spans="2:8">
       <c r="B10" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="C10" t="s">
         <v>25</v>
       </c>
       <c r="D10" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="E10">
         <v>1</v>
@@ -1998,7 +2023,7 @@
         <v>40</v>
       </c>
       <c r="G10" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="H10">
         <v>0</v>
@@ -2006,13 +2031,13 @@
     </row>
     <row r="11" spans="2:8">
       <c r="B11" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="C11" t="s">
         <v>20</v>
       </c>
       <c r="D11" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="E11">
         <v>1</v>
@@ -2021,21 +2046,21 @@
         <v>45</v>
       </c>
       <c r="G11" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="H11">
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="2:8">
+    <row r="12" spans="2:10">
       <c r="B12" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="C12" t="s">
         <v>20</v>
       </c>
       <c r="D12" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="E12">
         <v>1</v>
@@ -2046,16 +2071,22 @@
       <c r="H12">
         <v>0</v>
       </c>
-    </row>
-    <row r="13" spans="2:8">
+      <c r="I12">
+        <v>1.6</v>
+      </c>
+      <c r="J12">
+        <v>2.4</v>
+      </c>
+    </row>
+    <row r="13" spans="2:10">
       <c r="B13" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="C13" t="s">
         <v>33</v>
       </c>
       <c r="D13" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="E13">
         <v>1</v>
@@ -2066,16 +2097,22 @@
       <c r="H13">
         <v>0</v>
       </c>
+      <c r="I13">
+        <v>1.6</v>
+      </c>
+      <c r="J13">
+        <v>2.4</v>
+      </c>
     </row>
     <row r="14" spans="2:8">
       <c r="B14" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="C14" t="s">
         <v>37</v>
       </c>
       <c r="D14" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="E14">
         <v>1</v>
@@ -2084,7 +2121,7 @@
         <v>1</v>
       </c>
       <c r="G14" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="H14">
         <v>0</v>
@@ -2113,16 +2150,16 @@
         <v>45</v>
       </c>
       <c r="D1" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="E1" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="F1" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="G1" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
     </row>
     <row r="2" spans="1:7">
@@ -2130,22 +2167,22 @@
         <v>7</v>
       </c>
       <c r="B2" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="C2" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="D2" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="E2" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="F2" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="G2" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -2156,7 +2193,7 @@
         <v>15</v>
       </c>
       <c r="C3" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="D3" t="s">
         <v>15</v>
@@ -2165,7 +2202,7 @@
         <v>15</v>
       </c>
       <c r="F3" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="G3" t="s">
         <v>16</v>
@@ -2173,13 +2210,13 @@
     </row>
     <row r="4" spans="2:7">
       <c r="B4" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="C4" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="F4" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="G4">
         <v>5</v>
@@ -2187,13 +2224,13 @@
     </row>
     <row r="5" spans="2:7">
       <c r="B5" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="C5" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="F5" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="G5">
         <v>5</v>
@@ -2201,16 +2238,16 @@
     </row>
     <row r="6" spans="2:7">
       <c r="B6" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="C6" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="E6" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="F6" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="G6">
         <v>5</v>
@@ -2218,19 +2255,19 @@
     </row>
     <row r="7" spans="2:7">
       <c r="B7" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="C7" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="D7" t="s">
+        <v>100</v>
+      </c>
+      <c r="E7" t="s">
+        <v>101</v>
+      </c>
+      <c r="F7" t="s">
         <v>96</v>
-      </c>
-      <c r="E7" t="s">
-        <v>97</v>
-      </c>
-      <c r="F7" t="s">
-        <v>92</v>
       </c>
       <c r="G7">
         <v>5</v>
@@ -2238,16 +2275,16 @@
     </row>
     <row r="8" spans="2:7">
       <c r="B8" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="C8" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="E8" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="F8" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="G8">
         <v>0</v>

--- a/GourmetProject/GameConfig/Datas/reward.xlsx
+++ b/GourmetProject/GameConfig/Datas/reward.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="15200" activeTab="1"/>
+    <workbookView windowHeight="15200"/>
   </bookViews>
   <sheets>
     <sheet name="reward_package" sheetId="1" r:id="rId1"/>
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="187" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="87">
   <si>
     <t>##var</t>
   </si>
@@ -24,40 +24,22 @@
     <t>id</t>
   </si>
   <si>
-    <t>goldMin</t>
-  </si>
-  <si>
-    <t>goldMax</t>
-  </si>
-  <si>
-    <t>mainSlotGroupId</t>
-  </si>
-  <si>
-    <t>extraSlotGroupId</t>
-  </si>
-  <si>
-    <t>extraChance</t>
+    <t>baseDishSlotGroupId</t>
+  </si>
+  <si>
+    <t>specificSlotGroupId</t>
   </si>
   <si>
     <t>##comment</t>
   </si>
   <si>
-    <t>奖励包 id；Week.rewardPackageId 或 Action.rewardPackageId 引用它。</t>
-  </si>
-  <si>
-    <t>基础金币奖励下限；实际奖励会结合隐藏分/行动曲线派生。</t>
-  </si>
-  <si>
-    <t>基础金币奖励上限；实际奖励会结合隐藏分/行动曲线派生。</t>
-  </si>
-  <si>
-    <t>主奖励槽组 id，对应 reward.xlsx/reward_slot.groupId。</t>
-  </si>
-  <si>
-    <t>额外奖励槽组 id；extraChance 命中时额外抽取。</t>
-  </si>
-  <si>
-    <t>额外奖励出现概率，0..1。</t>
+    <t>奖励包 id</t>
+  </si>
+  <si>
+    <t>基础菜品奖励槽组 id。</t>
+  </si>
+  <si>
+    <t>行动预览对应的特定奖励槽组 id。</t>
   </si>
   <si>
     <t>##type</t>
@@ -66,145 +48,124 @@
     <t>string</t>
   </si>
   <si>
+    <t>(list#sep=,),string</t>
+  </si>
+  <si>
+    <t>reward_food_gold</t>
+  </si>
+  <si>
+    <t>base_dish</t>
+  </si>
+  <si>
+    <t>specific_gold</t>
+  </si>
+  <si>
+    <t>reward_food_dish</t>
+  </si>
+  <si>
+    <t>specific_dish</t>
+  </si>
+  <si>
+    <t>reward_food_passive</t>
+  </si>
+  <si>
+    <t>specific_passive</t>
+  </si>
+  <si>
+    <t>reward_food_active</t>
+  </si>
+  <si>
+    <t>specific_active</t>
+  </si>
+  <si>
+    <t>reward_food_fragment</t>
+  </si>
+  <si>
+    <t>specific_fragment</t>
+  </si>
+  <si>
+    <t>reward_food_hard_gold</t>
+  </si>
+  <si>
+    <t>reward_food_hard_dish</t>
+  </si>
+  <si>
+    <t>reward_food_hard_passive</t>
+  </si>
+  <si>
+    <t>reward_food_hard_active</t>
+  </si>
+  <si>
+    <t>reward_food_hard_fragment</t>
+  </si>
+  <si>
+    <t>reward_food_boss</t>
+  </si>
+  <si>
+    <t>boss_dish,boss_passive,boss_fragment</t>
+  </si>
+  <si>
+    <t>groupId</t>
+  </si>
+  <si>
+    <t>kind</t>
+  </si>
+  <si>
+    <t>choiceCount</t>
+  </si>
+  <si>
+    <t>requiredPickCount</t>
+  </si>
+  <si>
+    <t>weight</t>
+  </si>
+  <si>
+    <t>poolId</t>
+  </si>
+  <si>
+    <t>normalHiddenOffset</t>
+  </si>
+  <si>
+    <t>hardHiddenOffset</t>
+  </si>
+  <si>
+    <t>奖励槽ID</t>
+  </si>
+  <si>
+    <t>槽组ID</t>
+  </si>
+  <si>
+    <t>奖励类型</t>
+  </si>
+  <si>
+    <t>候选数量</t>
+  </si>
+  <si>
+    <t>需要领取的候选数量</t>
+  </si>
+  <si>
+    <t>槽权重</t>
+  </si>
+  <si>
+    <t>使用的奖励池ID</t>
+  </si>
+  <si>
+    <t>普通美食临时隐藏分修正（boss也读这些）</t>
+  </si>
+  <si>
+    <t>困难美食临时隐藏分修正</t>
+  </si>
+  <si>
+    <t>RewardKind</t>
+  </si>
+  <si>
     <t>int</t>
   </si>
   <si>
     <t>float</t>
   </si>
   <si>
-    <t>reward_w1</t>
-  </si>
-  <si>
-    <t>main_dish</t>
-  </si>
-  <si>
-    <t>extra_mixed</t>
-  </si>
-  <si>
-    <t>reward_w2</t>
-  </si>
-  <si>
-    <t>main_passive</t>
-  </si>
-  <si>
-    <t>reward_w3</t>
-  </si>
-  <si>
-    <t>reward_w4_boss</t>
-  </si>
-  <si>
-    <t>main_boss</t>
-  </si>
-  <si>
-    <t>reward_w5</t>
-  </si>
-  <si>
-    <t>main_fragment</t>
-  </si>
-  <si>
-    <t>reward_w6</t>
-  </si>
-  <si>
-    <t>reward_w7</t>
-  </si>
-  <si>
-    <t>main_dish_or_passive</t>
-  </si>
-  <si>
-    <t>reward_w8_boss</t>
-  </si>
-  <si>
-    <t>reward_food_gold</t>
-  </si>
-  <si>
-    <t>main_gold</t>
-  </si>
-  <si>
-    <t>reward_food_dish</t>
-  </si>
-  <si>
-    <t>reward_food_passive</t>
-  </si>
-  <si>
-    <t>reward_food_active</t>
-  </si>
-  <si>
-    <t>main_active</t>
-  </si>
-  <si>
-    <t>reward_food_fragment</t>
-  </si>
-  <si>
-    <t>reward_food_hard_gold</t>
-  </si>
-  <si>
-    <t>reward_food_hard_dish</t>
-  </si>
-  <si>
-    <t>reward_food_hard_passive</t>
-  </si>
-  <si>
-    <t>reward_food_hard_active</t>
-  </si>
-  <si>
-    <t>reward_food_hard_fragment</t>
-  </si>
-  <si>
-    <t>groupId</t>
-  </si>
-  <si>
-    <t>kind</t>
-  </si>
-  <si>
-    <t>choiceCount</t>
-  </si>
-  <si>
-    <t>weight</t>
-  </si>
-  <si>
-    <t>poolId</t>
-  </si>
-  <si>
-    <t>hiddenOffset</t>
-  </si>
-  <si>
-    <t>goldMultiplierMin</t>
-  </si>
-  <si>
-    <t>goldMultiplierMax</t>
-  </si>
-  <si>
-    <t>奖励槽ID</t>
-  </si>
-  <si>
-    <t>槽组ID</t>
-  </si>
-  <si>
-    <t>奖励类型</t>
-  </si>
-  <si>
-    <t>候选数量</t>
-  </si>
-  <si>
-    <t>槽权重</t>
-  </si>
-  <si>
-    <t>使用的奖励池ID</t>
-  </si>
-  <si>
-    <t>隐藏分偏移</t>
-  </si>
-  <si>
-    <t>金币下限(基于基础金币)</t>
-  </si>
-  <si>
-    <t>金币上限</t>
-  </si>
-  <si>
-    <t>RewardKind</t>
-  </si>
-  <si>
-    <t>slot_main_dish</t>
+    <t>slot_base_dish</t>
   </si>
   <si>
     <t>DishChoice</t>
@@ -213,7 +174,19 @@
     <t>pool_dish</t>
   </si>
   <si>
-    <t>slot_main_passive</t>
+    <t>slot_specific_gold</t>
+  </si>
+  <si>
+    <t>Gold</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>slot_specific_dish</t>
+  </si>
+  <si>
+    <t>slot_specific_passive</t>
   </si>
   <si>
     <t>PassiveItemChoice</t>
@@ -222,7 +195,16 @@
     <t>pool_passive</t>
   </si>
   <si>
-    <t>slot_main_fragment</t>
+    <t>slot_specific_active</t>
+  </si>
+  <si>
+    <t>ActiveItemGrant</t>
+  </si>
+  <si>
+    <t>pool_active</t>
+  </si>
+  <si>
+    <t>slot_specific_fragment</t>
   </si>
   <si>
     <t>FragmentChoice</t>
@@ -231,48 +213,30 @@
     <t>pool_fragment</t>
   </si>
   <si>
-    <t>slot_main_dish_late</t>
-  </si>
-  <si>
-    <t>slot_main_passive_late</t>
-  </si>
-  <si>
     <t>slot_boss_passive</t>
   </si>
   <si>
+    <t>boss_passive</t>
+  </si>
+  <si>
     <t>pool_passive_boss</t>
   </si>
   <si>
-    <t>slot_boss_active</t>
-  </si>
-  <si>
-    <t>ActiveItemGrant</t>
-  </si>
-  <si>
-    <t>pool_active</t>
-  </si>
-  <si>
-    <t>slot_extra_active</t>
-  </si>
-  <si>
-    <t>slot_extra_gold</t>
-  </si>
-  <si>
-    <t>Gold</t>
-  </si>
-  <si>
-    <t>slot_main_gold</t>
-  </si>
-  <si>
-    <t>slot_main_active</t>
+    <t>slot_boss_fragment</t>
+  </si>
+  <si>
+    <t>boss_fragment</t>
+  </si>
+  <si>
+    <t>slot_boss_gold</t>
+  </si>
+  <si>
+    <t>boss_gold</t>
   </si>
   <si>
     <t>specialTags</t>
   </si>
   <si>
-    <t>qualityWeights</t>
-  </si>
-  <si>
     <t>allowFallback</t>
   </si>
   <si>
@@ -288,9 +252,6 @@
     <t>特殊标签筛选</t>
   </si>
   <si>
-    <t>品质权重配置</t>
-  </si>
-  <si>
     <t>是否允许兜底</t>
   </si>
   <si>
@@ -306,28 +267,16 @@
     <t>Dish</t>
   </si>
   <si>
-    <t>true</t>
-  </si>
-  <si>
     <t>Fragment</t>
   </si>
   <si>
     <t>PassiveItem</t>
   </si>
   <si>
-    <t>Common:65|Uncommon:30|Rare:5</t>
-  </si>
-  <si>
     <t>BossReward|ScoreBuild</t>
   </si>
   <si>
-    <t>Common:35|Uncommon:40|Rare:20|Epic:5</t>
-  </si>
-  <si>
     <t>ActiveItem</t>
-  </si>
-  <si>
-    <t>Common:80|Uncommon:20</t>
   </si>
 </sst>
 </file>
@@ -943,7 +892,9 @@
   </cellStyleXfs>
   <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1290,18 +1241,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G21"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="6"/>
+  <dimension ref="A1:D14"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="3"/>
   <cols>
-    <col min="1" max="1" width="13.0769230769231" customWidth="1"/>
-    <col min="2" max="2" width="73.9230769230769" customWidth="1"/>
-    <col min="3" max="3" width="64.8461538461538" customWidth="1"/>
-    <col min="5" max="5" width="57.9230769230769" customWidth="1"/>
-    <col min="6" max="6" width="52.5384615384615" customWidth="1"/>
-    <col min="7" max="7" width="28.1538461538462" customWidth="1"/>
+    <col min="1" max="1" width="13.0769230769231" style="1" customWidth="1"/>
+    <col min="2" max="2" width="29.0769230769231" style="1" customWidth="1"/>
+    <col min="3" max="3" width="39.5384615384615" style="1" customWidth="1"/>
+    <col min="4" max="4" width="37.0769230769231" style="1" customWidth="1"/>
+    <col min="5" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:4">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1314,438 +1264,151 @@
       <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="B2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="C2" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="2" spans="1:7">
-      <c r="A2" s="1" t="s">
+      <c r="D2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="1" t="s">
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="B3" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="C3" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="D3" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="4" spans="2:4">
+      <c r="B4" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="C4" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="D4" s="1" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="3" spans="1:7">
-      <c r="A3" s="1" t="s">
+    <row r="5" spans="2:4">
+      <c r="B5" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="C5" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D5" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C3" s="1" t="s">
+    </row>
+    <row r="6" spans="2:4">
+      <c r="B6" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D3" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="E3" s="1" t="s">
+      <c r="C6" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="7" spans="2:4">
+      <c r="B7" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="8" spans="2:4">
+      <c r="B8" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="9" spans="2:4">
+      <c r="B9" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="10" spans="2:4">
+      <c r="B10" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D10" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="F3" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="G3" s="1" t="s">
+    </row>
+    <row r="11" spans="2:4">
+      <c r="B11" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D11" s="1" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="4" spans="1:7">
-      <c r="A4" s="1"/>
-      <c r="B4" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="C4" s="1">
-        <v>45</v>
-      </c>
-      <c r="D4" s="1">
-        <v>60</v>
-      </c>
-      <c r="E4" s="1" t="s">
+    <row r="12" spans="2:4">
+      <c r="B12" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D12" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="F4" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="G4" s="1">
-        <v>0.15</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5" s="1"/>
-      <c r="B5" s="1" t="s">
+    </row>
+    <row r="13" spans="2:4">
+      <c r="B13" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D13" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="C5" s="1">
-        <v>55</v>
-      </c>
-      <c r="D5" s="1">
-        <v>75</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="G5" s="1">
-        <v>0.2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6" s="1"/>
-      <c r="B6" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="C6" s="1">
-        <v>65</v>
-      </c>
-      <c r="D6" s="1">
-        <v>85</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="F6" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="G6" s="1">
-        <v>0.25</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7" s="1"/>
-      <c r="B7" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="C7" s="1">
-        <v>90</v>
-      </c>
-      <c r="D7" s="1">
-        <v>125</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="F7" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="G7" s="1">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8" s="1"/>
-      <c r="B8" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="C8" s="1">
-        <v>85</v>
-      </c>
-      <c r="D8" s="1">
-        <v>115</v>
-      </c>
-      <c r="E8" s="1" t="s">
+    </row>
+    <row r="14" spans="2:3">
+      <c r="B14" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="F8" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="G8" s="1">
-        <v>0.3</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9" s="1"/>
-      <c r="B9" s="1" t="s">
+      <c r="C14" s="1" t="s">
         <v>28</v>
-      </c>
-      <c r="C9" s="1">
-        <v>95</v>
-      </c>
-      <c r="D9" s="1">
-        <v>130</v>
-      </c>
-      <c r="E9" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="F9" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="G9" s="1">
-        <v>0.35</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10" s="1"/>
-      <c r="B10" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="C10" s="1">
-        <v>110</v>
-      </c>
-      <c r="D10" s="1">
-        <v>145</v>
-      </c>
-      <c r="E10" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="F10" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="G10" s="1">
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11" s="1"/>
-      <c r="B11" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="C11" s="1">
-        <v>140</v>
-      </c>
-      <c r="D11" s="1">
-        <v>185</v>
-      </c>
-      <c r="E11" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="F11" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="G11" s="1">
-        <v>0.6</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12" s="1"/>
-      <c r="B12" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="C12" s="1">
-        <v>22</v>
-      </c>
-      <c r="D12" s="1">
-        <v>36</v>
-      </c>
-      <c r="E12" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="F12" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="G12" s="1">
-        <v>0.1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="A13" s="1"/>
-      <c r="B13" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="C13" s="1">
-        <v>28</v>
-      </c>
-      <c r="D13" s="1">
-        <v>44</v>
-      </c>
-      <c r="E13" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="F13" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="G13" s="1">
-        <v>0.15</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="A14" s="1"/>
-      <c r="B14" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="C14" s="1">
-        <v>30</v>
-      </c>
-      <c r="D14" s="1">
-        <v>48</v>
-      </c>
-      <c r="E14" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="F14" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="G14" s="1">
-        <v>0.18</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7">
-      <c r="A15" s="1"/>
-      <c r="B15" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="C15" s="1">
-        <v>24</v>
-      </c>
-      <c r="D15" s="1">
-        <v>40</v>
-      </c>
-      <c r="E15" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="F15" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="G15" s="1">
-        <v>0.15</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7">
-      <c r="A16" s="1"/>
-      <c r="B16" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="C16" s="1">
-        <v>32</v>
-      </c>
-      <c r="D16" s="1">
-        <v>52</v>
-      </c>
-      <c r="E16" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="F16" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="G16" s="1">
-        <v>0.18</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7">
-      <c r="A17" s="1"/>
-      <c r="B17" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="C17" s="1">
-        <v>40</v>
-      </c>
-      <c r="D17" s="1">
-        <v>66</v>
-      </c>
-      <c r="E17" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="F17" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="G17" s="1">
-        <v>0.25</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7">
-      <c r="A18" s="1"/>
-      <c r="B18" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="C18" s="1">
-        <v>46</v>
-      </c>
-      <c r="D18" s="1">
-        <v>72</v>
-      </c>
-      <c r="E18" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="F18" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="G18" s="1">
-        <v>0.28</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7">
-      <c r="A19" s="1"/>
-      <c r="B19" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="C19" s="1">
-        <v>50</v>
-      </c>
-      <c r="D19" s="1">
-        <v>78</v>
-      </c>
-      <c r="E19" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="F19" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="G19" s="1">
-        <v>0.3</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7">
-      <c r="A20" s="1"/>
-      <c r="B20" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="C20" s="1">
-        <v>42</v>
-      </c>
-      <c r="D20" s="1">
-        <v>68</v>
-      </c>
-      <c r="E20" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="F20" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="G20" s="1">
-        <v>0.25</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7">
-      <c r="A21" s="1"/>
-      <c r="B21" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="C21" s="1">
-        <v>52</v>
-      </c>
-      <c r="D21" s="1">
-        <v>82</v>
-      </c>
-      <c r="E21" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="F21" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="G21" s="1">
-        <v>0.3</v>
       </c>
     </row>
   </sheetData>
@@ -1757,373 +1420,378 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:J14"/>
+  <dimension ref="A1:J12"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
-    <col min="1" max="1" width="13.0769230769231" customWidth="1"/>
-    <col min="2" max="2" width="23.6923076923077" customWidth="1"/>
-    <col min="3" max="3" width="22.6153846153846" customWidth="1"/>
-    <col min="4" max="4" width="19.2307692307692" customWidth="1"/>
-    <col min="5" max="5" width="13.0769230769231" customWidth="1"/>
-    <col min="6" max="6" width="8.15384615384615" customWidth="1"/>
-    <col min="7" max="7" width="18.7692307692308" customWidth="1"/>
-    <col min="8" max="8" width="13.5384615384615" customWidth="1"/>
-    <col min="9" max="9" width="26.2307692307692" customWidth="1"/>
-    <col min="10" max="10" width="19.3846153846154" customWidth="1"/>
+    <col min="1" max="1" width="13.0769230769231" style="1" customWidth="1"/>
+    <col min="2" max="2" width="23" style="1" customWidth="1"/>
+    <col min="3" max="3" width="18.3076923076923" style="1" customWidth="1"/>
+    <col min="4" max="4" width="19.2307692307692" style="1" customWidth="1"/>
+    <col min="5" max="5" width="13.0769230769231" style="1" customWidth="1"/>
+    <col min="6" max="6" width="22.4615384615385" style="1" customWidth="1"/>
+    <col min="7" max="7" width="8.15384615384615" style="1" customWidth="1"/>
+    <col min="8" max="8" width="18.7692307692308" style="1" customWidth="1"/>
+    <col min="9" max="9" width="46.0769230769231" style="1" customWidth="1"/>
+    <col min="10" max="10" width="27.3076923076923" style="1" customWidth="1"/>
+    <col min="11" max="11" width="31.0769230769231" style="1" customWidth="1"/>
+    <col min="12" max="12" width="19.3846153846154" style="1" customWidth="1"/>
+    <col min="13" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10">
-      <c r="A1" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10">
+      <c r="A2" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="I2" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="D1" t="s">
+      <c r="J2" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="E1" t="s">
+    </row>
+    <row r="3" spans="1:10">
+      <c r="A3" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D3" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="F1" t="s">
+      <c r="E3" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="G1" t="s">
+      <c r="F3" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="G3" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H3" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="4" spans="2:10">
+      <c r="B4" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="I1" t="s">
+      <c r="C4" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D4" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="J1" t="s">
+      <c r="E4" s="1">
+        <v>3</v>
+      </c>
+      <c r="F4" s="1">
+        <v>1</v>
+      </c>
+      <c r="G4" s="1">
+        <v>1</v>
+      </c>
+      <c r="H4" s="1" t="s">
         <v>51</v>
       </c>
-    </row>
-    <row r="2" spans="1:10">
-      <c r="A2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B2" t="s">
+      <c r="I4" s="1">
+        <v>0</v>
+      </c>
+      <c r="J4" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="2:10">
+      <c r="B5" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C5" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D5" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E5" s="1">
+        <v>1</v>
+      </c>
+      <c r="F5" s="1">
+        <v>1</v>
+      </c>
+      <c r="G5" s="1">
+        <v>1</v>
+      </c>
+      <c r="H5" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="E2" t="s">
+      <c r="I5" s="1">
+        <v>0</v>
+      </c>
+      <c r="J5" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="2:10">
+      <c r="B6" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="F2" t="s">
+      <c r="C6" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="E6" s="1">
+        <v>3</v>
+      </c>
+      <c r="F6" s="1">
+        <v>1</v>
+      </c>
+      <c r="G6" s="1">
+        <v>1</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="I6" s="1">
+        <v>0</v>
+      </c>
+      <c r="J6" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="2:10">
+      <c r="B7" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="G2" t="s">
+      <c r="C7" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D7" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="H2" t="s">
+      <c r="E7" s="1">
+        <v>3</v>
+      </c>
+      <c r="F7" s="1">
+        <v>1</v>
+      </c>
+      <c r="G7" s="1">
+        <v>1</v>
+      </c>
+      <c r="H7" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="I2" t="s">
+      <c r="I7" s="1">
+        <v>0</v>
+      </c>
+      <c r="J7" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="2:10">
+      <c r="B8" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="J2" t="s">
+      <c r="C8" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D8" s="1" t="s">
         <v>60</v>
       </c>
-    </row>
-    <row r="3" spans="1:10">
-      <c r="A3" t="s">
-        <v>14</v>
-      </c>
-      <c r="B3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C3" t="s">
-        <v>15</v>
-      </c>
-      <c r="D3" t="s">
+      <c r="E8" s="1">
+        <v>5</v>
+      </c>
+      <c r="F8" s="1">
+        <v>2</v>
+      </c>
+      <c r="G8" s="1">
+        <v>1</v>
+      </c>
+      <c r="H8" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="E3" t="s">
-        <v>16</v>
-      </c>
-      <c r="F3" t="s">
-        <v>17</v>
-      </c>
-      <c r="G3" t="s">
-        <v>15</v>
-      </c>
-      <c r="H3" t="s">
-        <v>16</v>
-      </c>
-      <c r="I3" t="s">
-        <v>17</v>
-      </c>
-      <c r="J3" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="4" spans="2:8">
-      <c r="B4" t="s">
+      <c r="I8" s="1">
+        <v>0</v>
+      </c>
+      <c r="J8" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9" spans="2:10">
+      <c r="B9" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="C4" t="s">
-        <v>19</v>
-      </c>
-      <c r="D4" t="s">
+      <c r="C9" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D9" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="E4">
+      <c r="E9" s="1">
         <v>3</v>
       </c>
-      <c r="F4">
-        <v>1</v>
-      </c>
-      <c r="G4" t="s">
+      <c r="F9" s="1">
+        <v>1</v>
+      </c>
+      <c r="G9" s="1">
+        <v>1</v>
+      </c>
+      <c r="H9" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="H4">
+      <c r="I9" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="2:8">
-      <c r="B5" t="s">
+      <c r="J9" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="2:10">
+      <c r="B10" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="C5" t="s">
-        <v>22</v>
-      </c>
-      <c r="D5" t="s">
+      <c r="C10" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="E5">
+      <c r="D10" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="E10" s="1">
         <v>3</v>
       </c>
-      <c r="F5">
-        <v>1</v>
-      </c>
-      <c r="G5" t="s">
+      <c r="F10" s="1">
+        <v>1</v>
+      </c>
+      <c r="G10" s="1">
+        <v>1</v>
+      </c>
+      <c r="H10" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="H5">
+      <c r="I10" s="1">
+        <v>10</v>
+      </c>
+      <c r="J10" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="2:8">
-      <c r="B6" t="s">
+    <row r="11" spans="2:10">
+      <c r="B11" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="C6" t="s">
-        <v>27</v>
-      </c>
-      <c r="D6" t="s">
+      <c r="C11" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="E6">
+      <c r="D11" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="E11" s="1">
         <v>3</v>
       </c>
-      <c r="F6">
-        <v>1</v>
-      </c>
-      <c r="G6" t="s">
+      <c r="F11" s="1">
+        <v>1</v>
+      </c>
+      <c r="G11" s="1">
+        <v>1</v>
+      </c>
+      <c r="H11" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="I11" s="1">
+        <v>10</v>
+      </c>
+      <c r="J11" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="2:10">
+      <c r="B12" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="H6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="2:8">
-      <c r="B7" t="s">
+      <c r="C12" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="C7" t="s">
-        <v>30</v>
-      </c>
-      <c r="D7" t="s">
-        <v>63</v>
-      </c>
-      <c r="E7">
-        <v>3</v>
-      </c>
-      <c r="F7">
-        <v>55</v>
-      </c>
-      <c r="G7" t="s">
-        <v>64</v>
-      </c>
-      <c r="H7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="2:8">
-      <c r="B8" t="s">
-        <v>72</v>
-      </c>
-      <c r="C8" t="s">
-        <v>30</v>
-      </c>
-      <c r="D8" t="s">
-        <v>66</v>
-      </c>
-      <c r="E8">
-        <v>3</v>
-      </c>
-      <c r="F8">
-        <v>45</v>
-      </c>
-      <c r="G8" t="s">
-        <v>67</v>
-      </c>
-      <c r="H8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="2:8">
-      <c r="B9" t="s">
-        <v>73</v>
-      </c>
-      <c r="C9" t="s">
-        <v>25</v>
-      </c>
-      <c r="D9" t="s">
-        <v>66</v>
-      </c>
-      <c r="E9">
-        <v>3</v>
-      </c>
-      <c r="F9">
-        <v>60</v>
-      </c>
-      <c r="G9" t="s">
-        <v>74</v>
-      </c>
-      <c r="H9">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="10" spans="2:8">
-      <c r="B10" t="s">
-        <v>75</v>
-      </c>
-      <c r="C10" t="s">
-        <v>25</v>
-      </c>
-      <c r="D10" t="s">
-        <v>76</v>
-      </c>
-      <c r="E10">
-        <v>1</v>
-      </c>
-      <c r="F10">
-        <v>40</v>
-      </c>
-      <c r="G10" t="s">
-        <v>77</v>
-      </c>
-      <c r="H10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="2:8">
-      <c r="B11" t="s">
-        <v>78</v>
-      </c>
-      <c r="C11" t="s">
-        <v>20</v>
-      </c>
-      <c r="D11" t="s">
-        <v>76</v>
-      </c>
-      <c r="E11">
-        <v>1</v>
-      </c>
-      <c r="F11">
-        <v>45</v>
-      </c>
-      <c r="G11" t="s">
-        <v>77</v>
-      </c>
-      <c r="H11">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="2:10">
-      <c r="B12" t="s">
-        <v>79</v>
-      </c>
-      <c r="C12" t="s">
-        <v>20</v>
-      </c>
-      <c r="D12" t="s">
-        <v>80</v>
-      </c>
-      <c r="E12">
-        <v>1</v>
-      </c>
-      <c r="F12">
-        <v>55</v>
-      </c>
-      <c r="H12">
-        <v>0</v>
-      </c>
-      <c r="I12">
-        <v>1.6</v>
-      </c>
-      <c r="J12">
-        <v>2.4</v>
-      </c>
-    </row>
-    <row r="13" spans="2:10">
-      <c r="B13" t="s">
-        <v>81</v>
-      </c>
-      <c r="C13" t="s">
-        <v>33</v>
-      </c>
-      <c r="D13" t="s">
-        <v>80</v>
-      </c>
-      <c r="E13">
-        <v>1</v>
-      </c>
-      <c r="F13">
-        <v>1</v>
-      </c>
-      <c r="H13">
-        <v>0</v>
-      </c>
-      <c r="I13">
-        <v>1.6</v>
-      </c>
-      <c r="J13">
-        <v>2.4</v>
-      </c>
-    </row>
-    <row r="14" spans="2:8">
-      <c r="B14" t="s">
-        <v>82</v>
-      </c>
-      <c r="C14" t="s">
-        <v>37</v>
-      </c>
-      <c r="D14" t="s">
-        <v>76</v>
-      </c>
-      <c r="E14">
-        <v>1</v>
-      </c>
-      <c r="F14">
-        <v>1</v>
-      </c>
-      <c r="G14" t="s">
-        <v>77</v>
-      </c>
-      <c r="H14">
+      <c r="D12" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="E12" s="1">
+        <v>1</v>
+      </c>
+      <c r="F12" s="1">
+        <v>1</v>
+      </c>
+      <c r="G12" s="1">
+        <v>1</v>
+      </c>
+      <c r="H12" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="I12" s="1">
+        <v>10</v>
+      </c>
+      <c r="J12" s="1">
         <v>0</v>
       </c>
     </row>
@@ -2136,10 +1804,19 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G8"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelRow="7" outlineLevelCol="6"/>
+  <dimension ref="A1:F8"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelRow="7" outlineLevelCol="5"/>
+  <cols>
+    <col min="1" max="1" width="13.0769230769231" customWidth="1"/>
+    <col min="2" max="2" width="18.7692307692308" customWidth="1"/>
+    <col min="3" max="3" width="17.6923076923077" customWidth="1"/>
+    <col min="4" max="4" width="24.3846153846154" customWidth="1"/>
+    <col min="5" max="5" width="44.1538461538462" customWidth="1"/>
+    <col min="6" max="6" width="15.1538461538462" customWidth="1"/>
+    <col min="7" max="7" width="32.1538461538462" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:6">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2147,146 +1824,140 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="D1" t="s">
+        <v>72</v>
+      </c>
+      <c r="E1" t="s">
+        <v>73</v>
+      </c>
+      <c r="F1" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
+      <c r="A2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" t="s">
+        <v>75</v>
+      </c>
+      <c r="C2" t="s">
+        <v>76</v>
+      </c>
+      <c r="D2" t="s">
+        <v>77</v>
+      </c>
+      <c r="E2" t="s">
+        <v>78</v>
+      </c>
+      <c r="F2" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3" t="s">
+        <v>80</v>
+      </c>
+      <c r="D3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E3" t="s">
+        <v>81</v>
+      </c>
+      <c r="F3" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="4" spans="2:6">
+      <c r="B4" t="s">
+        <v>51</v>
+      </c>
+      <c r="C4" t="s">
+        <v>82</v>
+      </c>
+      <c r="D4" t="s">
+        <v>54</v>
+      </c>
+      <c r="E4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F4">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" spans="2:6">
+      <c r="B5" t="s">
+        <v>64</v>
+      </c>
+      <c r="C5" t="s">
         <v>83</v>
       </c>
-      <c r="E1" t="s">
+      <c r="D5" t="s">
+        <v>54</v>
+      </c>
+      <c r="E5" t="b">
+        <v>1</v>
+      </c>
+      <c r="F5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="2:6">
+      <c r="B6" t="s">
+        <v>58</v>
+      </c>
+      <c r="C6" t="s">
         <v>84</v>
       </c>
-      <c r="F1" t="s">
+      <c r="D6" t="s">
+        <v>54</v>
+      </c>
+      <c r="E6" t="b">
+        <v>1</v>
+      </c>
+      <c r="F6">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="2:6">
+      <c r="B7" t="s">
+        <v>67</v>
+      </c>
+      <c r="C7" t="s">
+        <v>84</v>
+      </c>
+      <c r="D7" t="s">
         <v>85</v>
       </c>
-      <c r="G1" t="s">
+      <c r="E7" t="b">
+        <v>1</v>
+      </c>
+      <c r="F7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="2:6">
+      <c r="B8" t="s">
+        <v>61</v>
+      </c>
+      <c r="C8" t="s">
         <v>86</v>
       </c>
-    </row>
-    <row r="2" spans="1:7">
-      <c r="A2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B2" t="s">
-        <v>87</v>
-      </c>
-      <c r="C2" t="s">
-        <v>88</v>
-      </c>
-      <c r="D2" t="s">
-        <v>89</v>
-      </c>
-      <c r="E2" t="s">
-        <v>90</v>
-      </c>
-      <c r="F2" t="s">
-        <v>91</v>
-      </c>
-      <c r="G2" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
-      <c r="A3" t="s">
-        <v>14</v>
-      </c>
-      <c r="B3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C3" t="s">
-        <v>93</v>
-      </c>
-      <c r="D3" t="s">
-        <v>15</v>
-      </c>
-      <c r="E3" t="s">
-        <v>15</v>
-      </c>
-      <c r="F3" t="s">
-        <v>94</v>
-      </c>
-      <c r="G3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="4" spans="2:7">
-      <c r="B4" t="s">
-        <v>64</v>
-      </c>
-      <c r="C4" t="s">
-        <v>95</v>
-      </c>
-      <c r="F4" t="s">
-        <v>96</v>
-      </c>
-      <c r="G4">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="5" spans="2:7">
-      <c r="B5" t="s">
-        <v>70</v>
-      </c>
-      <c r="C5" t="s">
-        <v>97</v>
-      </c>
-      <c r="F5" t="s">
-        <v>96</v>
-      </c>
-      <c r="G5">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="6" spans="2:7">
-      <c r="B6" t="s">
-        <v>67</v>
-      </c>
-      <c r="C6" t="s">
-        <v>98</v>
-      </c>
-      <c r="E6" t="s">
-        <v>99</v>
-      </c>
-      <c r="F6" t="s">
-        <v>96</v>
-      </c>
-      <c r="G6">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7" spans="2:7">
-      <c r="B7" t="s">
-        <v>74</v>
-      </c>
-      <c r="C7" t="s">
-        <v>98</v>
-      </c>
-      <c r="D7" t="s">
-        <v>100</v>
-      </c>
-      <c r="E7" t="s">
-        <v>101</v>
-      </c>
-      <c r="F7" t="s">
-        <v>96</v>
-      </c>
-      <c r="G7">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="8" spans="2:7">
-      <c r="B8" t="s">
-        <v>77</v>
-      </c>
-      <c r="C8" t="s">
-        <v>102</v>
-      </c>
-      <c r="E8" t="s">
-        <v>103</v>
-      </c>
-      <c r="F8" t="s">
-        <v>96</v>
-      </c>
-      <c r="G8">
+      <c r="D8" t="s">
+        <v>54</v>
+      </c>
+      <c r="E8" t="b">
+        <v>1</v>
+      </c>
+      <c r="F8">
         <v>0</v>
       </c>
     </row>

--- a/GourmetProject/GameConfig/Datas/reward.xlsx
+++ b/GourmetProject/GameConfig/Datas/reward.xlsx
@@ -2333,7 +2333,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I13"/>
+  <dimension ref="A1:I14"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8" outlineLevelRow="7"/>
   <cols>
     <col width="13.0769230769231" customWidth="1" min="1" max="1"/>
@@ -2363,32 +2363,32 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>specialTags</t>
+          <t>allowFallback</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>allowFallback</t>
+          <t>distanceFloor</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>distanceFloor</t>
+          <t>explicitIds</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>explicitIds</t>
+          <t>minQuality</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>minQuality</t>
+          <t>withRandomFlavor</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>withRandomFlavor</t>
+          <t>*specialTags</t>
         </is>
       </c>
     </row>
@@ -2410,7 +2410,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>特殊标签筛选</t>
+          <t>是否允许兜底</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -2435,7 +2435,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>菜品奖励发放时附带随机风味</t>
+          <t>奖励池特殊标签筛选</t>
         </is>
       </c>
     </row>
@@ -2457,32 +2457,32 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
+          <t>bool</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
           <t>string</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
         <is>
           <t>bool</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>bool</t>
+          <t>list,RewardPoolSpecialTag</t>
         </is>
       </c>
     </row>
@@ -2497,17 +2497,16 @@
           <t>Dish</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="b">
-        <v>1</v>
-      </c>
-      <c r="F4" t="n">
+      <c r="D4" t="b">
+        <v>1</v>
+      </c>
+      <c r="E4" t="n">
         <v>5</v>
       </c>
-      <c r="H4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I4" t="b">
+      <c r="G4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2522,17 +2521,16 @@
           <t>Fragment</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="b">
-        <v>1</v>
-      </c>
-      <c r="F5" t="n">
+      <c r="D5" t="b">
+        <v>1</v>
+      </c>
+      <c r="E5" t="n">
         <v>5</v>
       </c>
-      <c r="H5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I5" t="b">
+      <c r="G5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2547,17 +2545,16 @@
           <t>PassiveItem</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="b">
-        <v>1</v>
-      </c>
-      <c r="F6" t="n">
+      <c r="D6" t="b">
+        <v>1</v>
+      </c>
+      <c r="E6" t="n">
         <v>5</v>
       </c>
-      <c r="H6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I6" t="b">
+      <c r="G6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2572,130 +2569,107 @@
           <t>PassiveItem</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>BossReward|ScoreBuild</t>
-        </is>
-      </c>
-      <c r="E7" t="b">
-        <v>1</v>
-      </c>
-      <c r="F7" t="n">
+      <c r="D7" t="b">
+        <v>1</v>
+      </c>
+      <c r="E7" t="n">
         <v>5</v>
       </c>
-      <c r="H7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I7" t="b">
-        <v>0</v>
+      <c r="G7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" t="b">
+        <v>0</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>BossReward</t>
+        </is>
       </c>
     </row>
     <row r="8">
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>pool_active</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>ActiveItem</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="b">
-        <v>1</v>
-      </c>
-      <c r="F8" t="n">
-        <v>0</v>
-      </c>
-      <c r="H8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I8" t="b">
-        <v>0</v>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>ScoreBuild</t>
+        </is>
       </c>
     </row>
     <row r="9">
       <c r="B9" t="inlineStr">
         <is>
-          <t>pool_flavored_dish</t>
+          <t>pool_active</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Dish</t>
-        </is>
-      </c>
-      <c r="E9" t="b">
-        <v>1</v>
-      </c>
-      <c r="F9" t="n">
-        <v>5</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I9" t="b">
-        <v>1</v>
+          <t>ActiveItem</t>
+        </is>
+      </c>
+      <c r="D9" t="b">
+        <v>1</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="B10" t="inlineStr">
         <is>
-          <t>pool_legendary</t>
+          <t>pool_flavored_dish</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>PassiveItem</t>
-        </is>
-      </c>
-      <c r="E10" t="b">
-        <v>1</v>
-      </c>
-      <c r="F10" t="n">
+          <t>Dish</t>
+        </is>
+      </c>
+      <c r="D10" t="b">
+        <v>1</v>
+      </c>
+      <c r="E10" t="n">
         <v>5</v>
       </c>
-      <c r="H10" t="n">
-        <v>4</v>
-      </c>
-      <c r="I10" t="b">
-        <v>0</v>
+      <c r="G10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="11">
       <c r="B11" t="inlineStr">
         <is>
-          <t>pool_lay_wood</t>
+          <t>pool_legendary</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>ActiveItem</t>
-        </is>
-      </c>
-      <c r="E11" t="b">
-        <v>1</v>
-      </c>
-      <c r="F11" t="n">
-        <v>0</v>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>item_active_lay_cherry|item_active_lay_walnut</t>
-        </is>
-      </c>
-      <c r="H11" t="n">
-        <v>0</v>
-      </c>
-      <c r="I11" t="b">
+          <t>PassiveItem</t>
+        </is>
+      </c>
+      <c r="D11" t="b">
+        <v>1</v>
+      </c>
+      <c r="E11" t="n">
+        <v>5</v>
+      </c>
+      <c r="G11" t="n">
+        <v>4</v>
+      </c>
+      <c r="H11" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="12">
       <c r="B12" t="inlineStr">
         <is>
-          <t>pool_lay_stone</t>
+          <t>pool_lay_wood</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -2703,50 +2677,79 @@
           <t>ActiveItem</t>
         </is>
       </c>
-      <c r="E12" t="b">
-        <v>1</v>
-      </c>
-      <c r="F12" t="n">
-        <v>0</v>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>item_active_lay_marble|item_active_lay_obsidian|item_active_lay_emerald</t>
-        </is>
-      </c>
-      <c r="H12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I12" t="b">
+      <c r="D12" t="b">
+        <v>1</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>item_active_lay_cherry|item_active_lay_walnut</t>
+        </is>
+      </c>
+      <c r="G12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="13">
       <c r="B13" t="inlineStr">
         <is>
+          <t>pool_lay_stone</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>ActiveItem</t>
+        </is>
+      </c>
+      <c r="D13" t="b">
+        <v>1</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>item_active_lay_marble|item_active_lay_obsidian|item_active_lay_emerald</t>
+        </is>
+      </c>
+      <c r="G13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" t="inlineStr">
+        <is>
           <t>pool_lay_metal</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C14" t="inlineStr">
         <is>
           <t>ActiveItem</t>
         </is>
       </c>
-      <c r="E13" t="b">
-        <v>1</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0</v>
-      </c>
-      <c r="G13" t="inlineStr">
+      <c r="D14" t="b">
+        <v>1</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" t="inlineStr">
         <is>
           <t>item_active_lay_gold|item_active_lay_silver</t>
         </is>
       </c>
-      <c r="H13" t="n">
-        <v>0</v>
-      </c>
-      <c r="I13" t="b">
+      <c r="G14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" t="b">
         <v>0</v>
       </c>
     </row>

--- a/GourmetProject/GameConfig/Datas/reward.xlsx
+++ b/GourmetProject/GameConfig/Datas/reward.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="15240" activeTab="1"/>
+    <workbookView windowHeight="15160" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="reward_package" sheetId="1" r:id="rId1"/>
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="308" uniqueCount="126">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="328" uniqueCount="134">
   <si>
     <t>##var</t>
   </si>
@@ -60,22 +60,22 @@
     <t>specific_gold</t>
   </si>
   <si>
-    <t>reward_food_dish</t>
-  </si>
-  <si>
-    <t>specific_dish</t>
-  </si>
-  <si>
     <t>reward_food_passive</t>
   </si>
   <si>
     <t>specific_passive</t>
   </si>
   <si>
-    <t>reward_food_active</t>
-  </si>
-  <si>
-    <t>specific_active</t>
+    <t>reward_food_active_strengthen</t>
+  </si>
+  <si>
+    <t>specific_active_strengthen</t>
+  </si>
+  <si>
+    <t>reward_food_active_adjust</t>
+  </si>
+  <si>
+    <t>specific_active_adjust</t>
   </si>
   <si>
     <t>reward_food_fragment</t>
@@ -87,13 +87,13 @@
     <t>reward_food_hard_gold</t>
   </si>
   <si>
-    <t>reward_food_hard_dish</t>
-  </si>
-  <si>
     <t>reward_food_hard_passive</t>
   </si>
   <si>
-    <t>reward_food_hard_active</t>
+    <t>reward_food_hard_active_strengthen</t>
+  </si>
+  <si>
+    <t>reward_food_hard_active_adjust</t>
   </si>
   <si>
     <t>reward_food_hard_fragment</t>
@@ -207,21 +207,18 @@
     <t>10,30</t>
   </si>
   <si>
-    <t>slot_specific_dish</t>
+    <t>slot_specific_passive</t>
+  </si>
+  <si>
+    <t>PassiveItemChoice</t>
+  </si>
+  <si>
+    <t>pool_passive</t>
   </si>
   <si>
     <t>3,6</t>
   </si>
   <si>
-    <t>slot_specific_passive</t>
-  </si>
-  <si>
-    <t>PassiveItemChoice</t>
-  </si>
-  <si>
-    <t>pool_passive</t>
-  </si>
-  <si>
     <t>slot_specific_fragment</t>
   </si>
   <si>
@@ -229,6 +226,42 @@
   </si>
   <si>
     <t>pool_fragment</t>
+  </si>
+  <si>
+    <t>slot_specific_active_strengthen</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>ActiveItemStrengthen</t>
+    </r>
+  </si>
+  <si>
+    <t>pool_active_strengthen</t>
+  </si>
+  <si>
+    <t>slot_specific_active_adjust</t>
+  </si>
+  <si>
+    <t>ActiveItemAdjust</t>
+  </si>
+  <si>
+    <t>pool_active_adjust</t>
+  </si>
+  <si>
+    <t>slot_boss_dish</t>
+  </si>
+  <si>
+    <t>boss_dish</t>
+  </si>
+  <si>
+    <t>10,0</t>
   </si>
   <si>
     <t>slot_boss_passive</t>
@@ -1013,7 +1046,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1021,8 +1054,14 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
@@ -1374,170 +1413,170 @@
   <dimension ref="A1:D14"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="3"/>
   <cols>
-    <col min="1" max="1" width="13.0769230769231" style="1" customWidth="1"/>
-    <col min="2" max="2" width="29.0769230769231" style="1" customWidth="1"/>
-    <col min="3" max="3" width="39.5384615384615" style="1" customWidth="1"/>
-    <col min="4" max="4" width="37.0769230769231" style="1" customWidth="1"/>
-    <col min="5" max="16384" width="9" style="1" customWidth="1"/>
+    <col min="1" max="1" width="13.0769230769231" style="5" customWidth="1"/>
+    <col min="2" max="2" width="37.5384615384615" style="5" customWidth="1"/>
+    <col min="3" max="3" width="39.5384615384615" style="5" customWidth="1"/>
+    <col min="4" max="4" width="37.0769230769231" style="5" customWidth="1"/>
+    <col min="5" max="16384" width="9" style="5" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
+      <c r="B1" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="5" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="2" spans="1:4">
-      <c r="A2" s="1" t="s">
+      <c r="A2" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="D2" s="5" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="3" spans="1:4">
-      <c r="A3" s="1" t="s">
+      <c r="A3" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="B3" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="C3" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="D3" s="5" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="4" spans="2:4">
-      <c r="B4" s="1" t="s">
+      <c r="B4" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="C4" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="D4" s="1" t="s">
+      <c r="D4" s="5" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="5" spans="2:4">
-      <c r="B5" s="1" t="s">
+      <c r="B5" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="C5" s="1" t="s">
+      <c r="C5" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="D5" s="1" t="s">
+      <c r="D5" s="5" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="6" spans="2:4">
-      <c r="B6" s="1" t="s">
+      <c r="B6" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="C6" s="1" t="s">
+      <c r="C6" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="D6" s="1" t="s">
+      <c r="D6" s="5" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="7" spans="2:4">
-      <c r="B7" s="1" t="s">
+      <c r="B7" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="C7" s="1" t="s">
+      <c r="C7" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="D7" s="1" t="s">
+      <c r="D7" s="5" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="8" spans="2:4">
-      <c r="B8" s="1" t="s">
+      <c r="B8" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="C8" s="1" t="s">
+      <c r="C8" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="D8" s="1" t="s">
+      <c r="D8" s="5" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="9" spans="2:4">
-      <c r="B9" s="1" t="s">
+      <c r="B9" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="C9" s="1" t="s">
+      <c r="C9" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="D9" s="1" t="s">
+      <c r="D9" s="5" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="10" spans="2:4">
-      <c r="B10" s="1" t="s">
+      <c r="B10" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="C10" s="1" t="s">
+      <c r="C10" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="D10" s="1" t="s">
+      <c r="D10" s="5" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="11" spans="2:4">
-      <c r="B11" s="1" t="s">
+      <c r="B11" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="C11" s="1" t="s">
+      <c r="C11" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="D11" s="1" t="s">
+      <c r="D11" s="5" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="12" spans="2:4">
-      <c r="B12" s="1" t="s">
+      <c r="B12" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="C12" s="1" t="s">
+      <c r="C12" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="D12" s="1" t="s">
+      <c r="D12" s="5" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="13" spans="2:4">
-      <c r="B13" s="1" t="s">
+      <c r="B13" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="C13" s="1" t="s">
+      <c r="C13" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="D13" s="1" t="s">
+      <c r="D13" s="5" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="14" spans="2:3">
-      <c r="B14" s="1" t="s">
+      <c r="B14" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="C14" s="1" t="s">
+      <c r="C14" s="5" t="s">
         <v>28</v>
       </c>
     </row>
@@ -1550,322 +1589,325 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:L25"/>
+  <dimension ref="A1:O27"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
-    <col min="1" max="1" width="13.0769230769231" style="1" customWidth="1"/>
-    <col min="2" max="2" width="23" style="1" customWidth="1"/>
-    <col min="3" max="3" width="18.3076923076923" style="1" customWidth="1"/>
-    <col min="4" max="4" width="19.2307692307692" style="1" customWidth="1"/>
-    <col min="5" max="5" width="13.0769230769231" style="1" customWidth="1"/>
-    <col min="6" max="6" width="22.4615384615385" style="1" customWidth="1"/>
-    <col min="7" max="7" width="8.15384615384615" style="1" customWidth="1"/>
-    <col min="8" max="8" width="18.7692307692308" style="1" customWidth="1"/>
-    <col min="9" max="9" width="22.4615384615385" style="1" customWidth="1"/>
-    <col min="10" max="10" width="27.3076923076923" style="1" customWidth="1"/>
-    <col min="11" max="11" width="31.0769230769231" style="1" customWidth="1"/>
-    <col min="12" max="12" width="19.3846153846154" style="1" customWidth="1"/>
-    <col min="13" max="16384" width="9" style="1" customWidth="1"/>
+    <col min="1" max="1" width="13.0769230769231" style="5" customWidth="1"/>
+    <col min="2" max="2" width="31.5384615384615" style="5" customWidth="1"/>
+    <col min="3" max="3" width="26.7692307692308" style="5" customWidth="1"/>
+    <col min="4" max="4" width="22" style="5" customWidth="1"/>
+    <col min="5" max="5" width="13.0769230769231" style="5" customWidth="1"/>
+    <col min="6" max="6" width="22.4615384615385" style="5" customWidth="1"/>
+    <col min="7" max="7" width="8.15384615384615" style="5" customWidth="1"/>
+    <col min="8" max="8" width="23.6923076923077" style="5" customWidth="1"/>
+    <col min="9" max="9" width="22.4615384615385" style="5" customWidth="1"/>
+    <col min="10" max="10" width="27.3076923076923" style="5" customWidth="1"/>
+    <col min="11" max="11" width="31.0769230769231" style="5" customWidth="1"/>
+    <col min="12" max="12" width="19.3846153846154" style="5" customWidth="1"/>
+    <col min="13" max="16384" width="9" style="5" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
+      <c r="B1" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J1" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="K1" t="s">
+      <c r="K1" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="L1" t="s">
+      <c r="L1" s="5" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="2" spans="1:12">
-      <c r="A2" s="1" t="s">
+      <c r="A2" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="D2" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="E2" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="F2" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="G2" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="H2" s="1" t="s">
+      <c r="H2" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="I2" t="s">
+      <c r="I2" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="J2" t="s">
+      <c r="J2" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="K2" t="s">
+      <c r="K2" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="L2" t="s">
+      <c r="L2" s="5" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="3" spans="1:12">
-      <c r="A3" s="1" t="s">
+      <c r="A3" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="B3" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="C3" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="D3" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="E3" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="F3" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="G3" s="1" t="s">
+      <c r="G3" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="H3" s="1" t="s">
+      <c r="H3" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="I3" t="s">
+      <c r="I3" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="J3" t="s">
+      <c r="J3" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="K3" t="s">
+      <c r="K3" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="L3" t="s">
+      <c r="L3" s="5" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="4" spans="2:12">
-      <c r="B4" s="1" t="s">
+      <c r="B4" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="C4" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="D4" s="1" t="s">
+      <c r="D4" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="E4" s="1">
+      <c r="E4" s="5">
         <v>3</v>
       </c>
-      <c r="F4" s="1">
-        <v>1</v>
-      </c>
-      <c r="G4" s="1">
-        <v>1</v>
-      </c>
-      <c r="H4" s="1" t="s">
+      <c r="F4" s="5">
+        <v>1</v>
+      </c>
+      <c r="G4" s="5">
+        <v>1</v>
+      </c>
+      <c r="H4" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="I4" t="s">
+      <c r="I4" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="J4" t="s">
-        <v>58</v>
-      </c>
-      <c r="K4" t="s">
-        <v>58</v>
-      </c>
-      <c r="L4" t="s">
+      <c r="J4" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="K4" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="L4" s="5" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="5" spans="2:12">
-      <c r="B5" s="1" t="s">
+      <c r="B5" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="C5" s="1" t="s">
+      <c r="C5" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="D5" s="1" t="s">
+      <c r="D5" s="5" t="s">
         <v>60</v>
       </c>
-      <c r="E5" s="1">
-        <v>1</v>
-      </c>
-      <c r="F5" s="1">
-        <v>1</v>
-      </c>
-      <c r="G5" s="1">
-        <v>1</v>
-      </c>
-      <c r="H5" s="1" t="s">
+      <c r="E5" s="5">
+        <v>1</v>
+      </c>
+      <c r="F5" s="5">
+        <v>1</v>
+      </c>
+      <c r="G5" s="5">
+        <v>1</v>
+      </c>
+      <c r="H5" s="5" t="s">
         <v>61</v>
       </c>
-      <c r="I5" t="s">
-        <v>58</v>
-      </c>
-      <c r="J5" t="s">
-        <v>58</v>
-      </c>
-      <c r="K5" t="s">
-        <v>58</v>
-      </c>
-      <c r="L5" t="s">
+      <c r="I5" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="J5" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="K5" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="L5" s="5" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="6" spans="2:12">
-      <c r="B6" s="1" t="s">
+      <c r="B6" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="C6" s="1" t="s">
+      <c r="C6" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="D6" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="E6" s="1">
+      <c r="D6" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="E6" s="5">
         <v>3</v>
       </c>
-      <c r="F6" s="1">
-        <v>1</v>
-      </c>
-      <c r="G6" s="1">
-        <v>1</v>
-      </c>
-      <c r="H6" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="I6" t="s">
-        <v>64</v>
-      </c>
-      <c r="J6" t="s">
-        <v>58</v>
-      </c>
-      <c r="K6" t="s">
-        <v>58</v>
-      </c>
-      <c r="L6" t="s">
+      <c r="F6" s="5">
+        <v>1</v>
+      </c>
+      <c r="G6" s="5">
+        <v>1</v>
+      </c>
+      <c r="H6" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="I6" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="J6" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="K6" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="L6" s="5" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="7" spans="2:12">
-      <c r="B7" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="C7" s="1" t="s">
+      <c r="B7" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="E7" s="5">
+        <v>3</v>
+      </c>
+      <c r="F7" s="5">
+        <v>1</v>
+      </c>
+      <c r="G7" s="5">
+        <v>1</v>
+      </c>
+      <c r="H7" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="I7" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="J7" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="K7" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="L7" s="5" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="8" ht="17" spans="2:15">
+      <c r="B8" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="C8" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="D7" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="E7" s="1">
+      <c r="D8" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="E8" s="2">
         <v>3</v>
       </c>
-      <c r="F7" s="1">
-        <v>1</v>
-      </c>
-      <c r="G7" s="1">
-        <v>1</v>
-      </c>
-      <c r="H7" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="I7" t="s">
-        <v>58</v>
-      </c>
-      <c r="J7" t="s">
-        <v>64</v>
-      </c>
-      <c r="K7" t="s">
-        <v>58</v>
-      </c>
-      <c r="L7" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="8" spans="2:12">
-      <c r="B8" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="E8" s="1">
-        <v>3</v>
-      </c>
-      <c r="F8" s="1">
-        <v>1</v>
-      </c>
-      <c r="G8" s="1">
-        <v>1</v>
-      </c>
-      <c r="H8" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="I8" t="s">
-        <v>58</v>
-      </c>
-      <c r="J8" t="s">
-        <v>58</v>
-      </c>
-      <c r="K8" t="s">
-        <v>64</v>
-      </c>
-      <c r="L8" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="9" spans="2:12">
+      <c r="F8" s="2">
+        <v>1</v>
+      </c>
+      <c r="G8" s="2">
+        <v>1</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="I8" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="J8" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="K8" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="L8" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="O8" s="5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="9" spans="2:15">
       <c r="B9" s="2" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>72</v>
+        <v>19</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>66</v>
+        <v>74</v>
       </c>
       <c r="E9" s="2">
         <v>3</v>
@@ -1877,578 +1919,652 @@
         <v>1</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="I9" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="J9" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="K9" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="L9" s="4" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="10" spans="2:12">
-      <c r="B10" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="C10" s="2" t="s">
+      <c r="I9" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="J9" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="K9" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="L9" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="O9" s="5" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="10" s="4" customFormat="1" spans="2:15">
+      <c r="B10" s="4" t="s">
         <v>76</v>
       </c>
-      <c r="D10" s="2" t="s">
+      <c r="C10" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="E10" s="4">
+        <v>3</v>
+      </c>
+      <c r="F10" s="4">
+        <v>1</v>
+      </c>
+      <c r="G10" s="4">
+        <v>1</v>
+      </c>
+      <c r="H10" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="I10" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="J10" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="K10" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="L10" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="O10" s="5"/>
+    </row>
+    <row r="11" s="4" customFormat="1" spans="2:12">
+      <c r="B11" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="E11" s="4">
+        <v>3</v>
+      </c>
+      <c r="F11" s="4">
+        <v>1</v>
+      </c>
+      <c r="G11" s="4">
+        <v>1</v>
+      </c>
+      <c r="H11" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="I11" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="J11" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="K11" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="L11" s="4" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="12" s="4" customFormat="1" spans="2:12">
+      <c r="B12" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="E12" s="4">
+        <v>3</v>
+      </c>
+      <c r="F12" s="4">
+        <v>1</v>
+      </c>
+      <c r="G12" s="4">
+        <v>1</v>
+      </c>
+      <c r="H12" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="E10" s="2">
+      <c r="I12" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="J12" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="K12" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="L12" s="4" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="13" s="4" customFormat="1" spans="2:12">
+      <c r="B13" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="D13" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="E13" s="4">
+        <v>1</v>
+      </c>
+      <c r="F13" s="4">
+        <v>1</v>
+      </c>
+      <c r="G13" s="4">
+        <v>1</v>
+      </c>
+      <c r="H13" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="I13" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="J13" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="K13" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="L13" s="4" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="14" spans="2:12">
+      <c r="B14" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="C14" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="D14" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="E14" s="5">
         <v>3</v>
       </c>
-      <c r="F10" s="2">
-        <v>1</v>
-      </c>
-      <c r="G10" s="2">
-        <v>1</v>
-      </c>
-      <c r="H10" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="I10" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="J10" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="K10" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="L10" s="4" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="11" spans="2:12">
-      <c r="B11" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="E11" s="2">
-        <v>1</v>
-      </c>
-      <c r="F11" s="2">
-        <v>1</v>
-      </c>
-      <c r="G11" s="2">
-        <v>1</v>
-      </c>
-      <c r="H11" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="I11" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="J11" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="K11" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="L11" s="4" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="12" spans="2:12">
-      <c r="B12" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="D12" s="3" t="s">
+      <c r="F14" s="5">
+        <v>1</v>
+      </c>
+      <c r="G14" s="5">
+        <v>1</v>
+      </c>
+      <c r="H14" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="I14" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="J14" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="K14" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="L14" s="5" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="15" spans="2:12">
+      <c r="B15" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="C15" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="D15" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="E12" s="3">
+      <c r="E15" s="5">
+        <v>1</v>
+      </c>
+      <c r="F15" s="5">
+        <v>1</v>
+      </c>
+      <c r="G15" s="5">
+        <v>1</v>
+      </c>
+      <c r="H15" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="I15" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="J15" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="K15" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="L15" s="5" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="16" spans="2:12">
+      <c r="B16" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="C16" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="D16" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="E16" s="5">
+        <v>1</v>
+      </c>
+      <c r="F16" s="5">
+        <v>1</v>
+      </c>
+      <c r="G16" s="5">
+        <v>1</v>
+      </c>
+      <c r="H16" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="I16" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="J16" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="K16" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="L16" s="5" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="17" spans="2:12">
+      <c r="B17" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="C17" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="D17" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="E17" s="5">
         <v>3</v>
       </c>
-      <c r="F12" s="3">
-        <v>1</v>
-      </c>
-      <c r="G12" s="3">
-        <v>1</v>
-      </c>
-      <c r="H12" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="I12" t="s">
-        <v>58</v>
-      </c>
-      <c r="J12" t="s">
-        <v>58</v>
-      </c>
-      <c r="K12" t="s">
-        <v>58</v>
-      </c>
-      <c r="L12" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="13" spans="2:12">
-      <c r="B13" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="D13" s="3" t="s">
+      <c r="F17" s="5">
+        <v>1</v>
+      </c>
+      <c r="G17" s="5">
+        <v>1</v>
+      </c>
+      <c r="H17" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="I17" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="J17" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="K17" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="L17" s="5" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="18" spans="2:12">
+      <c r="B18" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="C18" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="D18" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="E18" s="5">
+        <v>2</v>
+      </c>
+      <c r="F18" s="5">
+        <v>2</v>
+      </c>
+      <c r="G18" s="5">
+        <v>1</v>
+      </c>
+      <c r="H18" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="I18" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="J18" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="K18" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="L18" s="5" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="19" spans="2:12">
+      <c r="B19" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="C19" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="D19" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="E19" s="5">
+        <v>1</v>
+      </c>
+      <c r="F19" s="5">
+        <v>1</v>
+      </c>
+      <c r="G19" s="5">
+        <v>1</v>
+      </c>
+      <c r="H19" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="I19" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="J19" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="K19" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="L19" s="5" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="20" spans="2:12">
+      <c r="B20" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="C20" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="D20" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="E20" s="5">
+        <v>2</v>
+      </c>
+      <c r="F20" s="5">
+        <v>2</v>
+      </c>
+      <c r="G20" s="5">
+        <v>1</v>
+      </c>
+      <c r="H20" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="I20" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="J20" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="K20" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="L20" s="5" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="21" spans="2:12">
+      <c r="B21" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="C21" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="D21" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="E21" s="5">
+        <v>3</v>
+      </c>
+      <c r="F21" s="5">
+        <v>1</v>
+      </c>
+      <c r="G21" s="5">
+        <v>1</v>
+      </c>
+      <c r="H21" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="I21" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="J21" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="K21" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="L21" s="5" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="22" spans="2:12">
+      <c r="B22" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="C22" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="D22" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="E22" s="5">
+        <v>3</v>
+      </c>
+      <c r="F22" s="5">
+        <v>1</v>
+      </c>
+      <c r="G22" s="5">
+        <v>1</v>
+      </c>
+      <c r="H22" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="I22" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="J22" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="K22" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="L22" s="5" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="23" spans="2:12">
+      <c r="B23" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="C23" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="D23" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="E13" s="3">
-        <v>1</v>
-      </c>
-      <c r="F13" s="3">
-        <v>1</v>
-      </c>
-      <c r="G13" s="3">
-        <v>1</v>
-      </c>
-      <c r="H13" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="I13" t="s">
-        <v>58</v>
-      </c>
-      <c r="J13" t="s">
-        <v>58</v>
-      </c>
-      <c r="K13" t="s">
-        <v>58</v>
-      </c>
-      <c r="L13" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="14" spans="2:12">
-      <c r="B14" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="C14" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="D14" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="E14" s="3">
-        <v>1</v>
-      </c>
-      <c r="F14" s="3">
-        <v>1</v>
-      </c>
-      <c r="G14" s="3">
-        <v>1</v>
-      </c>
-      <c r="H14" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="I14" t="s">
-        <v>58</v>
-      </c>
-      <c r="J14" t="s">
-        <v>58</v>
-      </c>
-      <c r="K14" t="s">
-        <v>58</v>
-      </c>
-      <c r="L14" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="15" spans="2:12">
-      <c r="B15" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="C15" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="D15" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="E15" s="3">
+      <c r="E23" s="5">
         <v>3</v>
       </c>
-      <c r="F15" s="3">
-        <v>1</v>
-      </c>
-      <c r="G15" s="3">
-        <v>1</v>
-      </c>
-      <c r="H15" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="I15" t="s">
-        <v>58</v>
-      </c>
-      <c r="J15" t="s">
-        <v>58</v>
-      </c>
-      <c r="K15" t="s">
-        <v>58</v>
-      </c>
-      <c r="L15" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="16" spans="2:12">
-      <c r="B16" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="C16" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="D16" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="E16" s="3">
-        <v>2</v>
-      </c>
-      <c r="F16" s="3">
-        <v>2</v>
-      </c>
-      <c r="G16" s="3">
-        <v>1</v>
-      </c>
-      <c r="H16" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="I16" t="s">
-        <v>58</v>
-      </c>
-      <c r="J16" t="s">
-        <v>58</v>
-      </c>
-      <c r="K16" t="s">
-        <v>58</v>
-      </c>
-      <c r="L16" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="17" spans="2:12">
-      <c r="B17" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="C17" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="D17" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="E17" s="3">
-        <v>1</v>
-      </c>
-      <c r="F17" s="3">
-        <v>1</v>
-      </c>
-      <c r="G17" s="3">
-        <v>1</v>
-      </c>
-      <c r="H17" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="I17" t="s">
-        <v>58</v>
-      </c>
-      <c r="J17" t="s">
-        <v>58</v>
-      </c>
-      <c r="K17" t="s">
-        <v>58</v>
-      </c>
-      <c r="L17" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="18" spans="2:12">
-      <c r="B18" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="C18" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="D18" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="E18" s="3">
-        <v>2</v>
-      </c>
-      <c r="F18" s="3">
-        <v>2</v>
-      </c>
-      <c r="G18" s="3">
-        <v>1</v>
-      </c>
-      <c r="H18" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="I18" t="s">
-        <v>58</v>
-      </c>
-      <c r="J18" t="s">
-        <v>58</v>
-      </c>
-      <c r="K18" t="s">
-        <v>58</v>
-      </c>
-      <c r="L18" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="19" spans="2:12">
-      <c r="B19" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="C19" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="D19" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="E19" s="3">
+      <c r="F23" s="5">
         <v>3</v>
       </c>
-      <c r="F19" s="3">
-        <v>1</v>
-      </c>
-      <c r="G19" s="3">
-        <v>1</v>
-      </c>
-      <c r="H19" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="I19" t="s">
-        <v>58</v>
-      </c>
-      <c r="J19" t="s">
-        <v>58</v>
-      </c>
-      <c r="K19" t="s">
-        <v>58</v>
-      </c>
-      <c r="L19" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="20" spans="2:12">
-      <c r="B20" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="C20" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="D20" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="E20" s="3">
-        <v>3</v>
-      </c>
-      <c r="F20" s="3">
-        <v>1</v>
-      </c>
-      <c r="G20" s="3">
-        <v>1</v>
-      </c>
-      <c r="H20" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="I20" t="s">
-        <v>58</v>
-      </c>
-      <c r="J20" t="s">
-        <v>58</v>
-      </c>
-      <c r="K20" t="s">
-        <v>58</v>
-      </c>
-      <c r="L20" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="21" spans="2:12">
-      <c r="B21" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="C21" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="D21" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="E21" s="3">
-        <v>3</v>
-      </c>
-      <c r="F21" s="3">
-        <v>3</v>
-      </c>
-      <c r="G21" s="3">
-        <v>1</v>
-      </c>
-      <c r="H21" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="I21" t="s">
-        <v>58</v>
-      </c>
-      <c r="J21" t="s">
-        <v>58</v>
-      </c>
-      <c r="K21" t="s">
-        <v>58</v>
-      </c>
-      <c r="L21" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="22" spans="2:12">
-      <c r="B22" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="C22" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="D22" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="E22" s="3">
-        <v>1</v>
-      </c>
-      <c r="F22" s="3">
-        <v>1</v>
-      </c>
-      <c r="G22" s="3">
-        <v>1</v>
-      </c>
-      <c r="H22" s="3" t="s">
+      <c r="G23" s="5">
+        <v>1</v>
+      </c>
+      <c r="H23" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="I23" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="J23" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="K23" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="L23" s="5" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="24" spans="2:12">
+      <c r="B24" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="C24" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="D24" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="E24" s="5">
+        <v>1</v>
+      </c>
+      <c r="F24" s="5">
+        <v>1</v>
+      </c>
+      <c r="G24" s="5">
+        <v>1</v>
+      </c>
+      <c r="H24" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="I24" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="J24" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="K24" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="L24" s="5" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="25" spans="2:12">
+      <c r="B25" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="C25" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="D25" s="5" t="s">
         <v>94</v>
       </c>
-      <c r="I22" t="s">
-        <v>58</v>
-      </c>
-      <c r="J22" t="s">
-        <v>58</v>
-      </c>
-      <c r="K22" t="s">
-        <v>58</v>
-      </c>
-      <c r="L22" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="23" spans="2:12">
-      <c r="B23" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="C23" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="D23" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="E23" s="3">
-        <v>1</v>
-      </c>
-      <c r="F23" s="3">
-        <v>1</v>
-      </c>
-      <c r="G23" s="3">
-        <v>1</v>
-      </c>
-      <c r="H23" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="I23" t="s">
-        <v>58</v>
-      </c>
-      <c r="J23" t="s">
-        <v>58</v>
-      </c>
-      <c r="K23" t="s">
-        <v>58</v>
-      </c>
-      <c r="L23" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="24" spans="2:12">
-      <c r="B24" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="C24" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="D24" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="E24" s="3">
-        <v>1</v>
-      </c>
-      <c r="F24" s="3">
-        <v>1</v>
-      </c>
-      <c r="G24" s="3">
-        <v>1</v>
-      </c>
-      <c r="H24" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="I24" t="s">
-        <v>58</v>
-      </c>
-      <c r="J24" t="s">
-        <v>58</v>
-      </c>
-      <c r="K24" t="s">
-        <v>58</v>
-      </c>
-      <c r="L24" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="25" spans="2:12">
-      <c r="B25" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="C25" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="D25" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="E25" s="3">
-        <v>1</v>
-      </c>
-      <c r="F25" s="3">
-        <v>1</v>
-      </c>
-      <c r="G25" s="3">
-        <v>1</v>
-      </c>
-      <c r="H25" s="3" t="s">
-        <v>100</v>
-      </c>
-      <c r="I25" t="s">
-        <v>58</v>
-      </c>
-      <c r="J25" t="s">
-        <v>58</v>
-      </c>
-      <c r="K25" t="s">
-        <v>58</v>
-      </c>
-      <c r="L25" t="s">
+      <c r="E25" s="5">
+        <v>1</v>
+      </c>
+      <c r="F25" s="5">
+        <v>1</v>
+      </c>
+      <c r="G25" s="5">
+        <v>1</v>
+      </c>
+      <c r="H25" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="I25" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="J25" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="K25" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="L25" s="5" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="26" spans="2:12">
+      <c r="B26" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="C26" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="D26" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="E26" s="5">
+        <v>1</v>
+      </c>
+      <c r="F26" s="5">
+        <v>1</v>
+      </c>
+      <c r="G26" s="5">
+        <v>1</v>
+      </c>
+      <c r="H26" s="5" t="s">
+        <v>106</v>
+      </c>
+      <c r="I26" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="J26" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="K26" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="L26" s="5" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="27" spans="2:12">
+      <c r="B27" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="C27" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="D27" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="E27" s="5">
+        <v>1</v>
+      </c>
+      <c r="F27" s="5">
+        <v>1</v>
+      </c>
+      <c r="G27" s="5">
+        <v>1</v>
+      </c>
+      <c r="H27" s="5" t="s">
+        <v>108</v>
+      </c>
+      <c r="I27" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="J27" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="K27" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="L27" s="5" t="s">
         <v>58</v>
       </c>
     </row>
@@ -2464,316 +2580,337 @@
   <dimension ref="A1:I14"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
-    <col min="1" max="1" width="13.0769230769231" customWidth="1"/>
-    <col min="2" max="2" width="18.7692307692308" customWidth="1"/>
-    <col min="3" max="3" width="17.6923076923077" customWidth="1"/>
-    <col min="4" max="4" width="24.3846153846154" customWidth="1"/>
-    <col min="5" max="5" width="44.1538461538462" customWidth="1"/>
-    <col min="6" max="6" width="15.1538461538462" customWidth="1"/>
-    <col min="7" max="7" width="32.1538461538462" customWidth="1"/>
+    <col min="1" max="1" width="13.0769230769231" style="1" customWidth="1"/>
+    <col min="2" max="2" width="23.6923076923077" style="1" customWidth="1"/>
+    <col min="3" max="3" width="22" style="1" customWidth="1"/>
+    <col min="4" max="4" width="24.3846153846154" style="1" customWidth="1"/>
+    <col min="5" max="5" width="44.1538461538462" style="1" customWidth="1"/>
+    <col min="6" max="6" width="77.1538461538462" style="1" customWidth="1"/>
+    <col min="7" max="7" width="54.3076923076923" style="1" customWidth="1"/>
+    <col min="8" max="8" width="9" style="1"/>
+    <col min="9" max="9" width="27.0769230769231" style="1" customWidth="1"/>
+    <col min="10" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9">
-      <c r="A1" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D1" t="s">
-        <v>101</v>
-      </c>
-      <c r="E1" t="s">
+      <c r="D1" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
+      <c r="A2" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9">
+      <c r="A3" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="4" spans="2:8">
+      <c r="B4" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="D4" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="E4" s="1">
+        <v>5</v>
+      </c>
+      <c r="G4" s="1">
+        <v>0</v>
+      </c>
+      <c r="H4" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="2:8">
+      <c r="B5" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="D5" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="E5" s="1">
+        <v>5</v>
+      </c>
+      <c r="G5" s="1">
+        <v>0</v>
+      </c>
+      <c r="H5" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="2:8">
+      <c r="B6" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="D6" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="E6" s="1">
+        <v>5</v>
+      </c>
+      <c r="G6" s="1">
+        <v>0</v>
+      </c>
+      <c r="H6" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="2:9">
+      <c r="B7" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="D7" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="E7" s="1">
+        <v>5</v>
+      </c>
+      <c r="G7" s="1">
+        <v>0</v>
+      </c>
+      <c r="H7" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="I7" s="1" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="8" ht="17" spans="2:9">
+      <c r="B8" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="D8" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="E8" s="1">
+        <v>5</v>
+      </c>
+      <c r="G8" s="1">
+        <v>0</v>
+      </c>
+      <c r="H8" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="I8" s="1" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="9" spans="2:8">
+      <c r="B9" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="D9" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="E9" s="1">
+        <v>5</v>
+      </c>
+      <c r="G9" s="1">
+        <v>0</v>
+      </c>
+      <c r="H9" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="2:8">
+      <c r="B10" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="D10" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="E10" s="1">
+        <v>5</v>
+      </c>
+      <c r="G10" s="1">
+        <v>0</v>
+      </c>
+      <c r="H10" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="2:8">
+      <c r="B11" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="F1" t="s">
-        <v>103</v>
-      </c>
-      <c r="G1" t="s">
+      <c r="C11" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="D11" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="E11" s="1">
+        <v>5</v>
+      </c>
+      <c r="G11" s="1">
+        <v>4</v>
+      </c>
+      <c r="H11" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="2:8">
+      <c r="B12" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="H1" t="s">
-        <v>105</v>
-      </c>
-      <c r="I1" t="s">
+      <c r="C12" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="D12" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="E12" s="1">
+        <v>0</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="G12" s="1">
+        <v>0</v>
+      </c>
+      <c r="H12" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="2:8">
+      <c r="B13" s="1" t="s">
         <v>106</v>
       </c>
-    </row>
-    <row r="2" spans="1:9">
-      <c r="A2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B2" t="s">
-        <v>107</v>
-      </c>
-      <c r="C2" t="s">
+      <c r="C13" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="D13" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="E13" s="1">
+        <v>0</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="G13" s="1">
+        <v>0</v>
+      </c>
+      <c r="H13" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="2:8">
+      <c r="B14" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="D2" t="s">
-        <v>109</v>
-      </c>
-      <c r="E2" t="s">
-        <v>109</v>
-      </c>
-      <c r="F2" t="s">
-        <v>110</v>
-      </c>
-      <c r="G2" t="s">
-        <v>111</v>
-      </c>
-      <c r="H2" t="s">
-        <v>112</v>
-      </c>
-      <c r="I2" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9">
-      <c r="A3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C3" t="s">
-        <v>114</v>
-      </c>
-      <c r="D3" t="s">
-        <v>115</v>
-      </c>
-      <c r="E3" t="s">
-        <v>51</v>
-      </c>
-      <c r="F3" t="s">
-        <v>9</v>
-      </c>
-      <c r="G3" t="s">
-        <v>51</v>
-      </c>
-      <c r="H3" t="s">
-        <v>115</v>
-      </c>
-      <c r="I3" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="4" spans="2:8">
-      <c r="B4" t="s">
-        <v>56</v>
-      </c>
-      <c r="C4" t="s">
-        <v>117</v>
-      </c>
-      <c r="D4" t="b">
-        <v>1</v>
-      </c>
-      <c r="E4">
-        <v>5</v>
-      </c>
-      <c r="G4">
+      <c r="C14" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="D14" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="E14" s="1">
         <v>0</v>
       </c>
-      <c r="H4" t="b">
+      <c r="F14" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="G14" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="2:8">
-      <c r="B5" t="s">
-        <v>70</v>
-      </c>
-      <c r="C5" t="s">
-        <v>118</v>
-      </c>
-      <c r="D5" t="b">
-        <v>1</v>
-      </c>
-      <c r="E5">
-        <v>5</v>
-      </c>
-      <c r="G5">
-        <v>0</v>
-      </c>
-      <c r="H5" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="2:8">
-      <c r="B6" t="s">
-        <v>67</v>
-      </c>
-      <c r="C6" t="s">
-        <v>119</v>
-      </c>
-      <c r="D6" t="b">
-        <v>1</v>
-      </c>
-      <c r="E6">
-        <v>5</v>
-      </c>
-      <c r="G6">
-        <v>0</v>
-      </c>
-      <c r="H6" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="2:9">
-      <c r="B7" t="s">
-        <v>73</v>
-      </c>
-      <c r="C7" t="s">
-        <v>119</v>
-      </c>
-      <c r="D7" t="b">
-        <v>1</v>
-      </c>
-      <c r="E7">
-        <v>5</v>
-      </c>
-      <c r="G7">
-        <v>0</v>
-      </c>
-      <c r="H7" t="b">
-        <v>0</v>
-      </c>
-      <c r="I7" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="8" spans="9:9">
-      <c r="I8" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="9" spans="2:8">
-      <c r="B9" t="s">
-        <v>87</v>
-      </c>
-      <c r="C9" t="s">
-        <v>122</v>
-      </c>
-      <c r="D9" t="b">
-        <v>1</v>
-      </c>
-      <c r="E9">
-        <v>0</v>
-      </c>
-      <c r="G9">
-        <v>0</v>
-      </c>
-      <c r="H9" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="2:8">
-      <c r="B10" t="s">
-        <v>92</v>
-      </c>
-      <c r="C10" t="s">
-        <v>117</v>
-      </c>
-      <c r="D10" t="b">
-        <v>1</v>
-      </c>
-      <c r="E10">
-        <v>5</v>
-      </c>
-      <c r="G10">
-        <v>0</v>
-      </c>
-      <c r="H10" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" spans="2:8">
-      <c r="B11" t="s">
-        <v>94</v>
-      </c>
-      <c r="C11" t="s">
-        <v>119</v>
-      </c>
-      <c r="D11" t="b">
-        <v>1</v>
-      </c>
-      <c r="E11">
-        <v>5</v>
-      </c>
-      <c r="G11">
-        <v>4</v>
-      </c>
-      <c r="H11" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="2:8">
-      <c r="B12" t="s">
-        <v>96</v>
-      </c>
-      <c r="C12" t="s">
-        <v>122</v>
-      </c>
-      <c r="D12" t="b">
-        <v>1</v>
-      </c>
-      <c r="E12">
-        <v>0</v>
-      </c>
-      <c r="F12" t="s">
-        <v>123</v>
-      </c>
-      <c r="G12">
-        <v>0</v>
-      </c>
-      <c r="H12" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="2:8">
-      <c r="B13" t="s">
-        <v>98</v>
-      </c>
-      <c r="C13" t="s">
-        <v>122</v>
-      </c>
-      <c r="D13" t="b">
-        <v>1</v>
-      </c>
-      <c r="E13">
-        <v>0</v>
-      </c>
-      <c r="F13" t="s">
-        <v>124</v>
-      </c>
-      <c r="G13">
-        <v>0</v>
-      </c>
-      <c r="H13" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="2:8">
-      <c r="B14" t="s">
-        <v>100</v>
-      </c>
-      <c r="C14" t="s">
-        <v>122</v>
-      </c>
-      <c r="D14" t="b">
-        <v>1</v>
-      </c>
-      <c r="E14">
-        <v>0</v>
-      </c>
-      <c r="F14" t="s">
-        <v>125</v>
-      </c>
-      <c r="G14">
-        <v>0</v>
-      </c>
-      <c r="H14" t="b">
+      <c r="H14" s="1" t="b">
         <v>0</v>
       </c>
     </row>

--- a/GourmetProject/GameConfig/Datas/reward.xlsx
+++ b/GourmetProject/GameConfig/Datas/reward.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="15340" activeTab="1"/>
+    <workbookView windowHeight="15280" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="reward_package" sheetId="1" r:id="rId1"/>
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="337" uniqueCount="129">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="337" uniqueCount="130">
   <si>
     <t>##var</t>
   </si>
@@ -222,16 +222,19 @@
     <t>pool_fragment</t>
   </si>
   <si>
+    <t>0,6</t>
+  </si>
+  <si>
+    <t>slot_specific_passive</t>
+  </si>
+  <si>
+    <t>PassiveItemChoice</t>
+  </si>
+  <si>
+    <t>pool_passive</t>
+  </si>
+  <si>
     <t>3,6</t>
-  </si>
-  <si>
-    <t>slot_specific_passive</t>
-  </si>
-  <si>
-    <t>PassiveItemChoice</t>
-  </si>
-  <si>
-    <t>pool_passive</t>
   </si>
   <si>
     <t>slot_specific_active_strengthen</t>
@@ -1010,7 +1013,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1022,12 +1025,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="49">
@@ -1959,7 +1956,7 @@
         <v>61</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="K7" s="3" t="s">
         <v>61</v>
@@ -1969,37 +1966,37 @@
       </c>
     </row>
     <row r="8" s="3" customFormat="1" ht="17" spans="2:15">
-      <c r="B8" s="6" t="s">
-        <v>72</v>
-      </c>
-      <c r="C8" s="6" t="s">
+      <c r="B8" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="C8" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="D8" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="E8" s="6">
+      <c r="D8" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="E8" s="3">
         <v>2</v>
       </c>
-      <c r="F8" s="6">
-        <v>1</v>
-      </c>
-      <c r="G8" s="6">
-        <v>1</v>
-      </c>
-      <c r="H8" s="6" t="s">
-        <v>74</v>
-      </c>
-      <c r="I8" s="6" t="s">
-        <v>61</v>
-      </c>
-      <c r="J8" s="6" t="s">
-        <v>61</v>
-      </c>
-      <c r="K8" s="6" t="s">
-        <v>61</v>
-      </c>
-      <c r="L8" s="6" t="s">
+      <c r="F8" s="3">
+        <v>1</v>
+      </c>
+      <c r="G8" s="3">
+        <v>1</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="I8" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="J8" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="K8" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="L8" s="3" t="s">
         <v>61</v>
       </c>
       <c r="O8" s="3" t="s">
@@ -2007,37 +2004,37 @@
       </c>
     </row>
     <row r="9" s="3" customFormat="1" spans="2:15">
-      <c r="B9" s="6" t="s">
-        <v>75</v>
-      </c>
-      <c r="C9" s="6" t="s">
+      <c r="B9" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="C9" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="D9" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="E9" s="6">
+      <c r="D9" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="E9" s="3">
         <v>2</v>
       </c>
-      <c r="F9" s="6">
-        <v>1</v>
-      </c>
-      <c r="G9" s="6">
-        <v>1</v>
-      </c>
-      <c r="H9" s="6" t="s">
-        <v>77</v>
-      </c>
-      <c r="I9" s="6" t="s">
-        <v>61</v>
-      </c>
-      <c r="J9" s="6" t="s">
-        <v>61</v>
-      </c>
-      <c r="K9" s="6" t="s">
-        <v>61</v>
-      </c>
-      <c r="L9" s="6" t="s">
+      <c r="F9" s="3">
+        <v>1</v>
+      </c>
+      <c r="G9" s="3">
+        <v>1</v>
+      </c>
+      <c r="H9" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="I9" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="J9" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="K9" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="L9" s="3" t="s">
         <v>61</v>
       </c>
       <c r="O9" s="3" t="s">
@@ -2046,7 +2043,7 @@
     </row>
     <row r="10" s="2" customFormat="1" spans="2:12">
       <c r="B10" s="2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>24</v>
@@ -2070,7 +2067,7 @@
         <v>61</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="K10" s="2" t="s">
         <v>61</v>
@@ -2082,13 +2079,13 @@
     <row r="11" s="4" customFormat="1" ht="17" spans="1:15">
       <c r="A11" s="2"/>
       <c r="B11" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>26</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E11" s="2">
         <v>4</v>
@@ -2100,7 +2097,7 @@
         <v>1</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="I11" s="2" t="s">
         <v>61</v>
@@ -2123,13 +2120,13 @@
     <row r="12" s="4" customFormat="1" spans="1:15">
       <c r="A12" s="2"/>
       <c r="B12" s="2" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>28</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E12" s="2">
         <v>4</v>
@@ -2141,7 +2138,7 @@
         <v>1</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="I12" s="2" t="s">
         <v>61</v>
@@ -2161,150 +2158,150 @@
         <v>19</v>
       </c>
     </row>
-    <row r="13" s="5" customFormat="1" spans="2:15">
-      <c r="B13" s="5" t="s">
-        <v>81</v>
-      </c>
-      <c r="C13" s="5" t="s">
+    <row r="13" s="3" customFormat="1" spans="2:15">
+      <c r="B13" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="D13" s="5" t="s">
+      <c r="C13" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="D13" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="E13" s="5">
+      <c r="E13" s="3">
         <v>3</v>
       </c>
-      <c r="F13" s="5">
-        <v>1</v>
-      </c>
-      <c r="G13" s="5">
-        <v>1</v>
-      </c>
-      <c r="H13" s="5" t="s">
+      <c r="F13" s="3">
+        <v>1</v>
+      </c>
+      <c r="G13" s="3">
+        <v>1</v>
+      </c>
+      <c r="H13" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="I13" s="5" t="s">
-        <v>83</v>
-      </c>
-      <c r="J13" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="K13" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="L13" s="5" t="s">
+      <c r="I13" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="J13" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="K13" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="L13" s="3" t="s">
         <v>61</v>
       </c>
       <c r="O13" s="1"/>
     </row>
-    <row r="14" s="5" customFormat="1" spans="2:12">
-      <c r="B14" s="5" t="s">
-        <v>84</v>
-      </c>
-      <c r="C14" s="5" t="s">
+    <row r="14" s="3" customFormat="1" spans="2:12">
+      <c r="B14" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="D14" s="5" t="s">
+      <c r="C14" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="D14" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="E14" s="5">
+      <c r="E14" s="3">
         <v>3</v>
       </c>
-      <c r="F14" s="5">
-        <v>1</v>
-      </c>
-      <c r="G14" s="5">
-        <v>1</v>
-      </c>
-      <c r="H14" s="5" t="s">
-        <v>86</v>
-      </c>
-      <c r="I14" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="J14" s="5" t="s">
+      <c r="F14" s="3">
+        <v>1</v>
+      </c>
+      <c r="G14" s="3">
+        <v>1</v>
+      </c>
+      <c r="H14" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="K14" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="L14" s="5" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="15" s="5" customFormat="1" spans="2:12">
-      <c r="B15" s="5" t="s">
+      <c r="I14" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="J14" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="C15" s="5" t="s">
+      <c r="K14" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="L14" s="3" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="15" s="3" customFormat="1" spans="2:12">
+      <c r="B15" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="D15" s="5" t="s">
+      <c r="C15" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="D15" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="E15" s="5">
+      <c r="E15" s="3">
         <v>3</v>
       </c>
-      <c r="F15" s="5">
-        <v>1</v>
-      </c>
-      <c r="G15" s="5">
-        <v>1</v>
-      </c>
-      <c r="H15" s="5" t="s">
+      <c r="F15" s="3">
+        <v>1</v>
+      </c>
+      <c r="G15" s="3">
+        <v>1</v>
+      </c>
+      <c r="H15" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="I15" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="J15" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="K15" s="5" t="s">
-        <v>87</v>
-      </c>
-      <c r="L15" s="5" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="16" s="5" customFormat="1" spans="2:12">
-      <c r="B16" s="5" t="s">
-        <v>90</v>
-      </c>
-      <c r="C16" s="5" t="s">
+      <c r="I15" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="J15" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="K15" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="L15" s="3" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="16" s="3" customFormat="1" spans="2:12">
+      <c r="B16" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="D16" s="5" t="s">
+      <c r="C16" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="D16" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="E16" s="5">
-        <v>1</v>
-      </c>
-      <c r="F16" s="5">
-        <v>1</v>
-      </c>
-      <c r="G16" s="5">
-        <v>1</v>
-      </c>
-      <c r="I16" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="J16" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="K16" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="L16" s="5" t="s">
-        <v>92</v>
+      <c r="E16" s="3">
+        <v>1</v>
+      </c>
+      <c r="F16" s="3">
+        <v>1</v>
+      </c>
+      <c r="G16" s="3">
+        <v>1</v>
+      </c>
+      <c r="I16" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="J16" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="K16" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="L16" s="3" t="s">
+        <v>93</v>
       </c>
     </row>
     <row r="17" spans="2:12">
       <c r="B17" s="1" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D17" s="1" t="s">
         <v>58</v>
@@ -2336,10 +2333,10 @@
     </row>
     <row r="18" spans="2:12">
       <c r="B18" s="1" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D18" s="1" t="s">
         <v>58</v>
@@ -2371,10 +2368,10 @@
     </row>
     <row r="19" spans="2:12">
       <c r="B19" s="1" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D19" s="1" t="s">
         <v>70</v>
@@ -2406,10 +2403,10 @@
     </row>
     <row r="20" spans="2:12">
       <c r="B20" s="1" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D20" s="1" t="s">
         <v>70</v>
@@ -2441,10 +2438,10 @@
     </row>
     <row r="21" spans="2:12">
       <c r="B21" s="1" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D21" s="1" t="s">
         <v>70</v>
@@ -2476,13 +2473,13 @@
     </row>
     <row r="22" spans="2:12">
       <c r="B22" s="1" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E22" s="1">
         <v>1</v>
@@ -2494,7 +2491,7 @@
         <v>1</v>
       </c>
       <c r="H22" s="1" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="I22" s="1" t="s">
         <v>61</v>
@@ -2511,13 +2508,13 @@
     </row>
     <row r="23" spans="2:12">
       <c r="B23" s="1" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E23" s="1">
         <v>2</v>
@@ -2529,7 +2526,7 @@
         <v>1</v>
       </c>
       <c r="H23" s="1" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="I23" s="1" t="s">
         <v>61</v>
@@ -2546,13 +2543,13 @@
     </row>
     <row r="24" spans="2:12">
       <c r="B24" s="1" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E24" s="1">
         <v>3</v>
@@ -2564,7 +2561,7 @@
         <v>1</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="I24" s="1" t="s">
         <v>61</v>
@@ -2581,10 +2578,10 @@
     </row>
     <row r="25" spans="2:12">
       <c r="B25" s="1" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D25" s="1" t="s">
         <v>66</v>
@@ -2616,10 +2613,10 @@
     </row>
     <row r="26" spans="2:12">
       <c r="B26" s="1" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D26" s="1" t="s">
         <v>58</v>
@@ -2634,7 +2631,7 @@
         <v>1</v>
       </c>
       <c r="H26" s="1" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="I26" s="1" t="s">
         <v>61</v>
@@ -2651,10 +2648,10 @@
     </row>
     <row r="27" spans="2:12">
       <c r="B27" s="1" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D27" s="1" t="s">
         <v>70</v>
@@ -2669,7 +2666,7 @@
         <v>1</v>
       </c>
       <c r="H27" s="1" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="I27" s="1" t="s">
         <v>61</v>
@@ -2686,13 +2683,13 @@
     </row>
     <row r="28" spans="2:12">
       <c r="B28" s="1" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E28" s="1">
         <v>1</v>
@@ -2704,7 +2701,7 @@
         <v>1</v>
       </c>
       <c r="H28" s="1" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="I28" s="1" t="s">
         <v>61</v>
@@ -2721,13 +2718,13 @@
     </row>
     <row r="29" spans="2:12">
       <c r="B29" s="1" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E29" s="1">
         <v>1</v>
@@ -2739,7 +2736,7 @@
         <v>1</v>
       </c>
       <c r="H29" s="1" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="I29" s="1" t="s">
         <v>61</v>
@@ -2756,13 +2753,13 @@
     </row>
     <row r="30" spans="2:12">
       <c r="B30" s="1" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E30" s="1">
         <v>1</v>
@@ -2774,7 +2771,7 @@
         <v>1</v>
       </c>
       <c r="H30" s="1" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="I30" s="1" t="s">
         <v>61</v>
@@ -2824,10 +2821,10 @@
         <v>33</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -2835,16 +2832,16 @@
         <v>4</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -2855,13 +2852,13 @@
         <v>9</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="4" spans="2:4">
@@ -2869,7 +2866,7 @@
         <v>59</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="D4" s="1" t="b">
         <v>1</v>
@@ -2880,7 +2877,7 @@
         <v>67</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="D5" s="1" t="b">
         <v>1</v>
@@ -2891,7 +2888,7 @@
         <v>71</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="D6" s="1" t="b">
         <v>1</v>
@@ -2899,38 +2896,38 @@
     </row>
     <row r="7" spans="2:5">
       <c r="B7" s="1" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="D7" s="1" t="b">
         <v>1</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
     </row>
     <row r="8" ht="17" spans="2:5">
       <c r="B8" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="C8" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="C8" s="2" t="s">
-        <v>73</v>
-      </c>
       <c r="D8" s="1" t="b">
         <v>1</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="9" spans="2:4">
       <c r="B9" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="C9" s="2" t="s">
         <v>77</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>76</v>
       </c>
       <c r="D9" s="1" t="b">
         <v>1</v>
@@ -2938,10 +2935,10 @@
     </row>
     <row r="10" spans="2:4">
       <c r="B10" s="1" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="D10" s="1" t="b">
         <v>1</v>
@@ -2949,10 +2946,10 @@
     </row>
     <row r="11" spans="2:4">
       <c r="B11" s="1" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="D11" s="1" t="b">
         <v>1</v>
@@ -2960,10 +2957,10 @@
     </row>
     <row r="12" spans="2:4">
       <c r="B12" s="1" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="D12" s="1" t="b">
         <v>1</v>
@@ -2971,10 +2968,10 @@
     </row>
     <row r="13" spans="2:4">
       <c r="B13" s="1" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="D13" s="1" t="b">
         <v>1</v>
@@ -2982,10 +2979,10 @@
     </row>
     <row r="14" spans="2:4">
       <c r="B14" s="1" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="D14" s="1" t="b">
         <v>1</v>

--- a/GourmetProject/GameConfig/Datas/reward.xlsx
+++ b/GourmetProject/GameConfig/Datas/reward.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="reward_package" sheetId="1" r:id="R228534bdab874d5a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="reward_slot" sheetId="2" r:id="R6c799ef32e764c49"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="reward_pool" sheetId="3" r:id="R7c79b8ad6ec74a81"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="reward_package" sheetId="1" r:id="R9ffbb541a73342da"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="reward_slot" sheetId="2" r:id="R50bbe82e48d24f14"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="reward_pool" sheetId="3" r:id="Rabbe8cbeec2a41ef"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -3298,6 +3298,9 @@
       <x:c r="D12" s="1" t="b">
         <x:v>1</x:v>
       </x:c>
+      <x:c r="E12" t="str">
+        <x:v>LayWood</x:v>
+      </x:c>
     </x:row>
     <x:row r="13">
       <x:c r="B13" s="1" t="s">
@@ -3309,6 +3312,9 @@
       <x:c r="D13" s="1" t="b">
         <x:v>1</x:v>
       </x:c>
+      <x:c r="E13" t="str">
+        <x:v>LayStone</x:v>
+      </x:c>
     </x:row>
     <x:row r="14">
       <x:c r="B14" s="1" t="s">
@@ -3319,6 +3325,9 @@
       </x:c>
       <x:c r="D14" s="1" t="b">
         <x:v>1</x:v>
+      </x:c>
+      <x:c r="E14" t="str">
+        <x:v>LayMetal</x:v>
       </x:c>
     </x:row>
     <x:row r="15">

--- a/GourmetProject/GameConfig/Datas/reward.xlsx
+++ b/GourmetProject/GameConfig/Datas/reward.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="reward_package" sheetId="1" r:id="R9ffbb541a73342da"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="reward_slot" sheetId="2" r:id="R50bbe82e48d24f14"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="reward_pool" sheetId="3" r:id="Rabbe8cbeec2a41ef"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="reward_package" sheetId="1" r:id="R887d51f2c4884f8f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="reward_slot" sheetId="2" r:id="R7cb21451f40a4dbf"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="reward_pool" sheetId="3" r:id="R9107a5e099134f7e"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -30,9 +30,6 @@
     <x:t xml:space="preserve">奖励包 id</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">基础菜品奖励槽组 id。</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">行动预览对应的特定奖励槽组 id。</x:t>
   </x:si>
   <x:si>
@@ -138,6 +135,12 @@
     <x:t xml:space="preserve">goldHiddenOffset</x:t>
   </x:si>
   <x:si>
+    <x:t xml:space="preserve">name</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">ruleTemplate</x:t>
+  </x:si>
+  <x:si>
     <x:t xml:space="preserve">奖励槽ID</x:t>
   </x:si>
   <x:si>
@@ -159,18 +162,15 @@
     <x:t xml:space="preserve">使用的奖励池ID</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">菜品奖励隐藏分修正</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">被动道具奖励隐藏分修正</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">胃部碎片奖励隐藏分修正</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">金币奖励隐藏分修正；index0=Normal，index1=Super。</x:t>
   </x:si>
   <x:si>
+    <x:t xml:space="preserve">奖励组显示名称</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">规则文案模板；仅支持 {choiceCount} 与 {requiredPickCount}。</x:t>
+  </x:si>
+  <x:si>
     <x:t xml:space="preserve">RewardKind</x:t>
   </x:si>
   <x:si>
@@ -198,6 +198,13 @@
     <x:t xml:space="preserve">0,0</x:t>
   </x:si>
   <x:si>
+    <x:t xml:space="preserve">食物</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">从 {choiceCount} 个食物中
+选择 {requiredPickCount} 个加入食谱</x:t>
+  </x:si>
+  <x:si>
     <x:t xml:space="preserve">slot_specific_gold</x:t>
   </x:si>
   <x:si>
@@ -207,6 +214,12 @@
     <x:t xml:space="preserve">10,30</x:t>
   </x:si>
   <x:si>
+    <x:t xml:space="preserve">金币</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">金币+ {requiredPickCount}</x:t>
+  </x:si>
+  <x:si>
     <x:t xml:space="preserve">slot_specific_fragment</x:t>
   </x:si>
   <x:si>
@@ -219,6 +232,13 @@
     <x:t xml:space="preserve">0,6</x:t>
   </x:si>
   <x:si>
+    <x:t xml:space="preserve">餐桌格</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">从 {choiceCount} 个餐桌格中
+选择 {requiredPickCount} 个拼入餐桌</x:t>
+  </x:si>
+  <x:si>
     <x:t xml:space="preserve">slot_specific_passive</x:t>
   </x:si>
   <x:si>
@@ -231,7 +251,264 @@
     <x:t xml:space="preserve">3,6</x:t>
   </x:si>
   <x:si>
+    <x:t xml:space="preserve">装饰品</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">从 {choiceCount} 个装饰品中
+选择 {requiredPickCount} 个</x:t>
+  </x:si>
+  <x:si>
     <x:t xml:space="preserve">slot_specific_active_strengthen</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">ActiveItemStrengthen</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">pool_active_strengthen</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">强化箱</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">从 {choiceCount} 个强化箱中
+选择 {requiredPickCount} 个</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">slot_specific_active_adjust</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">ActiveItemAdjust</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">pool_active_adjust</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">调整单</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">从 {choiceCount} 个调整单中
+选择 {requiredPickCount} 个</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">slot_specific_hard_passive</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">slot_specific_hard_active_strengthen</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">slot_specific_hard_active_adjust</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">slot_boss_dish</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">boss_dish</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">10,0</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">slot_boss_passive</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">boss_passive</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">pool_passive_boss</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">7,0</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">slot_boss_fragment</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">boss_fragment</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">slot_boss_gold</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">boss_gold</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">50,0</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">dish_choice_3</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">dish_grant_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">随机获得 {requiredPickCount} 个食物</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">passive_choice_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">随机获得 {requiredPickCount} 个装饰品</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">passive_choice_3</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">passive_grant_2</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">获得全部 {choiceCount} 个装饰品</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">active_grant_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">ActiveItemGrant</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">pool_active</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">消耗品</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">随机获得 {requiredPickCount} 个消耗品</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">active_grant_2</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">获得全部 {choiceCount} 个消耗品</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">active_choice_3</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">消耗品选择</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">从 {choiceCount} 个消耗品中
+选择 {requiredPickCount} 个</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">fragment_choice_3</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">从 {choiceCount} 个餐桌格中
+选择 {requiredPickCount} 个</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">flavored_dish_3</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">pool_flavored_dish</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">风味食物</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">获得全部 {choiceCount} 个风味食物</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">legendary_choice_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">pool_legendary</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">传说装饰品</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">随机获得 {requiredPickCount} 个传说装饰品</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">lay_wood</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">pool_lay_wood</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">木质强化箱</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">随机获得 {requiredPickCount} 个木质强化箱</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">lay_stone</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">pool_lay_stone</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">石质强化箱</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">随机获得 {requiredPickCount} 个石质强化箱</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">lay_metal</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">pool_lay_metal</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">金属强化箱</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">随机获得 {requiredPickCount} 个金属强化箱</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">slot_machine_gold</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">slot_machine_basic</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">slot_machine_fragment</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">slot_machine_active</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">slot_machine_passive</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">allowFallback</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">*specialTags</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">奖励池ID</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">奖励池类型</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">是否允许兜底</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">奖励池特殊标签筛选</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">RewardPoolKind</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">bool</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">list,RewardPoolSpecialTag</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Dish</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Fragment</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">PassiveItem</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">BossReward</x:t>
   </x:si>
   <x:si>
     <x:r>
@@ -245,169 +522,19 @@
     </x:r>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">pool_active_strengthen</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">slot_specific_active_adjust</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">ActiveItemAdjust</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">pool_active_adjust</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">slot_specific_hard_passive</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">slot_specific_hard_active_strengthen</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">slot_specific_hard_active_adjust</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">slot_boss_dish</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">boss_dish</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">10,0</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">slot_boss_passive</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">boss_passive</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">pool_passive_boss</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">7,0</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">slot_boss_fragment</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">boss_fragment</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">slot_boss_gold</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">boss_gold</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">50,0</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">dish_choice_3</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">dish_grant_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">passive_choice_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">passive_choice_3</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">passive_grant_2</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">active_grant_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">ActiveItemGrant</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">pool_active</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">active_grant_2</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">active_choice_3</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">fragment_choice_3</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">flavored_dish_3</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">pool_flavored_dish</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">legendary_choice_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">pool_legendary</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">lay_wood</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">pool_lay_wood</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">lay_stone</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">pool_lay_stone</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">lay_metal</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">pool_lay_metal</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">allowFallback</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">*specialTags</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">奖励池ID</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">奖励池类型</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">是否允许兜底</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">奖励池特殊标签筛选</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">RewardPoolKind</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">bool</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">list,RewardPoolSpecialTag</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Dish</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Fragment</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">PassiveItem</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">BossReward</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">ScoreBuild</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">ActiveItem</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">LayWood</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">LayStone</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">LayMetal</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -526,7 +653,7 @@
       <x:name val="宋体"/>
     </x:font>
     <x:font>
-      <x:sz val="11"/>
+      <x:sz val="1100"/>
       <x:color theme="1"/>
       <x:name val="Calibri"/>
     </x:font>
@@ -928,7 +1055,7 @@
       <x:alignment vertical="center"/>
     </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="10">
+  <x:cellXfs count="5">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <x:alignment horizontal="center" vertical="center"/>
@@ -939,23 +1066,8 @@
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="center"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment wrapText="1"/>
-    </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="center" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
-      <x:extLst>
-        <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
-          <xfpb:xfComplement xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" i="0"/>
-        </x:ext>
-      </x:extLst>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="49">
@@ -1192,23 +1304,6 @@
 </x:styleSheet>
 </file>
 
-<file path=xl/featurePropertyBag/featurePropertyBag.xml><?xml version="1.0" encoding="utf-8"?>
-<xfpb:FeaturePropertyBags xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag">
-  <xfpb:bag type="Checkbox"/>
-  <xfpb:bag type="XFControls">
-    <xfpb:bagId k="CellControl">0</xfpb:bagId>
-  </xfpb:bag>
-  <xfpb:bag type="XFComplement">
-    <xfpb:bagId k="XFControls">1</xfpb:bagId>
-  </xfpb:bag>
-  <xfpb:bag type="XFComplements" extRef="XFComplementsMapperExtRef">
-    <xfpb:a k="MappedFeaturePropertyBags">
-      <xfpb:bagId>2</xfpb:bagId>
-    </xfpb:a>
-  </xfpb:bag>
-</xfpb:FeaturePropertyBags>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -1453,143 +1548,143 @@
       <x:c r="B2" s="1" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="C2" s="1" t="s">
+      <x:c r="C2" s="1" t="str">
+        <x:v>基础食物奖励槽组 id。</x:v>
+      </x:c>
+      <x:c r="D2" s="1" t="s">
         <x:v>6</x:v>
-      </x:c>
-      <x:c r="D2" s="1" t="s">
-        <x:v>7</x:v>
       </x:c>
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="1" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="B3" s="1" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="B3" s="1" t="s">
+      <x:c r="C3" s="1" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="C3" s="1" t="s">
-        <x:v>10</x:v>
-      </x:c>
       <x:c r="D3" s="1" t="s">
-        <x:v>9</x:v>
+        <x:v>8</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
       <x:c r="B4" s="1" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="C4" s="1" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="C4" s="1" t="s">
+      <x:c r="D4" s="1" t="s">
         <x:v>12</x:v>
-      </x:c>
-      <x:c r="D4" s="1" t="s">
-        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
       <x:c r="B5" s="1" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C5" s="1" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="D5" s="1" t="s">
         <x:v>14</x:v>
-      </x:c>
-      <x:c r="C5" s="1" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="D5" s="1" t="s">
-        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
       <x:c r="B6" s="1" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C6" s="1" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="D6" s="1" t="s">
         <x:v>16</x:v>
-      </x:c>
-      <x:c r="C6" s="1" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="D6" s="1" t="s">
-        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
       <x:c r="B7" s="1" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="C7" s="1" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="D7" s="1" t="s">
         <x:v>18</x:v>
-      </x:c>
-      <x:c r="C7" s="1" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="D7" s="1" t="s">
-        <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
       <x:c r="B8" s="1" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="C8" s="1" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="D8" s="1" t="s">
         <x:v>20</x:v>
-      </x:c>
-      <x:c r="C8" s="1" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="D8" s="1" t="s">
-        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
       <x:c r="B9" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C9" s="1" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="D9" s="1" t="s">
         <x:v>12</x:v>
-      </x:c>
-      <x:c r="D9" s="1" t="s">
-        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="10">
       <x:c r="B10" s="1" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="C10" s="1" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="D10" s="2" t="s">
         <x:v>23</x:v>
-      </x:c>
-      <x:c r="C10" s="1" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="D10" s="2" t="s">
-        <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="11">
       <x:c r="B11" s="1" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="C11" s="1" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="D11" s="2" t="s">
         <x:v>25</x:v>
-      </x:c>
-      <x:c r="C11" s="1" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="D11" s="2" t="s">
-        <x:v>26</x:v>
       </x:c>
     </x:row>
     <x:row r="12">
       <x:c r="B12" s="1" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="C12" s="1" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="D12" s="2" t="s">
         <x:v>27</x:v>
-      </x:c>
-      <x:c r="C12" s="1" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="D12" s="2" t="s">
-        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="13">
       <x:c r="B13" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C13" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="D13" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="14">
       <x:c r="B14" s="1" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="C14" s="1" t="s">
         <x:v>30</x:v>
-      </x:c>
-      <x:c r="C14" s="1" t="s">
-        <x:v>31</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -1613,13 +1708,13 @@
     <x:col min="10" max="10" width="27.30769157409668" style="1" customWidth="1"/>
     <x:col min="11" max="11" width="31.076923370361328" style="1" customWidth="1"/>
     <x:col min="12" max="12" width="59.38461685180664" style="1" customWidth="1"/>
-    <x:col min="13" max="16384" width="9" style="1" customWidth="1"/>
-    <x:col min="13" max="13" width="24" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="46" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="54" hidden="0" customWidth="1"/>
+    <x:col min="13" max="13" width="24" style="1" customWidth="1"/>
+    <x:col min="14" max="14" width="46" style="1" customWidth="1"/>
+    <x:col min="15" max="15" width="54" style="1" customWidth="1"/>
+    <x:col min="16" max="16384" width="9" style="1" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1">
+    <x:row r="1" ht="17">
       <x:c r="A1" s="1" t="s">
         <x:v>0</x:v>
       </x:c>
@@ -1627,101 +1722,97 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="C1" s="1" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="D1" s="1" t="s">
         <x:v>32</x:v>
       </x:c>
-      <x:c r="D1" s="1" t="s">
+      <x:c r="E1" s="1" t="s">
         <x:v>33</x:v>
       </x:c>
-      <x:c r="E1" s="1" t="s">
+      <x:c r="F1" s="1" t="s">
         <x:v>34</x:v>
       </x:c>
-      <x:c r="F1" s="1" t="s">
+      <x:c r="G1" s="1" t="s">
         <x:v>35</x:v>
       </x:c>
-      <x:c r="G1" s="1" t="s">
+      <x:c r="H1" s="1" t="s">
         <x:v>36</x:v>
       </x:c>
-      <x:c r="H1" s="1" t="s">
+      <x:c r="I1" s="1" t="s">
         <x:v>37</x:v>
       </x:c>
-      <x:c r="I1" s="1" t="s">
+      <x:c r="J1" s="1" t="s">
         <x:v>38</x:v>
       </x:c>
-      <x:c r="J1" s="1" t="s">
+      <x:c r="K1" s="1" t="s">
         <x:v>39</x:v>
       </x:c>
-      <x:c r="K1" s="1" t="s">
+      <x:c r="L1" s="1" t="s">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="L1" s="1" t="s">
+      <x:c r="M1" s="4" t="s">
         <x:v>41</x:v>
       </x:c>
-      <x:c r="M1" s="6" t="str">
-        <x:v>name</x:v>
-      </x:c>
-      <x:c r="N1" s="6" t="str">
-        <x:v>desc</x:v>
-      </x:c>
-      <x:c r="O1" s="6" t="str">
-        <x:v>ruleTemplate</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="2">
+      <x:c r="N1" s="4" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="O1"/>
+    </x:row>
+    <x:row r="2" ht="34">
       <x:c r="A2" s="1" t="s">
         <x:v>4</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="C2" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="D2" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="E2" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="F2" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="G2" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="H2" s="1" t="s">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="I2" s="1" t="s">
         <x:v>49</x:v>
       </x:c>
-      <x:c r="J2" s="1" t="s">
+      <x:c r="I2" s="1" t="str">
+        <x:v>食物奖励隐藏分修正</x:v>
+      </x:c>
+      <x:c r="J2" s="1" t="str">
+        <x:v>装饰品奖励隐藏分修正</x:v>
+      </x:c>
+      <x:c r="K2" s="1" t="str">
+        <x:v>餐桌格奖励隐藏分修正</x:v>
+      </x:c>
+      <x:c r="L2" s="1" t="s">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="K2" s="1" t="s">
+      <x:c r="M2" s="4" t="s">
         <x:v>51</x:v>
       </x:c>
-      <x:c r="L2" s="1" t="s">
+      <x:c r="N2" s="4" t="s">
         <x:v>52</x:v>
       </x:c>
-      <x:c r="M2" s="6" t="str">
-        <x:v>奖励组显示名称</x:v>
-      </x:c>
-      <x:c r="N2" s="6" t="str">
-        <x:v>奖励组用途描述</x:v>
-      </x:c>
-      <x:c r="O2" s="6" t="str">
-        <x:v>规则文案模板；仅支持 {choiceCount} 与 {requiredPickCount}。</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="3">
+      <x:c r="O2"/>
+    </x:row>
+    <x:row r="3" ht="17">
       <x:c r="A3" s="1" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="B3" s="1" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="B3" s="1" t="s">
-        <x:v>9</x:v>
-      </x:c>
       <x:c r="C3" s="1" t="s">
-        <x:v>9</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="D3" s="1" t="s">
         <x:v>53</x:v>
@@ -1736,7 +1827,7 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="H3" s="1" t="s">
-        <x:v>9</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="I3" s="1" t="s">
         <x:v>56</x:v>
@@ -1750,22 +1841,20 @@
       <x:c r="L3" s="1" t="s">
         <x:v>56</x:v>
       </x:c>
-      <x:c r="M3" s="6" t="str">
-        <x:v>string</x:v>
-      </x:c>
-      <x:c r="N3" s="6" t="str">
-        <x:v>string</x:v>
-      </x:c>
-      <x:c r="O3" s="6" t="str">
-        <x:v>string</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="4">
+      <x:c r="M3" s="4" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="N3" s="4" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="O3"/>
+    </x:row>
+    <x:row r="4" ht="34">
       <x:c r="B4" s="1" t="s">
         <x:v>57</x:v>
       </x:c>
       <x:c r="C4" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="D4" s="1" t="s">
         <x:v>58</x:v>
@@ -1794,25 +1883,23 @@
       <x:c r="L4" s="1" t="s">
         <x:v>61</x:v>
       </x:c>
-      <x:c r="M4" s="6" t="str">
-        <x:v>基础菜品选择</x:v>
-      </x:c>
-      <x:c r="N4" s="6" t="str">
-        <x:v>从菜品池中挑选一个基础菜品加入菜谱池。</x:v>
-      </x:c>
-      <x:c r="O4" s="6" t="str">
-        <x:v>从 {choiceCount} 个菜品中选择 {requiredPickCount} 个。</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="5">
+      <x:c r="M4" s="4" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="N4" s="4" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="O4"/>
+    </x:row>
+    <x:row r="5" ht="17">
       <x:c r="B5" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="C5" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="D5" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="E5" s="1">
         <x:v>1</x:v>
@@ -1833,27 +1920,25 @@
         <x:v>61</x:v>
       </x:c>
       <x:c r="L5" s="1" t="s">
-        <x:v>64</x:v>
-      </x:c>
-      <x:c r="M5" s="6" t="str">
-        <x:v>额外金币</x:v>
-      </x:c>
-      <x:c r="N5" s="6" t="str">
-        <x:v>领取一笔由当前美食结算生成的额外金币。</x:v>
-      </x:c>
-      <x:c r="O5" s="6" t="str">
-        <x:v>获得 {requiredPickCount} 份金币奖励。</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="6">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="M5" s="4" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="N5" s="4" t="s">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="O5"/>
+    </x:row>
+    <x:row r="6" ht="34">
       <x:c r="B6" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="C6" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="D6" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="E6" s="1">
         <x:v>3</x:v>
@@ -1865,7 +1950,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="H6" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="I6" s="1" t="s">
         <x:v>61</x:v>
@@ -1874,30 +1959,28 @@
         <x:v>61</x:v>
       </x:c>
       <x:c r="K6" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="L6" s="1" t="s">
         <x:v>61</x:v>
       </x:c>
-      <x:c r="M6" s="6" t="str">
-        <x:v>餐桌碎片选择</x:v>
-      </x:c>
-      <x:c r="N6" s="6" t="str">
-        <x:v>从餐桌碎片池中挑选一块碎片并进入餐桌编辑。</x:v>
-      </x:c>
-      <x:c r="O6" s="6" t="str">
-        <x:v>从 {choiceCount} 个餐桌碎片中选择 {requiredPickCount} 个。</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="7" s="3" customFormat="1">
+      <x:c r="M6" s="4" t="s">
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="N6" s="4" t="s">
+        <x:v>74</x:v>
+      </x:c>
+      <x:c r="O6"/>
+    </x:row>
+    <x:row r="7" s="3" customFormat="1" ht="34">
       <x:c r="B7" s="3" t="s">
-        <x:v>69</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="C7" s="3" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="D7" s="3" t="s">
-        <x:v>70</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="E7" s="3">
         <x:v>2</x:v>
@@ -1909,13 +1992,13 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="H7" s="3" t="s">
-        <x:v>71</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="I7" s="3" t="s">
         <x:v>61</x:v>
       </x:c>
       <x:c r="J7" s="3" t="s">
-        <x:v>72</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="K7" s="3" t="s">
         <x:v>61</x:v>
@@ -1923,37 +2006,35 @@
       <x:c r="L7" s="3" t="s">
         <x:v>61</x:v>
       </x:c>
-      <x:c r="M7" s="6" t="str">
-        <x:v>被动道具选择</x:v>
-      </x:c>
-      <x:c r="N7" s="6" t="str">
-        <x:v>从可用被动道具中挑选一个，获得后持续生效。</x:v>
-      </x:c>
-      <x:c r="O7" s="6" t="str">
-        <x:v>从 {choiceCount} 个被动道具中选择 {requiredPickCount} 个。</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="8" s="3" customFormat="1" ht="17">
+      <x:c r="M7" s="4" t="s">
+        <x:v>79</x:v>
+      </x:c>
+      <x:c r="N7" s="4" t="s">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="O7"/>
+    </x:row>
+    <x:row r="8" s="3" customFormat="1" ht="34">
       <x:c r="B8" s="3" t="s">
-        <x:v>73</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="C8" s="3" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="D8" s="5" t="s">
-        <x:v>74</x:v>
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="D8" s="1" t="s">
+        <x:v>82</x:v>
       </x:c>
       <x:c r="E8" s="3">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="F8" s="3">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="F8" s="3">
-        <x:v>1</x:v>
-      </x:c>
       <x:c r="G8" s="3">
         <x:v>1</x:v>
       </x:c>
       <x:c r="H8" s="3" t="s">
-        <x:v>75</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="I8" s="3" t="s">
         <x:v>61</x:v>
@@ -1967,200 +2048,188 @@
       <x:c r="L8" s="3" t="s">
         <x:v>61</x:v>
       </x:c>
-      <x:c r="M8" s="6" t="str">
-        <x:v>主动道具强化选择</x:v>
-      </x:c>
-      <x:c r="N8" s="6" t="str">
-        <x:v>从强化类主动道具中挑选一个。</x:v>
-      </x:c>
-      <x:c r="O8" s="7" t="str">
-        <x:v>从 {choiceCount} 个主动道具强化中选择 {requiredPickCount} 个。</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" s="3" customFormat="1">
+      <x:c r="M8" s="4" t="s">
+        <x:v>84</x:v>
+      </x:c>
+      <x:c r="N8" s="4" t="s">
+        <x:v>85</x:v>
+      </x:c>
+      <x:c r="O8"/>
+    </x:row>
+    <x:row r="9" s="3" customFormat="1" ht="34">
       <x:c r="B9" s="3" t="s">
+        <x:v>86</x:v>
+      </x:c>
+      <x:c r="C9" s="3" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="D9" s="3" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="E9" s="3">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="F9" s="3">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="G9" s="3">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H9" s="3" t="s">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="I9" s="3" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="J9" s="3" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="K9" s="3" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="L9" s="3" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="M9" s="4" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="N9" s="4" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="O9"/>
+    </x:row>
+    <x:row r="10" s="3" customFormat="1" ht="34">
+      <x:c r="B10" s="3" t="s">
+        <x:v>91</x:v>
+      </x:c>
+      <x:c r="C10" s="3" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="D10" s="3" t="s">
         <x:v>76</x:v>
       </x:c>
-      <x:c r="C9" s="3" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="D9" s="3" t="s">
+      <x:c r="E10" s="3">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="F10" s="3">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G10" s="3">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H10" s="3" t="s">
         <x:v>77</x:v>
       </x:c>
-      <x:c r="E9" s="3">
+      <x:c r="I10" s="3" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="J10" s="3" t="s">
+        <x:v>78</x:v>
+      </x:c>
+      <x:c r="K10" s="3" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="L10" s="3" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="M10" s="4" t="s">
+        <x:v>79</x:v>
+      </x:c>
+      <x:c r="N10" s="4" t="s">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="O10"/>
+    </x:row>
+    <x:row r="11" s="3" customFormat="1" ht="34">
+      <x:c r="B11" s="3" t="s">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="C11" s="3" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="D11" s="3" t="s">
+        <x:v>82</x:v>
+      </x:c>
+      <x:c r="E11" s="3">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="F11" s="3">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="F9" s="3">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="G9" s="3">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H9" s="3" t="s">
-        <x:v>78</x:v>
-      </x:c>
-      <x:c r="I9" s="3" t="s">
-        <x:v>61</x:v>
-      </x:c>
-      <x:c r="J9" s="3" t="s">
-        <x:v>61</x:v>
-      </x:c>
-      <x:c r="K9" s="3" t="s">
-        <x:v>61</x:v>
-      </x:c>
-      <x:c r="L9" s="3" t="s">
-        <x:v>61</x:v>
-      </x:c>
-      <x:c r="M9" s="6" t="str">
-        <x:v>主动道具调整选择</x:v>
-      </x:c>
-      <x:c r="N9" s="6" t="str">
-        <x:v>从调整类主动道具中挑选一个。</x:v>
-      </x:c>
-      <x:c r="O9" s="7" t="str">
-        <x:v>从 {choiceCount} 个主动道具调整中选择 {requiredPickCount} 个。</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" s="2" customFormat="1">
-      <x:c r="B10" s="2" t="s">
-        <x:v>79</x:v>
-      </x:c>
-      <x:c r="C10" s="2" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="D10" s="2" t="s">
-        <x:v>70</x:v>
-      </x:c>
-      <x:c r="E10" s="2">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="F10" s="2">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="G10" s="2">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H10" s="2" t="s">
-        <x:v>71</x:v>
-      </x:c>
-      <x:c r="I10" s="2" t="s">
-        <x:v>61</x:v>
-      </x:c>
-      <x:c r="J10" s="2" t="s">
-        <x:v>72</x:v>
-      </x:c>
-      <x:c r="K10" s="2" t="s">
-        <x:v>61</x:v>
-      </x:c>
-      <x:c r="L10" s="2" t="s">
-        <x:v>61</x:v>
-      </x:c>
-      <x:c r="M10" s="6" t="str">
-        <x:v>困难被动道具选择</x:v>
-      </x:c>
-      <x:c r="N10" s="6" t="str">
-        <x:v>从更高阶的被动道具中挑选一个，获得后持续生效。</x:v>
-      </x:c>
-      <x:c r="O10" s="6" t="str">
-        <x:v>从 {choiceCount} 个困难被动道具中选择 {requiredPickCount} 个。</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" s="4" customFormat="1" ht="17">
-      <x:c r="A11" s="2"/>
-      <x:c r="B11" s="2" t="s">
-        <x:v>80</x:v>
-      </x:c>
-      <x:c r="C11" s="2" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="D11" s="4" t="s">
-        <x:v>74</x:v>
-      </x:c>
-      <x:c r="E11" s="2">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="F11" s="2">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="G11" s="2">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H11" s="2" t="s">
-        <x:v>75</x:v>
-      </x:c>
-      <x:c r="I11" s="2" t="s">
-        <x:v>61</x:v>
-      </x:c>
-      <x:c r="J11" s="2" t="s">
-        <x:v>61</x:v>
-      </x:c>
-      <x:c r="K11" s="2" t="s">
-        <x:v>61</x:v>
-      </x:c>
-      <x:c r="L11" s="2" t="s">
-        <x:v>61</x:v>
-      </x:c>
-      <x:c r="M11" s="8" t="str">
-        <x:v>困难主动道具强化选择</x:v>
-      </x:c>
-      <x:c r="N11" s="8" t="str">
-        <x:v>从更高阶的强化类主动道具中挑选一个。</x:v>
-      </x:c>
-      <x:c r="O11" s="8" t="str">
-        <x:v>从 {choiceCount} 个困难主动道具强化中选择 {requiredPickCount} 个。</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12" s="4" customFormat="1">
-      <x:c r="A12" s="2"/>
-      <x:c r="B12" s="2" t="s">
-        <x:v>81</x:v>
-      </x:c>
-      <x:c r="C12" s="2" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="D12" s="2" t="s">
-        <x:v>77</x:v>
-      </x:c>
-      <x:c r="E12" s="2">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="F12" s="2">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="G12" s="2">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H12" s="2" t="s">
-        <x:v>78</x:v>
-      </x:c>
-      <x:c r="I12" s="2" t="s">
-        <x:v>61</x:v>
-      </x:c>
-      <x:c r="J12" s="2" t="s">
-        <x:v>61</x:v>
-      </x:c>
-      <x:c r="K12" s="2" t="s">
-        <x:v>61</x:v>
-      </x:c>
-      <x:c r="L12" s="2" t="s">
-        <x:v>61</x:v>
-      </x:c>
-      <x:c r="M12" s="8" t="str">
-        <x:v>困难主动道具调整选择</x:v>
-      </x:c>
-      <x:c r="N12" s="8" t="str">
-        <x:v>从更高阶的调整类主动道具中挑选一个。</x:v>
-      </x:c>
-      <x:c r="O12" s="8" t="str">
-        <x:v>从 {choiceCount} 个困难主动道具调整中选择 {requiredPickCount} 个。</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13" s="3" customFormat="1">
+      <x:c r="G11" s="3">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H11" s="3" t="s">
+        <x:v>83</x:v>
+      </x:c>
+      <x:c r="I11" s="3" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="J11" s="3" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="K11" s="3" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="L11" s="3" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="M11" s="4" t="s">
+        <x:v>84</x:v>
+      </x:c>
+      <x:c r="N11" s="4" t="s">
+        <x:v>85</x:v>
+      </x:c>
+      <x:c r="O11"/>
+    </x:row>
+    <x:row r="12" s="3" customFormat="1" ht="34">
+      <x:c r="B12" s="3" t="s">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="C12" s="3" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="D12" s="3" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="E12" s="3">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="F12" s="3">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="G12" s="3">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H12" s="3" t="s">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="I12" s="3" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="J12" s="3" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="K12" s="3" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="L12" s="3" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="M12" s="4" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="N12" s="4" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="O12"/>
+    </x:row>
+    <x:row r="13" s="3" customFormat="1" ht="34">
       <x:c r="B13" s="3" t="s">
-        <x:v>82</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="C13" s="3" t="s">
-        <x:v>83</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="D13" s="3" t="s">
         <x:v>58</x:v>
@@ -2178,7 +2247,7 @@
         <x:v>59</x:v>
       </x:c>
       <x:c r="I13" s="3" t="s">
-        <x:v>84</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="J13" s="3" t="s">
         <x:v>61</x:v>
@@ -2189,25 +2258,23 @@
       <x:c r="L13" s="3" t="s">
         <x:v>61</x:v>
       </x:c>
-      <x:c r="M13" s="6" t="str">
-        <x:v>Boss 菜品选择</x:v>
-      </x:c>
-      <x:c r="N13" s="6" t="str">
-        <x:v>击败 Boss 后从高阶菜品中挑选一个加入菜谱池。</x:v>
-      </x:c>
-      <x:c r="O13" s="7" t="str">
-        <x:v>从 {choiceCount} 个 Boss 菜品中选择 {requiredPickCount} 个。</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="14" s="3" customFormat="1">
+      <x:c r="M13" s="4" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="N13" s="4" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="O13"/>
+    </x:row>
+    <x:row r="14" s="3" customFormat="1" ht="34">
       <x:c r="B14" s="3" t="s">
-        <x:v>85</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C14" s="3" t="s">
-        <x:v>86</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="D14" s="3" t="s">
-        <x:v>70</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="E14" s="3">
         <x:v>3</x:v>
@@ -2219,13 +2286,13 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="H14" s="3" t="s">
-        <x:v>87</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="I14" s="3" t="s">
         <x:v>61</x:v>
       </x:c>
       <x:c r="J14" s="3" t="s">
-        <x:v>88</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="K14" s="3" t="s">
         <x:v>61</x:v>
@@ -2233,25 +2300,23 @@
       <x:c r="L14" s="3" t="s">
         <x:v>61</x:v>
       </x:c>
-      <x:c r="M14" s="6" t="str">
-        <x:v>Boss 被动道具选择</x:v>
-      </x:c>
-      <x:c r="N14" s="6" t="str">
-        <x:v>击败 Boss 后从专属被动道具中挑选一个。</x:v>
-      </x:c>
-      <x:c r="O14" s="6" t="str">
-        <x:v>从 {choiceCount} 个 Boss 被动道具中选择 {requiredPickCount} 个。</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="15" s="3" customFormat="1">
+      <x:c r="M14" s="4" t="s">
+        <x:v>79</x:v>
+      </x:c>
+      <x:c r="N14" s="4" t="s">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="O14"/>
+    </x:row>
+    <x:row r="15" s="3" customFormat="1" ht="34">
       <x:c r="B15" s="3" t="s">
-        <x:v>89</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="C15" s="3" t="s">
-        <x:v>90</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="D15" s="3" t="s">
-        <x:v>66</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="E15" s="3">
         <x:v>3</x:v>
@@ -2263,77 +2328,73 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="H15" s="3" t="s">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="I15" s="3" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="J15" s="3" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="K15" s="3" t="s">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="L15" s="3" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="M15" s="4" t="s">
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="N15" s="4" t="s">
+        <x:v>74</x:v>
+      </x:c>
+      <x:c r="O15"/>
+    </x:row>
+    <x:row r="16" s="3" customFormat="1" ht="17">
+      <x:c r="B16" s="3" t="s">
+        <x:v>103</x:v>
+      </x:c>
+      <x:c r="C16" s="3" t="s">
+        <x:v>104</x:v>
+      </x:c>
+      <x:c r="D16" s="3" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="E16" s="3">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F16" s="3">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G16" s="3">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I16" s="3" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="J16" s="3" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="K16" s="3" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="L16" s="3" t="s">
+        <x:v>105</x:v>
+      </x:c>
+      <x:c r="M16" s="4" t="s">
         <x:v>67</x:v>
       </x:c>
-      <x:c r="I15" s="3" t="s">
-        <x:v>61</x:v>
-      </x:c>
-      <x:c r="J15" s="3" t="s">
-        <x:v>61</x:v>
-      </x:c>
-      <x:c r="K15" s="3" t="s">
-        <x:v>88</x:v>
-      </x:c>
-      <x:c r="L15" s="3" t="s">
-        <x:v>61</x:v>
-      </x:c>
-      <x:c r="M15" s="6" t="str">
-        <x:v>Boss 餐桌碎片选择</x:v>
-      </x:c>
-      <x:c r="N15" s="6" t="str">
-        <x:v>击败 Boss 后从高阶餐桌碎片中挑选一块。</x:v>
-      </x:c>
-      <x:c r="O15" s="6" t="str">
-        <x:v>从 {choiceCount} 个 Boss 餐桌碎片中选择 {requiredPickCount} 个。</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="16" s="3" customFormat="1">
-      <x:c r="B16" s="3" t="s">
-        <x:v>91</x:v>
-      </x:c>
-      <x:c r="C16" s="3" t="s">
-        <x:v>92</x:v>
-      </x:c>
-      <x:c r="D16" s="3" t="s">
-        <x:v>63</x:v>
-      </x:c>
-      <x:c r="E16" s="3">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="F16" s="3">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="G16" s="3">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="I16" s="3" t="s">
-        <x:v>61</x:v>
-      </x:c>
-      <x:c r="J16" s="3" t="s">
-        <x:v>61</x:v>
-      </x:c>
-      <x:c r="K16" s="3" t="s">
-        <x:v>61</x:v>
-      </x:c>
-      <x:c r="L16" s="3" t="s">
-        <x:v>93</x:v>
-      </x:c>
-      <x:c r="M16" s="6" t="str">
-        <x:v>Boss 金币奖励</x:v>
-      </x:c>
-      <x:c r="N16" s="6" t="str">
-        <x:v>领取击败 Boss 后获得的额外金币。</x:v>
-      </x:c>
-      <x:c r="O16" s="6" t="str">
-        <x:v>获得 {requiredPickCount} 份 Boss 金币奖励。</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="17">
+      <x:c r="N16" s="4" t="s">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="O16"/>
+    </x:row>
+    <x:row r="17" ht="34">
       <x:c r="B17" s="1" t="s">
-        <x:v>94</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="C17" s="1" t="s">
-        <x:v>94</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="D17" s="1" t="s">
         <x:v>58</x:v>
@@ -2362,22 +2423,20 @@
       <x:c r="L17" s="1" t="s">
         <x:v>61</x:v>
       </x:c>
-      <x:c r="M17" s="6" t="str">
-        <x:v>菜品选择</x:v>
-      </x:c>
-      <x:c r="N17" s="6" t="str">
-        <x:v>从随机菜品中挑选一个加入菜谱池。</x:v>
-      </x:c>
-      <x:c r="O17" s="6" t="str">
-        <x:v>从 {choiceCount} 个菜品中选择 {requiredPickCount} 个。</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18">
+      <x:c r="M17" s="4" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="N17" s="4" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="O17"/>
+    </x:row>
+    <x:row r="18" ht="17">
       <x:c r="B18" s="1" t="s">
-        <x:v>95</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="C18" s="1" t="s">
-        <x:v>95</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="D18" s="1" t="s">
         <x:v>58</x:v>
@@ -2406,25 +2465,23 @@
       <x:c r="L18" s="1" t="s">
         <x:v>61</x:v>
       </x:c>
-      <x:c r="M18" s="6" t="str">
-        <x:v>随机菜品</x:v>
-      </x:c>
-      <x:c r="N18" s="6" t="str">
-        <x:v>随机获得一个菜品并加入菜谱池。</x:v>
-      </x:c>
-      <x:c r="O18" s="6" t="str">
-        <x:v>随机获得 {requiredPickCount} 个菜品。</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19">
+      <x:c r="M18" s="4" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="N18" s="4" t="s">
+        <x:v>108</x:v>
+      </x:c>
+      <x:c r="O18"/>
+    </x:row>
+    <x:row r="19" ht="17">
       <x:c r="B19" s="1" t="s">
-        <x:v>96</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="C19" s="1" t="s">
-        <x:v>96</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="D19" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="E19" s="1">
         <x:v>1</x:v>
@@ -2436,7 +2493,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="H19" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="I19" s="1" t="s">
         <x:v>61</x:v>
@@ -2450,25 +2507,23 @@
       <x:c r="L19" s="1" t="s">
         <x:v>61</x:v>
       </x:c>
-      <x:c r="M19" s="6" t="str">
-        <x:v>随机被动道具</x:v>
-      </x:c>
-      <x:c r="N19" s="6" t="str">
-        <x:v>随机获得一个被动道具，获得后持续生效。</x:v>
-      </x:c>
-      <x:c r="O19" s="6" t="str">
-        <x:v>随机获得 {requiredPickCount} 个被动道具。</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="20">
+      <x:c r="M19" s="4" t="s">
+        <x:v>79</x:v>
+      </x:c>
+      <x:c r="N19" s="4" t="s">
+        <x:v>110</x:v>
+      </x:c>
+      <x:c r="O19"/>
+    </x:row>
+    <x:row r="20" ht="34">
       <x:c r="B20" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="C20" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="D20" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="E20" s="1">
         <x:v>3</x:v>
@@ -2480,7 +2535,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="H20" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="I20" s="1" t="s">
         <x:v>61</x:v>
@@ -2494,25 +2549,23 @@
       <x:c r="L20" s="1" t="s">
         <x:v>61</x:v>
       </x:c>
-      <x:c r="M20" s="6" t="str">
-        <x:v>被动道具选择</x:v>
-      </x:c>
-      <x:c r="N20" s="6" t="str">
-        <x:v>从随机被动道具中挑选一个，获得后持续生效。</x:v>
-      </x:c>
-      <x:c r="O20" s="6" t="str">
-        <x:v>从 {choiceCount} 个被动道具中选择 {requiredPickCount} 个。</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="21">
+      <x:c r="M20" s="4" t="s">
+        <x:v>79</x:v>
+      </x:c>
+      <x:c r="N20" s="4" t="s">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="O20"/>
+    </x:row>
+    <x:row r="21" ht="17">
       <x:c r="B21" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="C21" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="D21" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="E21" s="1">
         <x:v>2</x:v>
@@ -2524,7 +2577,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="H21" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="I21" s="1" t="s">
         <x:v>61</x:v>
@@ -2538,25 +2591,23 @@
       <x:c r="L21" s="1" t="s">
         <x:v>61</x:v>
       </x:c>
-      <x:c r="M21" s="6" t="str">
-        <x:v>被动道具奖励</x:v>
-      </x:c>
-      <x:c r="N21" s="6" t="str">
-        <x:v>获得本组全部被动道具，获得后持续生效。</x:v>
-      </x:c>
-      <x:c r="O21" s="6" t="str">
-        <x:v>获得全部 {choiceCount} 个被动道具。</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="22">
+      <x:c r="M21" s="4" t="s">
+        <x:v>79</x:v>
+      </x:c>
+      <x:c r="N21" s="4" t="s">
+        <x:v>113</x:v>
+      </x:c>
+      <x:c r="O21"/>
+    </x:row>
+    <x:row r="22" ht="17">
       <x:c r="B22" s="1" t="s">
-        <x:v>99</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="C22" s="1" t="s">
-        <x:v>99</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="D22" s="1" t="s">
-        <x:v>100</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="E22" s="1">
         <x:v>1</x:v>
@@ -2568,7 +2619,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="H22" s="1" t="s">
-        <x:v>101</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="I22" s="1" t="s">
         <x:v>61</x:v>
@@ -2582,25 +2633,23 @@
       <x:c r="L22" s="1" t="s">
         <x:v>61</x:v>
       </x:c>
-      <x:c r="M22" s="6" t="str">
-        <x:v>随机主动道具</x:v>
-      </x:c>
-      <x:c r="N22" s="6" t="str">
-        <x:v>随机获得一个可在战斗中使用的主动道具。</x:v>
-      </x:c>
-      <x:c r="O22" s="6" t="str">
-        <x:v>随机获得 {requiredPickCount} 个主动道具。</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="23">
+      <x:c r="M22" s="4" t="s">
+        <x:v>117</x:v>
+      </x:c>
+      <x:c r="N22" s="4" t="s">
+        <x:v>118</x:v>
+      </x:c>
+      <x:c r="O22"/>
+    </x:row>
+    <x:row r="23" ht="17">
       <x:c r="B23" s="1" t="s">
-        <x:v>102</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="C23" s="1" t="s">
-        <x:v>102</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="D23" s="1" t="s">
-        <x:v>100</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="E23" s="1">
         <x:v>2</x:v>
@@ -2612,7 +2661,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="H23" s="1" t="s">
-        <x:v>101</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="I23" s="1" t="s">
         <x:v>61</x:v>
@@ -2626,25 +2675,23 @@
       <x:c r="L23" s="1" t="s">
         <x:v>61</x:v>
       </x:c>
-      <x:c r="M23" s="6" t="str">
-        <x:v>主动道具奖励</x:v>
-      </x:c>
-      <x:c r="N23" s="6" t="str">
-        <x:v>获得本组全部主动道具，可在战斗中使用。</x:v>
-      </x:c>
-      <x:c r="O23" s="6" t="str">
-        <x:v>获得全部 {choiceCount} 个主动道具。</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="24">
+      <x:c r="M23" s="4" t="s">
+        <x:v>117</x:v>
+      </x:c>
+      <x:c r="N23" s="4" t="s">
+        <x:v>120</x:v>
+      </x:c>
+      <x:c r="O23"/>
+    </x:row>
+    <x:row r="24" ht="34">
       <x:c r="B24" s="1" t="s">
-        <x:v>103</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="C24" s="1" t="s">
-        <x:v>103</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="D24" s="1" t="s">
-        <x:v>100</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="E24" s="1">
         <x:v>3</x:v>
@@ -2656,7 +2703,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="H24" s="1" t="s">
-        <x:v>101</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="I24" s="1" t="s">
         <x:v>61</x:v>
@@ -2670,25 +2717,23 @@
       <x:c r="L24" s="1" t="s">
         <x:v>61</x:v>
       </x:c>
-      <x:c r="M24" s="6" t="str">
-        <x:v>主动道具选择</x:v>
-      </x:c>
-      <x:c r="N24" s="6" t="str">
-        <x:v>从随机主动道具中挑选一个，可在战斗中使用。</x:v>
-      </x:c>
-      <x:c r="O24" s="6" t="str">
-        <x:v>从 {choiceCount} 个主动道具中选择 {requiredPickCount} 个。</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="25">
+      <x:c r="M24" s="4" t="s">
+        <x:v>122</x:v>
+      </x:c>
+      <x:c r="N24" s="4" t="s">
+        <x:v>123</x:v>
+      </x:c>
+      <x:c r="O24"/>
+    </x:row>
+    <x:row r="25" ht="34">
       <x:c r="B25" s="1" t="s">
-        <x:v>104</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="C25" s="1" t="s">
-        <x:v>104</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="D25" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="E25" s="1">
         <x:v>3</x:v>
@@ -2700,7 +2745,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="H25" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="I25" s="1" t="s">
         <x:v>61</x:v>
@@ -2714,22 +2759,20 @@
       <x:c r="L25" s="1" t="s">
         <x:v>61</x:v>
       </x:c>
-      <x:c r="M25" s="6" t="str">
-        <x:v>餐桌碎片选择</x:v>
-      </x:c>
-      <x:c r="N25" s="6" t="str">
-        <x:v>从餐桌碎片中挑选一块并进入餐桌编辑。</x:v>
-      </x:c>
-      <x:c r="O25" s="6" t="str">
-        <x:v>从 {choiceCount} 个餐桌碎片中选择 {requiredPickCount} 个。</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="26">
+      <x:c r="M25" s="4" t="s">
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="N25" s="4" t="s">
+        <x:v>125</x:v>
+      </x:c>
+      <x:c r="O25"/>
+    </x:row>
+    <x:row r="26" ht="17">
       <x:c r="B26" s="1" t="s">
-        <x:v>105</x:v>
+        <x:v>126</x:v>
       </x:c>
       <x:c r="C26" s="1" t="s">
-        <x:v>105</x:v>
+        <x:v>126</x:v>
       </x:c>
       <x:c r="D26" s="1" t="s">
         <x:v>58</x:v>
@@ -2744,7 +2787,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="H26" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="I26" s="1" t="s">
         <x:v>61</x:v>
@@ -2758,369 +2801,346 @@
       <x:c r="L26" s="1" t="s">
         <x:v>61</x:v>
       </x:c>
-      <x:c r="M26" s="6" t="str">
-        <x:v>风味菜品奖励</x:v>
-      </x:c>
-      <x:c r="N26" s="6" t="str">
-        <x:v>获得本组全部风味菜品并加入菜谱池。</x:v>
-      </x:c>
-      <x:c r="O26" s="6" t="str">
-        <x:v>获得全部 {choiceCount} 个风味菜品。</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="27">
+      <x:c r="M26" s="4" t="s">
+        <x:v>128</x:v>
+      </x:c>
+      <x:c r="N26" s="4" t="s">
+        <x:v>129</x:v>
+      </x:c>
+      <x:c r="O26"/>
+    </x:row>
+    <x:row r="27" ht="17">
       <x:c r="B27" s="1" t="s">
-        <x:v>107</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="C27" s="1" t="s">
-        <x:v>107</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="D27" s="1" t="s">
+        <x:v>76</x:v>
+      </x:c>
+      <x:c r="E27" s="1">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F27" s="1">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G27" s="1">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H27" s="1" t="s">
+        <x:v>131</x:v>
+      </x:c>
+      <x:c r="I27" s="1" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="J27" s="1" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="K27" s="1" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="L27" s="1" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="M27" s="4" t="s">
+        <x:v>132</x:v>
+      </x:c>
+      <x:c r="N27" s="4" t="s">
+        <x:v>133</x:v>
+      </x:c>
+      <x:c r="O27"/>
+    </x:row>
+    <x:row r="28" ht="17">
+      <x:c r="B28" s="1" t="s">
+        <x:v>134</x:v>
+      </x:c>
+      <x:c r="C28" s="1" t="s">
+        <x:v>134</x:v>
+      </x:c>
+      <x:c r="D28" s="1" t="s">
+        <x:v>115</x:v>
+      </x:c>
+      <x:c r="E28" s="1">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F28" s="1">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G28" s="1">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H28" s="1" t="s">
+        <x:v>135</x:v>
+      </x:c>
+      <x:c r="I28" s="1" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="J28" s="1" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="K28" s="1" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="L28" s="1" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="M28" s="4" t="s">
+        <x:v>136</x:v>
+      </x:c>
+      <x:c r="N28" s="4" t="s">
+        <x:v>137</x:v>
+      </x:c>
+      <x:c r="O28"/>
+    </x:row>
+    <x:row r="29" ht="17">
+      <x:c r="B29" s="1" t="s">
+        <x:v>138</x:v>
+      </x:c>
+      <x:c r="C29" s="1" t="s">
+        <x:v>138</x:v>
+      </x:c>
+      <x:c r="D29" s="1" t="s">
+        <x:v>115</x:v>
+      </x:c>
+      <x:c r="E29" s="1">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F29" s="1">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G29" s="1">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H29" s="1" t="s">
+        <x:v>139</x:v>
+      </x:c>
+      <x:c r="I29" s="1" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="J29" s="1" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="K29" s="1" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="L29" s="1" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="M29" s="4" t="s">
+        <x:v>140</x:v>
+      </x:c>
+      <x:c r="N29" s="4" t="s">
+        <x:v>141</x:v>
+      </x:c>
+      <x:c r="O29"/>
+    </x:row>
+    <x:row r="30" ht="17">
+      <x:c r="B30" s="1" t="s">
+        <x:v>142</x:v>
+      </x:c>
+      <x:c r="C30" s="1" t="s">
+        <x:v>142</x:v>
+      </x:c>
+      <x:c r="D30" s="1" t="s">
+        <x:v>115</x:v>
+      </x:c>
+      <x:c r="E30" s="1">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F30" s="1">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G30" s="1">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H30" s="1" t="s">
+        <x:v>143</x:v>
+      </x:c>
+      <x:c r="I30" s="1" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="J30" s="1" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="K30" s="1" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="L30" s="1" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="M30" s="4" t="s">
+        <x:v>144</x:v>
+      </x:c>
+      <x:c r="N30" s="4" t="s">
+        <x:v>145</x:v>
+      </x:c>
+      <x:c r="O30"/>
+    </x:row>
+    <x:row r="31" ht="17">
+      <x:c r="B31" s="1" t="s">
+        <x:v>146</x:v>
+      </x:c>
+      <x:c r="C31" s="1" t="s">
+        <x:v>147</x:v>
+      </x:c>
+      <x:c r="D31" s="1" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="E31" s="1">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F31" s="1">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G31" s="1">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="I31" s="1" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="J31" s="1" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="K31" s="1" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="L31" s="1" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="M31" s="4" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="N31" s="4" t="s">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="O31"/>
+    </x:row>
+    <x:row r="32" ht="34">
+      <x:c r="B32" s="1" t="s">
+        <x:v>148</x:v>
+      </x:c>
+      <x:c r="C32" s="1" t="s">
+        <x:v>147</x:v>
+      </x:c>
+      <x:c r="D32" s="1" t="s">
         <x:v>70</x:v>
       </x:c>
-      <x:c r="E27" s="1">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="F27" s="1">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="G27" s="1">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H27" s="1" t="s">
-        <x:v>108</x:v>
-      </x:c>
-      <x:c r="I27" s="1" t="s">
-        <x:v>61</x:v>
-      </x:c>
-      <x:c r="J27" s="1" t="s">
-        <x:v>61</x:v>
-      </x:c>
-      <x:c r="K27" s="1" t="s">
-        <x:v>61</x:v>
-      </x:c>
-      <x:c r="L27" s="1" t="s">
-        <x:v>61</x:v>
-      </x:c>
-      <x:c r="M27" s="6" t="str">
-        <x:v>随机传说道具</x:v>
-      </x:c>
-      <x:c r="N27" s="6" t="str">
-        <x:v>随机获得一个传说品质的被动道具。</x:v>
-      </x:c>
-      <x:c r="O27" s="6" t="str">
-        <x:v>随机获得 {requiredPickCount} 个传说道具。</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="28">
-      <x:c r="B28" s="1" t="s">
-        <x:v>109</x:v>
-      </x:c>
-      <x:c r="C28" s="1" t="s">
-        <x:v>109</x:v>
-      </x:c>
-      <x:c r="D28" s="1" t="s">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="E28" s="1">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="F28" s="1">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="G28" s="1">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H28" s="1" t="s">
-        <x:v>110</x:v>
-      </x:c>
-      <x:c r="I28" s="1" t="s">
-        <x:v>61</x:v>
-      </x:c>
-      <x:c r="J28" s="1" t="s">
-        <x:v>61</x:v>
-      </x:c>
-      <x:c r="K28" s="1" t="s">
-        <x:v>61</x:v>
-      </x:c>
-      <x:c r="L28" s="1" t="s">
-        <x:v>61</x:v>
-      </x:c>
-      <x:c r="M28" s="6" t="str">
-        <x:v>随机木质铺设道具</x:v>
-      </x:c>
-      <x:c r="N28" s="6" t="str">
-        <x:v>随机获得一个木质铺设类主动道具。</x:v>
-      </x:c>
-      <x:c r="O28" s="6" t="str">
-        <x:v>随机获得 {requiredPickCount} 个木质铺设道具。</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="29">
-      <x:c r="B29" s="1" t="s">
-        <x:v>111</x:v>
-      </x:c>
-      <x:c r="C29" s="1" t="s">
-        <x:v>111</x:v>
-      </x:c>
-      <x:c r="D29" s="1" t="s">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="E29" s="1">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="F29" s="1">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="G29" s="1">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H29" s="1" t="s">
-        <x:v>112</x:v>
-      </x:c>
-      <x:c r="I29" s="1" t="s">
-        <x:v>61</x:v>
-      </x:c>
-      <x:c r="J29" s="1" t="s">
-        <x:v>61</x:v>
-      </x:c>
-      <x:c r="K29" s="1" t="s">
-        <x:v>61</x:v>
-      </x:c>
-      <x:c r="L29" s="1" t="s">
-        <x:v>61</x:v>
-      </x:c>
-      <x:c r="M29" s="6" t="str">
-        <x:v>随机石质铺设道具</x:v>
-      </x:c>
-      <x:c r="N29" s="6" t="str">
-        <x:v>随机获得一个石质铺设类主动道具。</x:v>
-      </x:c>
-      <x:c r="O29" s="6" t="str">
-        <x:v>随机获得 {requiredPickCount} 个石质铺设道具。</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="30">
-      <x:c r="B30" s="1" t="s">
-        <x:v>113</x:v>
-      </x:c>
-      <x:c r="C30" s="1" t="s">
-        <x:v>113</x:v>
-      </x:c>
-      <x:c r="D30" s="1" t="s">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="E30" s="1">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="F30" s="1">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="G30" s="1">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H30" s="1" t="s">
-        <x:v>114</x:v>
-      </x:c>
-      <x:c r="I30" s="1" t="s">
-        <x:v>61</x:v>
-      </x:c>
-      <x:c r="J30" s="1" t="s">
-        <x:v>61</x:v>
-      </x:c>
-      <x:c r="K30" s="1" t="s">
-        <x:v>61</x:v>
-      </x:c>
-      <x:c r="L30" s="1" t="s">
-        <x:v>61</x:v>
-      </x:c>
-      <x:c r="M30" s="6" t="str">
-        <x:v>随机金属铺设道具</x:v>
-      </x:c>
-      <x:c r="N30" s="6" t="str">
-        <x:v>随机获得一个金属铺设类主动道具。</x:v>
-      </x:c>
-      <x:c r="O30" s="6" t="str">
-        <x:v>随机获得 {requiredPickCount} 个金属铺设道具。</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="31">
-      <x:c r="A31"/>
-      <x:c r="B31" t="str">
-        <x:v>slot_machine_gold</x:v>
-      </x:c>
-      <x:c r="C31" t="str">
-        <x:v>slot_machine_basic</x:v>
-      </x:c>
-      <x:c r="D31" t="str">
-        <x:v>Gold</x:v>
-      </x:c>
-      <x:c r="E31" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="F31" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="G31" t="n">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="H31"/>
-      <x:c r="I31" t="str">
-        <x:v>0,0</x:v>
-      </x:c>
-      <x:c r="J31" t="str">
-        <x:v>0,0</x:v>
-      </x:c>
-      <x:c r="K31" t="str">
-        <x:v>0,0</x:v>
-      </x:c>
-      <x:c r="L31" t="str">
-        <x:v>10,30</x:v>
-      </x:c>
-      <x:c r="M31" t="str">
-        <x:v>抽奖机金币</x:v>
-      </x:c>
-      <x:c r="N31" t="str">
-        <x:v>从抽奖机中获得一笔金币奖励。</x:v>
-      </x:c>
-      <x:c r="O31" t="str">
-        <x:v>获得 {requiredPickCount} 份金币奖励。</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="32">
-      <x:c r="A32"/>
-      <x:c r="B32" t="str">
-        <x:v>slot_machine_fragment</x:v>
-      </x:c>
-      <x:c r="C32" t="str">
-        <x:v>slot_machine_basic</x:v>
-      </x:c>
-      <x:c r="D32" t="str">
-        <x:v>FragmentChoice</x:v>
-      </x:c>
-      <x:c r="E32" t="n">
+      <x:c r="E32" s="1">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="F32" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="G32" t="n">
+      <x:c r="F32" s="1">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G32" s="1">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="H32" t="str">
-        <x:v>pool_fragment</x:v>
-      </x:c>
-      <x:c r="I32" t="str">
-        <x:v>0,0</x:v>
-      </x:c>
-      <x:c r="J32" t="str">
-        <x:v>0,0</x:v>
-      </x:c>
-      <x:c r="K32" t="str">
-        <x:v>0,6</x:v>
-      </x:c>
-      <x:c r="L32" t="str">
-        <x:v>0,0</x:v>
-      </x:c>
-      <x:c r="M32" t="str">
-        <x:v>抽奖机餐桌碎片</x:v>
-      </x:c>
-      <x:c r="N32" t="str">
-        <x:v>从抽奖机的餐桌碎片候选中挑选一块。</x:v>
-      </x:c>
-      <x:c r="O32" t="str">
-        <x:v>从 {choiceCount} 个餐桌碎片中选择 {requiredPickCount} 个。</x:v>
-      </x:c>
+      <x:c r="H32" s="1" t="s">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="I32" s="1" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="J32" s="1" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="K32" s="1" t="s">
+        <x:v>72</x:v>
+      </x:c>
+      <x:c r="L32" s="1" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="M32" s="4" t="s">
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="N32" s="4" t="s">
+        <x:v>74</x:v>
+      </x:c>
+      <x:c r="O32"/>
     </x:row>
     <x:row r="33">
-      <x:c r="A33"/>
-      <x:c r="B33" t="str">
-        <x:v>slot_machine_active</x:v>
-      </x:c>
-      <x:c r="C33" t="str">
-        <x:v>slot_machine_basic</x:v>
-      </x:c>
-      <x:c r="D33" t="str">
-        <x:v>ActiveItemGrant</x:v>
-      </x:c>
-      <x:c r="E33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="F33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="G33" t="n">
+      <x:c r="B33" s="1" t="s">
+        <x:v>149</x:v>
+      </x:c>
+      <x:c r="C33" s="1" t="s">
+        <x:v>147</x:v>
+      </x:c>
+      <x:c r="D33" s="1" t="s">
+        <x:v>115</x:v>
+      </x:c>
+      <x:c r="E33" s="1">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F33" s="1">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G33" s="1">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="H33" t="str">
-        <x:v>pool_active</x:v>
-      </x:c>
-      <x:c r="I33" t="str">
-        <x:v>0,0</x:v>
-      </x:c>
-      <x:c r="J33" t="str">
-        <x:v>0,0</x:v>
-      </x:c>
-      <x:c r="K33" t="str">
-        <x:v>0,0</x:v>
-      </x:c>
-      <x:c r="L33" t="str">
-        <x:v>0,0</x:v>
-      </x:c>
-      <x:c r="M33" t="str">
-        <x:v>抽奖机主动道具</x:v>
-      </x:c>
-      <x:c r="N33" t="str">
-        <x:v>从抽奖机中获得一个可在战斗中使用的主动道具。</x:v>
-      </x:c>
-      <x:c r="O33" t="str">
-        <x:v>随机获得 {requiredPickCount} 个主动道具。</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="34">
-      <x:c r="A34"/>
-      <x:c r="B34" t="str">
-        <x:v>slot_machine_passive</x:v>
-      </x:c>
-      <x:c r="C34" t="str">
-        <x:v>slot_machine_basic</x:v>
-      </x:c>
-      <x:c r="D34" t="str">
-        <x:v>PassiveItemChoice</x:v>
-      </x:c>
-      <x:c r="E34" t="n">
+      <x:c r="H33" s="1" t="s">
+        <x:v>116</x:v>
+      </x:c>
+      <x:c r="I33" s="1" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="J33" s="1" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="K33" s="1" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="L33" s="1" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="M33" s="1" t="s">
+        <x:v>117</x:v>
+      </x:c>
+      <x:c r="N33" s="1" t="s">
+        <x:v>118</x:v>
+      </x:c>
+      <x:c r="O33"/>
+    </x:row>
+    <x:row r="34" ht="34">
+      <x:c r="B34" s="1" t="s">
+        <x:v>150</x:v>
+      </x:c>
+      <x:c r="C34" s="1" t="s">
+        <x:v>147</x:v>
+      </x:c>
+      <x:c r="D34" s="1" t="s">
+        <x:v>76</x:v>
+      </x:c>
+      <x:c r="E34" s="1">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="F34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="G34" t="n">
+      <x:c r="F34" s="1">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G34" s="1">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="H34" t="str">
-        <x:v>pool_passive</x:v>
-      </x:c>
-      <x:c r="I34" t="str">
-        <x:v>0,0</x:v>
-      </x:c>
-      <x:c r="J34" t="str">
-        <x:v>3,6</x:v>
-      </x:c>
-      <x:c r="K34" t="str">
-        <x:v>0,0</x:v>
-      </x:c>
-      <x:c r="L34" t="str">
-        <x:v>0,0</x:v>
-      </x:c>
-      <x:c r="M34" t="str">
-        <x:v>抽奖机被动道具</x:v>
-      </x:c>
-      <x:c r="N34" t="str">
-        <x:v>从抽奖机候选中挑选一个被动道具，获得后持续生效。</x:v>
-      </x:c>
-      <x:c r="O34" t="str">
-        <x:v>从 {choiceCount} 个被动道具中选择 {requiredPickCount} 个。</x:v>
-      </x:c>
+      <x:c r="H34" s="1" t="s">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="I34" s="1" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="J34" s="1" t="s">
+        <x:v>78</x:v>
+      </x:c>
+      <x:c r="K34" s="1" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="L34" s="1" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="M34" s="1" t="s">
+        <x:v>79</x:v>
+      </x:c>
+      <x:c r="N34" s="4" t="s">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="O34"/>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3151,13 +3171,13 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="C1" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="D1" s="1" t="s">
-        <x:v>115</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="E1" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>152</x:v>
       </x:c>
     </x:row>
     <x:row r="2">
@@ -3165,33 +3185,33 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
-        <x:v>117</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="C2" s="1" t="s">
-        <x:v>118</x:v>
+        <x:v>154</x:v>
       </x:c>
       <x:c r="D2" s="1" t="s">
-        <x:v>119</x:v>
+        <x:v>155</x:v>
       </x:c>
       <x:c r="E2" s="1" t="s">
-        <x:v>120</x:v>
+        <x:v>156</x:v>
       </x:c>
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="1" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="B3" s="1" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="B3" s="1" t="s">
-        <x:v>9</x:v>
-      </x:c>
       <x:c r="C3" s="1" t="s">
-        <x:v>121</x:v>
+        <x:v>157</x:v>
       </x:c>
       <x:c r="D3" s="1" t="s">
-        <x:v>122</x:v>
+        <x:v>158</x:v>
       </x:c>
       <x:c r="E3" s="1" t="s">
-        <x:v>123</x:v>
+        <x:v>159</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
@@ -3199,7 +3219,7 @@
         <x:v>59</x:v>
       </x:c>
       <x:c r="C4" s="1" t="s">
-        <x:v>124</x:v>
+        <x:v>160</x:v>
       </x:c>
       <x:c r="D4" s="1" t="b">
         <x:v>1</x:v>
@@ -3207,10 +3227,10 @@
     </x:row>
     <x:row r="5">
       <x:c r="B5" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="C5" s="1" t="s">
-        <x:v>125</x:v>
+        <x:v>161</x:v>
       </x:c>
       <x:c r="D5" s="1" t="b">
         <x:v>1</x:v>
@@ -3218,10 +3238,10 @@
     </x:row>
     <x:row r="6">
       <x:c r="B6" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="C6" s="1" t="s">
-        <x:v>126</x:v>
+        <x:v>162</x:v>
       </x:c>
       <x:c r="D6" s="1" t="b">
         <x:v>1</x:v>
@@ -3229,38 +3249,38 @@
     </x:row>
     <x:row r="7">
       <x:c r="B7" s="1" t="s">
-        <x:v>87</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="C7" s="1" t="s">
-        <x:v>126</x:v>
+        <x:v>162</x:v>
       </x:c>
       <x:c r="D7" s="1" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="E7" s="1" t="s">
-        <x:v>127</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="8" ht="17">
+        <x:v>163</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" ht="409.5">
       <x:c r="B8" s="2" t="s">
-        <x:v>75</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="C8" s="2" t="s">
-        <x:v>74</x:v>
+        <x:v>164</x:v>
       </x:c>
       <x:c r="D8" s="1" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="E8" s="1" t="s">
-        <x:v>128</x:v>
+        <x:v>165</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
       <x:c r="B9" s="2" t="s">
-        <x:v>78</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="C9" s="2" t="s">
-        <x:v>77</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="D9" s="1" t="b">
         <x:v>1</x:v>
@@ -3268,10 +3288,10 @@
     </x:row>
     <x:row r="10">
       <x:c r="B10" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="C10" s="1" t="s">
-        <x:v>124</x:v>
+        <x:v>160</x:v>
       </x:c>
       <x:c r="D10" s="1" t="b">
         <x:v>1</x:v>
@@ -3279,10 +3299,10 @@
     </x:row>
     <x:row r="11">
       <x:c r="B11" s="1" t="s">
-        <x:v>108</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="C11" s="1" t="s">
-        <x:v>126</x:v>
+        <x:v>162</x:v>
       </x:c>
       <x:c r="D11" s="1" t="b">
         <x:v>1</x:v>
@@ -3290,55 +3310,55 @@
     </x:row>
     <x:row r="12">
       <x:c r="B12" s="1" t="s">
-        <x:v>110</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="C12" s="1" t="s">
-        <x:v>129</x:v>
+        <x:v>166</x:v>
       </x:c>
       <x:c r="D12" s="1" t="b">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="E12" t="str">
-        <x:v>LayWood</x:v>
+      <x:c r="E12" t="s">
+        <x:v>167</x:v>
       </x:c>
     </x:row>
     <x:row r="13">
       <x:c r="B13" s="1" t="s">
-        <x:v>112</x:v>
+        <x:v>139</x:v>
       </x:c>
       <x:c r="C13" s="1" t="s">
-        <x:v>129</x:v>
+        <x:v>166</x:v>
       </x:c>
       <x:c r="D13" s="1" t="b">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="E13" t="str">
-        <x:v>LayStone</x:v>
+      <x:c r="E13" t="s">
+        <x:v>168</x:v>
       </x:c>
     </x:row>
     <x:row r="14">
       <x:c r="B14" s="1" t="s">
-        <x:v>114</x:v>
+        <x:v>143</x:v>
       </x:c>
       <x:c r="C14" s="1" t="s">
-        <x:v>129</x:v>
+        <x:v>166</x:v>
       </x:c>
       <x:c r="D14" s="1" t="b">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="E14" t="str">
-        <x:v>LayMetal</x:v>
+      <x:c r="E14" t="s">
+        <x:v>169</x:v>
       </x:c>
     </x:row>
     <x:row r="15">
       <x:c r="A15"/>
-      <x:c r="B15" t="str">
-        <x:v>pool_active</x:v>
-      </x:c>
-      <x:c r="C15" t="str">
-        <x:v>ActiveItem</x:v>
-      </x:c>
-      <x:c r="D15" s="9" t="b">
+      <x:c r="B15" t="s">
+        <x:v>116</x:v>
+      </x:c>
+      <x:c r="C15" t="s">
+        <x:v>166</x:v>
+      </x:c>
+      <x:c r="D15" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="E15"/>

--- a/GourmetProject/GameConfig/Datas/reward.xlsx
+++ b/GourmetProject/GameConfig/Datas/reward.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="15340" activeTab="1"/>
+    <workbookView windowHeight="15360" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="reward_package" sheetId="1" r:id="rId1"/>
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="437" uniqueCount="174">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="437" uniqueCount="175">
   <si>
     <t>##var</t>
   </si>
@@ -246,235 +246,238 @@
     <t>pool_fragment</t>
   </si>
   <si>
+    <t>0,10</t>
+  </si>
+  <si>
+    <t>餐桌格</t>
+  </si>
+  <si>
+    <t>从 {choiceCount} 个餐桌格中选择 {requiredPickCount} 个拼入餐桌</t>
+  </si>
+  <si>
+    <t>slot_specific_passive</t>
+  </si>
+  <si>
+    <t>PassiveItemChoice</t>
+  </si>
+  <si>
+    <t>pool_passive</t>
+  </si>
+  <si>
+    <t>3,6</t>
+  </si>
+  <si>
+    <t>装饰品</t>
+  </si>
+  <si>
+    <t>从 {choiceCount} 个装饰品中选择 {requiredPickCount} 个</t>
+  </si>
+  <si>
+    <t>slot_specific_active_strengthen</t>
+  </si>
+  <si>
+    <t>ActiveItemStrengthen</t>
+  </si>
+  <si>
+    <t>pool_active_strengthen</t>
+  </si>
+  <si>
+    <t>强化箱</t>
+  </si>
+  <si>
+    <t>从 {choiceCount} 个强化箱中选择 {requiredPickCount} 个</t>
+  </si>
+  <si>
+    <t>slot_specific_active_adjust</t>
+  </si>
+  <si>
+    <t>ActiveItemAdjust</t>
+  </si>
+  <si>
+    <t>pool_active_adjust</t>
+  </si>
+  <si>
+    <t>调整单</t>
+  </si>
+  <si>
+    <t>从 {choiceCount} 个调整单中选择 {requiredPickCount} 个</t>
+  </si>
+  <si>
+    <t>slot_specific_hard_passive</t>
+  </si>
+  <si>
+    <t>slot_specific_hard_active_strengthen</t>
+  </si>
+  <si>
+    <t>slot_specific_hard_active_adjust</t>
+  </si>
+  <si>
+    <t>slot_boss_dish</t>
+  </si>
+  <si>
+    <t>boss_dish</t>
+  </si>
+  <si>
+    <t>10,0</t>
+  </si>
+  <si>
+    <t>slot_boss_passive</t>
+  </si>
+  <si>
+    <t>boss_passive</t>
+  </si>
+  <si>
+    <t>pool_passive_boss</t>
+  </si>
+  <si>
+    <t>7,0</t>
+  </si>
+  <si>
+    <t>slot_boss_fragment</t>
+  </si>
+  <si>
+    <t>boss_fragment</t>
+  </si>
+  <si>
+    <t>slot_boss_gold</t>
+  </si>
+  <si>
+    <t>boss_gold</t>
+  </si>
+  <si>
+    <t>50,0</t>
+  </si>
+  <si>
+    <t>dish_choice_3</t>
+  </si>
+  <si>
+    <t>dish_grant_1</t>
+  </si>
+  <si>
+    <t>随机获得 {requiredPickCount} 个食物</t>
+  </si>
+  <si>
+    <t>passive_choice_1</t>
+  </si>
+  <si>
+    <t>随机获得 {requiredPickCount} 个装饰品</t>
+  </si>
+  <si>
+    <t>passive_choice_3</t>
+  </si>
+  <si>
+    <t>passive_grant_2</t>
+  </si>
+  <si>
+    <t>获得全部 {choiceCount} 个装饰品</t>
+  </si>
+  <si>
+    <t>active_grant_1</t>
+  </si>
+  <si>
+    <t>ActiveItemGrant</t>
+  </si>
+  <si>
+    <t>pool_active</t>
+  </si>
+  <si>
+    <t>消耗品</t>
+  </si>
+  <si>
+    <t>随机获得 {requiredPickCount} 个消耗品</t>
+  </si>
+  <si>
+    <t>active_grant_2</t>
+  </si>
+  <si>
+    <t>获得全部 {choiceCount} 个消耗品</t>
+  </si>
+  <si>
+    <t>active_choice_3</t>
+  </si>
+  <si>
+    <t>消耗品选择</t>
+  </si>
+  <si>
+    <t>从 {choiceCount} 个消耗品中选择 {requiredPickCount} 个</t>
+  </si>
+  <si>
+    <t>fragment_choice_3</t>
+  </si>
+  <si>
+    <t>从 {choiceCount} 个餐桌格中选择 {requiredPickCount} 个</t>
+  </si>
+  <si>
+    <t>flavored_dish_3</t>
+  </si>
+  <si>
+    <t>pool_flavored_dish</t>
+  </si>
+  <si>
+    <t>风味食物</t>
+  </si>
+  <si>
+    <t>获得全部 {choiceCount} 个风味食物</t>
+  </si>
+  <si>
+    <t>legendary_choice_1</t>
+  </si>
+  <si>
+    <t>pool_legendary</t>
+  </si>
+  <si>
+    <t>传说装饰品</t>
+  </si>
+  <si>
+    <t>随机获得 {requiredPickCount} 个传说装饰品</t>
+  </si>
+  <si>
+    <t>lay_wood</t>
+  </si>
+  <si>
+    <t>pool_lay_wood</t>
+  </si>
+  <si>
+    <t>木质强化箱</t>
+  </si>
+  <si>
+    <t>随机获得 {requiredPickCount} 个木质强化箱</t>
+  </si>
+  <si>
+    <t>lay_stone</t>
+  </si>
+  <si>
+    <t>pool_lay_stone</t>
+  </si>
+  <si>
+    <t>石质强化箱</t>
+  </si>
+  <si>
+    <t>随机获得 {requiredPickCount} 个石质强化箱</t>
+  </si>
+  <si>
+    <t>lay_metal</t>
+  </si>
+  <si>
+    <t>pool_lay_metal</t>
+  </si>
+  <si>
+    <t>金属强化箱</t>
+  </si>
+  <si>
+    <t>随机获得 {requiredPickCount} 个金属强化箱</t>
+  </si>
+  <si>
+    <t>slot_machine_gold</t>
+  </si>
+  <si>
+    <t>slot_machine_basic</t>
+  </si>
+  <si>
+    <t>slot_machine_fragment</t>
+  </si>
+  <si>
     <t>0,6</t>
-  </si>
-  <si>
-    <t>餐桌格</t>
-  </si>
-  <si>
-    <t>从 {choiceCount} 个餐桌格中选择 {requiredPickCount} 个拼入餐桌</t>
-  </si>
-  <si>
-    <t>slot_specific_passive</t>
-  </si>
-  <si>
-    <t>PassiveItemChoice</t>
-  </si>
-  <si>
-    <t>pool_passive</t>
-  </si>
-  <si>
-    <t>3,6</t>
-  </si>
-  <si>
-    <t>装饰品</t>
-  </si>
-  <si>
-    <t>从 {choiceCount} 个装饰品中选择 {requiredPickCount} 个</t>
-  </si>
-  <si>
-    <t>slot_specific_active_strengthen</t>
-  </si>
-  <si>
-    <t>ActiveItemStrengthen</t>
-  </si>
-  <si>
-    <t>pool_active_strengthen</t>
-  </si>
-  <si>
-    <t>强化箱</t>
-  </si>
-  <si>
-    <t>从 {choiceCount} 个强化箱中选择 {requiredPickCount} 个</t>
-  </si>
-  <si>
-    <t>slot_specific_active_adjust</t>
-  </si>
-  <si>
-    <t>ActiveItemAdjust</t>
-  </si>
-  <si>
-    <t>pool_active_adjust</t>
-  </si>
-  <si>
-    <t>调整单</t>
-  </si>
-  <si>
-    <t>从 {choiceCount} 个调整单中选择 {requiredPickCount} 个</t>
-  </si>
-  <si>
-    <t>slot_specific_hard_passive</t>
-  </si>
-  <si>
-    <t>slot_specific_hard_active_strengthen</t>
-  </si>
-  <si>
-    <t>slot_specific_hard_active_adjust</t>
-  </si>
-  <si>
-    <t>slot_boss_dish</t>
-  </si>
-  <si>
-    <t>boss_dish</t>
-  </si>
-  <si>
-    <t>10,0</t>
-  </si>
-  <si>
-    <t>slot_boss_passive</t>
-  </si>
-  <si>
-    <t>boss_passive</t>
-  </si>
-  <si>
-    <t>pool_passive_boss</t>
-  </si>
-  <si>
-    <t>7,0</t>
-  </si>
-  <si>
-    <t>slot_boss_fragment</t>
-  </si>
-  <si>
-    <t>boss_fragment</t>
-  </si>
-  <si>
-    <t>slot_boss_gold</t>
-  </si>
-  <si>
-    <t>boss_gold</t>
-  </si>
-  <si>
-    <t>50,0</t>
-  </si>
-  <si>
-    <t>dish_choice_3</t>
-  </si>
-  <si>
-    <t>dish_grant_1</t>
-  </si>
-  <si>
-    <t>随机获得 {requiredPickCount} 个食物</t>
-  </si>
-  <si>
-    <t>passive_choice_1</t>
-  </si>
-  <si>
-    <t>随机获得 {requiredPickCount} 个装饰品</t>
-  </si>
-  <si>
-    <t>passive_choice_3</t>
-  </si>
-  <si>
-    <t>passive_grant_2</t>
-  </si>
-  <si>
-    <t>获得全部 {choiceCount} 个装饰品</t>
-  </si>
-  <si>
-    <t>active_grant_1</t>
-  </si>
-  <si>
-    <t>ActiveItemGrant</t>
-  </si>
-  <si>
-    <t>pool_active</t>
-  </si>
-  <si>
-    <t>消耗品</t>
-  </si>
-  <si>
-    <t>随机获得 {requiredPickCount} 个消耗品</t>
-  </si>
-  <si>
-    <t>active_grant_2</t>
-  </si>
-  <si>
-    <t>获得全部 {choiceCount} 个消耗品</t>
-  </si>
-  <si>
-    <t>active_choice_3</t>
-  </si>
-  <si>
-    <t>消耗品选择</t>
-  </si>
-  <si>
-    <t>从 {choiceCount} 个消耗品中选择 {requiredPickCount} 个</t>
-  </si>
-  <si>
-    <t>fragment_choice_3</t>
-  </si>
-  <si>
-    <t>从 {choiceCount} 个餐桌格中选择 {requiredPickCount} 个</t>
-  </si>
-  <si>
-    <t>flavored_dish_3</t>
-  </si>
-  <si>
-    <t>pool_flavored_dish</t>
-  </si>
-  <si>
-    <t>风味食物</t>
-  </si>
-  <si>
-    <t>获得全部 {choiceCount} 个风味食物</t>
-  </si>
-  <si>
-    <t>legendary_choice_1</t>
-  </si>
-  <si>
-    <t>pool_legendary</t>
-  </si>
-  <si>
-    <t>传说装饰品</t>
-  </si>
-  <si>
-    <t>随机获得 {requiredPickCount} 个传说装饰品</t>
-  </si>
-  <si>
-    <t>lay_wood</t>
-  </si>
-  <si>
-    <t>pool_lay_wood</t>
-  </si>
-  <si>
-    <t>木质强化箱</t>
-  </si>
-  <si>
-    <t>随机获得 {requiredPickCount} 个木质强化箱</t>
-  </si>
-  <si>
-    <t>lay_stone</t>
-  </si>
-  <si>
-    <t>pool_lay_stone</t>
-  </si>
-  <si>
-    <t>石质强化箱</t>
-  </si>
-  <si>
-    <t>随机获得 {requiredPickCount} 个石质强化箱</t>
-  </si>
-  <si>
-    <t>lay_metal</t>
-  </si>
-  <si>
-    <t>pool_lay_metal</t>
-  </si>
-  <si>
-    <t>金属强化箱</t>
-  </si>
-  <si>
-    <t>随机获得 {requiredPickCount} 个金属强化箱</t>
-  </si>
-  <si>
-    <t>slot_machine_gold</t>
-  </si>
-  <si>
-    <t>slot_machine_basic</t>
-  </si>
-  <si>
-    <t>slot_machine_fragment</t>
   </si>
   <si>
     <t>slot_machine_active</t>
@@ -1895,7 +1898,7 @@
       </c>
       <c r="O1"/>
     </row>
-    <row r="2" ht="34" spans="1:15">
+    <row r="2" ht="17" spans="1:15">
       <c r="A2" s="1" t="s">
         <v>4</v>
       </c>
@@ -3192,7 +3195,7 @@
         <v>65</v>
       </c>
       <c r="K32" s="1" t="s">
-        <v>76</v>
+        <v>153</v>
       </c>
       <c r="L32" s="1" t="s">
         <v>65</v>
@@ -3207,7 +3210,7 @@
     </row>
     <row r="33" ht="17" spans="2:15">
       <c r="B33" s="1" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C33" s="1" t="s">
         <v>151</v>
@@ -3249,7 +3252,7 @@
     </row>
     <row r="34" ht="17" spans="2:15">
       <c r="B34" s="1" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C34" s="1" t="s">
         <v>151</v>
@@ -3324,10 +3327,10 @@
         <v>33</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -3335,16 +3338,16 @@
         <v>4</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -3355,13 +3358,13 @@
         <v>9</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="4" spans="2:4">
@@ -3369,7 +3372,7 @@
         <v>63</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="D4" s="1" t="b">
         <v>1</v>
@@ -3380,7 +3383,7 @@
         <v>75</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="D5" s="1" t="b">
         <v>1</v>
@@ -3391,7 +3394,7 @@
         <v>81</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="D6" s="1" t="b">
         <v>1</v>
@@ -3402,13 +3405,13 @@
         <v>103</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="D7" s="1" t="b">
         <v>1</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="8" ht="409.5" spans="2:5">
@@ -3416,13 +3419,13 @@
         <v>87</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="D8" s="1" t="b">
         <v>1</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="9" spans="2:4">
@@ -3441,7 +3444,7 @@
         <v>131</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="D10" s="1" t="b">
         <v>1</v>
@@ -3452,7 +3455,7 @@
         <v>135</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="D11" s="1" t="b">
         <v>1</v>
@@ -3463,13 +3466,13 @@
         <v>139</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="D12" s="1" t="b">
         <v>1</v>
       </c>
       <c r="E12" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
     </row>
     <row r="13" spans="2:5">
@@ -3477,13 +3480,13 @@
         <v>143</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="D13" s="1" t="b">
         <v>1</v>
       </c>
       <c r="E13" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="14" spans="2:5">
@@ -3491,13 +3494,13 @@
         <v>147</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="D14" s="1" t="b">
         <v>1</v>
       </c>
       <c r="E14" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="15" spans="1:5">
@@ -3506,7 +3509,7 @@
         <v>120</v>
       </c>
       <c r="C15" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="D15" t="b">
         <v>1</v>

--- a/GourmetProject/GameConfig/Datas/reward.xlsx
+++ b/GourmetProject/GameConfig/Datas/reward.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="reward_package" sheetId="1" r:id="R0dd3cb49083c4e34"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="reward_slot" sheetId="2" r:id="Rf5597d1267634f34"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="reward_pool" sheetId="3" r:id="Rf72b1e1401464d02"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="reward_package" sheetId="1" r:id="Ra8d1fb4bae4c4417"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="reward_slot" sheetId="2" r:id="R7b8a8705b3494db3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="reward_pool" sheetId="3" r:id="Re1159c8427d44dc5"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -141,9 +141,6 @@
     <x:t xml:space="preserve">name</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">ruleTemplate</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">奖励槽ID</x:t>
   </x:si>
   <x:si>
@@ -180,9 +177,6 @@
     <x:t xml:space="preserve">奖励组显示名称</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">规则文案模板；仅支持 {choiceCount} 与 {requiredPickCount}。</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">RewardKind</x:t>
   </x:si>
   <x:si>
@@ -213,9 +207,6 @@
     <x:t xml:space="preserve">食物</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">从 {choiceCount} 个食物中选择 {requiredPickCount} 个加入食谱</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">slot_specific_gold</x:t>
   </x:si>
   <x:si>
@@ -228,9 +219,6 @@
     <x:t xml:space="preserve">金币</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">金币+ {requiredPickCount}</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">slot_specific_fragment</x:t>
   </x:si>
   <x:si>
@@ -246,9 +234,6 @@
     <x:t xml:space="preserve">餐桌格</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">从 {choiceCount} 个餐桌格中选择 {requiredPickCount} 个拼入餐桌</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">slot_specific_passive</x:t>
   </x:si>
   <x:si>
@@ -264,9 +249,6 @@
     <x:t xml:space="preserve">装饰品</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">从 {choiceCount} 个装饰品中选择 {requiredPickCount} 个</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">slot_specific_active_strengthen</x:t>
   </x:si>
   <x:si>
@@ -279,9 +261,6 @@
     <x:t xml:space="preserve">强化箱</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">从 {choiceCount} 个强化箱中选择 {requiredPickCount} 个</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">slot_specific_active_adjust</x:t>
   </x:si>
   <x:si>
@@ -294,9 +273,6 @@
     <x:t xml:space="preserve">调整单</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">从 {choiceCount} 个调整单中选择 {requiredPickCount} 个</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">slot_specific_hard_passive</x:t>
   </x:si>
   <x:si>
@@ -348,24 +324,15 @@
     <x:t xml:space="preserve">dish_grant_1</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">随机获得 {requiredPickCount} 个食物</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">passive_choice_1</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">随机获得 {requiredPickCount} 个装饰品</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">passive_choice_3</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">passive_grant_2</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">获得全部 {choiceCount} 个装饰品</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">active_grant_1</x:t>
   </x:si>
   <x:si>
@@ -378,30 +345,18 @@
     <x:t xml:space="preserve">消耗品</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">随机获得 {requiredPickCount} 个消耗品</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">active_grant_2</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">获得全部 {choiceCount} 个消耗品</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">active_choice_3</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">消耗品选择</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">从 {choiceCount} 个消耗品中选择 {requiredPickCount} 个</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">fragment_choice_3</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">从 {choiceCount} 个餐桌格中选择 {requiredPickCount} 个</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">flavored_dish_3</x:t>
   </x:si>
   <x:si>
@@ -411,9 +366,6 @@
     <x:t xml:space="preserve">风味食物</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">获得全部 {choiceCount} 个风味食物</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">legendary_choice_1</x:t>
   </x:si>
   <x:si>
@@ -423,9 +375,6 @@
     <x:t xml:space="preserve">传说装饰品</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">随机获得 {requiredPickCount} 个传说装饰品</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">lay_wood</x:t>
   </x:si>
   <x:si>
@@ -435,9 +384,6 @@
     <x:t xml:space="preserve">木质强化箱</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">随机获得 {requiredPickCount} 个木质强化箱</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">lay_stone</x:t>
   </x:si>
   <x:si>
@@ -447,9 +393,6 @@
     <x:t xml:space="preserve">石质强化箱</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">随机获得 {requiredPickCount} 个石质强化箱</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">lay_metal</x:t>
   </x:si>
   <x:si>
@@ -457,9 +400,6 @@
   </x:si>
   <x:si>
     <x:t xml:space="preserve">金属强化箱</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">随机获得 {requiredPickCount} 个金属强化箱</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">slot_machine_gold</x:t>
@@ -1762,8 +1702,8 @@
       <x:c r="M1" s="4" t="s">
         <x:v>42</x:v>
       </x:c>
-      <x:c r="N1" s="4" t="s">
-        <x:v>43</x:v>
+      <x:c r="N1" s="4" t="str">
+        <x:v>ruleTemplate</x:v>
       </x:c>
       <x:c r="O1"/>
     </x:row>
@@ -1772,43 +1712,43 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="C2" s="1" t="s">
         <x:v>44</x:v>
       </x:c>
-      <x:c r="C2" s="1" t="s">
+      <x:c r="D2" s="1" t="s">
         <x:v>45</x:v>
       </x:c>
-      <x:c r="D2" s="1" t="s">
+      <x:c r="E2" s="1" t="s">
         <x:v>46</x:v>
       </x:c>
-      <x:c r="E2" s="1" t="s">
+      <x:c r="F2" s="1" t="s">
         <x:v>47</x:v>
       </x:c>
-      <x:c r="F2" s="1" t="s">
+      <x:c r="G2" s="1" t="s">
         <x:v>48</x:v>
       </x:c>
-      <x:c r="G2" s="1" t="s">
+      <x:c r="H2" s="1" t="s">
         <x:v>49</x:v>
       </x:c>
-      <x:c r="H2" s="1" t="s">
+      <x:c r="I2" s="1" t="s">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="I2" s="1" t="s">
+      <x:c r="J2" s="1" t="s">
         <x:v>51</x:v>
       </x:c>
-      <x:c r="J2" s="1" t="s">
+      <x:c r="K2" s="1" t="s">
         <x:v>52</x:v>
       </x:c>
-      <x:c r="K2" s="1" t="s">
+      <x:c r="L2" s="1" t="s">
         <x:v>53</x:v>
       </x:c>
-      <x:c r="L2" s="1" t="s">
+      <x:c r="M2" s="4" t="s">
         <x:v>54</x:v>
       </x:c>
-      <x:c r="M2" s="4" t="s">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="N2" s="4" t="s">
-        <x:v>56</x:v>
+      <x:c r="N2" s="4" t="str">
+        <x:v>规则文案模板；仅支持 {choiceCount} 与 {requiredPickCount}。</x:v>
       </x:c>
       <x:c r="O2"/>
     </x:row>
@@ -1823,49 +1763,49 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D3" s="1" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="E3" s="1" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="F3" s="1" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="G3" s="1" t="s">
         <x:v>57</x:v>
-      </x:c>
-      <x:c r="E3" s="1" t="s">
-        <x:v>58</x:v>
-      </x:c>
-      <x:c r="F3" s="1" t="s">
-        <x:v>58</x:v>
-      </x:c>
-      <x:c r="G3" s="1" t="s">
-        <x:v>59</x:v>
       </x:c>
       <x:c r="H3" s="1" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="I3" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="J3" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="K3" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="L3" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="M3" s="4" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="N3" s="4" t="s">
-        <x:v>9</x:v>
+      <x:c r="N3" s="4" t="str">
+        <x:v>string</x:v>
       </x:c>
       <x:c r="O3"/>
     </x:row>
     <x:row r="4" ht="17">
       <x:c r="B4" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="C4" s="1" t="s">
         <x:v>12</x:v>
       </x:c>
       <x:c r="D4" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="E4" s="1">
         <x:v>3</x:v>
@@ -1877,37 +1817,37 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="H4" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="I4" s="1" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="J4" s="1" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="K4" s="1" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="L4" s="1" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="M4" s="4" t="s">
         <x:v>64</x:v>
       </x:c>
-      <x:c r="J4" s="1" t="s">
-        <x:v>65</x:v>
-      </x:c>
-      <x:c r="K4" s="1" t="s">
-        <x:v>65</x:v>
-      </x:c>
-      <x:c r="L4" s="1" t="s">
-        <x:v>65</x:v>
-      </x:c>
-      <x:c r="M4" s="4" t="s">
-        <x:v>66</x:v>
-      </x:c>
-      <x:c r="N4" s="4" t="s">
-        <x:v>67</x:v>
+      <x:c r="N4" s="4" t="str">
+        <x:v>从 {choiceCount} 个食物中选择 {requiredPickCount} 个加入食谱</x:v>
       </x:c>
       <x:c r="O4"/>
     </x:row>
     <x:row r="5" ht="17">
       <x:c r="B5" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="C5" s="1" t="s">
         <x:v>13</x:v>
       </x:c>
       <x:c r="D5" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="E5" s="1">
         <x:v>1</x:v>
@@ -1919,34 +1859,34 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I5" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="J5" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="K5" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="L5" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="M5" s="4" t="s">
-        <x:v>71</x:v>
-      </x:c>
-      <x:c r="N5" s="4" t="s">
-        <x:v>72</x:v>
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="N5" s="4" t="str">
+        <x:v>[gold]金币+ {requiredPickCount}[/gold]</x:v>
       </x:c>
       <x:c r="O5"/>
     </x:row>
     <x:row r="6" ht="17">
       <x:c r="B6" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="C6" s="1" t="s">
         <x:v>21</x:v>
       </x:c>
       <x:c r="D6" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="E6" s="1">
         <x:v>3</x:v>
@@ -1958,38 +1898,38 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="H6" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="I6" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="J6" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="K6" s="1" t="s">
-        <x:v>76</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="L6" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="M6" s="4" t="s">
-        <x:v>77</x:v>
-      </x:c>
-      <x:c r="N6" s="4" t="s">
-        <x:v>78</x:v>
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="N6" s="4" t="str">
+        <x:v>从 {choiceCount} 个餐桌格中选择 {requiredPickCount} 个拼入餐桌</x:v>
       </x:c>
       <x:c r="O6"/>
     </x:row>
     <x:row r="7" s="3" customFormat="1" ht="17">
       <x:c r="A7" s="1"/>
       <x:c r="B7" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="C7" s="1" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="D7" s="1" t="s">
-        <x:v>80</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="E7" s="1">
         <x:v>2</x:v>
@@ -2001,38 +1941,38 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="H7" s="1" t="s">
-        <x:v>81</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="I7" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="J7" s="1" t="s">
-        <x:v>82</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="K7" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="L7" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="M7" s="4" t="s">
-        <x:v>83</x:v>
-      </x:c>
-      <x:c r="N7" s="4" t="s">
-        <x:v>84</x:v>
+        <x:v>78</x:v>
+      </x:c>
+      <x:c r="N7" s="4" t="str">
+        <x:v>从 {choiceCount} 个[term]装饰品[/term]中选择 {requiredPickCount} 个</x:v>
       </x:c>
       <x:c r="O7"/>
     </x:row>
     <x:row r="8" s="3" customFormat="1" ht="17">
       <x:c r="A8" s="1"/>
       <x:c r="B8" s="1" t="s">
-        <x:v>85</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="C8" s="1" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="D8" s="1" t="s">
-        <x:v>86</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="E8" s="1">
         <x:v>3</x:v>
@@ -2044,38 +1984,38 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="H8" s="1" t="s">
-        <x:v>87</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="I8" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="J8" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="K8" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="L8" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="M8" s="4" t="s">
-        <x:v>88</x:v>
-      </x:c>
-      <x:c r="N8" s="4" t="s">
-        <x:v>89</x:v>
+        <x:v>82</x:v>
+      </x:c>
+      <x:c r="N8" s="4" t="str">
+        <x:v>从 {choiceCount} 个强化箱中选择 {requiredPickCount} 个</x:v>
       </x:c>
       <x:c r="O8"/>
     </x:row>
     <x:row r="9" s="3" customFormat="1" ht="17">
       <x:c r="A9" s="1"/>
       <x:c r="B9" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="C9" s="1" t="s">
         <x:v>19</x:v>
       </x:c>
       <x:c r="D9" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="E9" s="1">
         <x:v>3</x:v>
@@ -2087,38 +2027,38 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="H9" s="1" t="s">
-        <x:v>92</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="I9" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="J9" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="K9" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="L9" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="M9" s="4" t="s">
-        <x:v>93</x:v>
-      </x:c>
-      <x:c r="N9" s="4" t="s">
-        <x:v>94</x:v>
+        <x:v>86</x:v>
+      </x:c>
+      <x:c r="N9" s="4" t="str">
+        <x:v>从 {choiceCount} 个调整单中选择 {requiredPickCount} 个</x:v>
       </x:c>
       <x:c r="O9"/>
     </x:row>
     <x:row r="10" s="3" customFormat="1" ht="17">
       <x:c r="A10" s="1"/>
       <x:c r="B10" s="1" t="s">
-        <x:v>95</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="C10" s="1" t="s">
         <x:v>24</x:v>
       </x:c>
       <x:c r="D10" s="1" t="s">
-        <x:v>80</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="E10" s="1">
         <x:v>4</x:v>
@@ -2130,38 +2070,38 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="H10" s="1" t="s">
-        <x:v>81</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="I10" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="J10" s="1" t="s">
-        <x:v>82</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="K10" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="L10" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="M10" s="4" t="s">
-        <x:v>83</x:v>
-      </x:c>
-      <x:c r="N10" s="4" t="s">
-        <x:v>84</x:v>
+        <x:v>78</x:v>
+      </x:c>
+      <x:c r="N10" s="4" t="str">
+        <x:v>从 {choiceCount} 个[term]装饰品[/term]中选择 {requiredPickCount} 个</x:v>
       </x:c>
       <x:c r="O10"/>
     </x:row>
     <x:row r="11" s="3" customFormat="1" ht="17">
       <x:c r="A11" s="1"/>
       <x:c r="B11" s="1" t="s">
-        <x:v>96</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="C11" s="1" t="s">
         <x:v>26</x:v>
       </x:c>
       <x:c r="D11" s="1" t="s">
-        <x:v>86</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="E11" s="1">
         <x:v>5</x:v>
@@ -2173,38 +2113,38 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="H11" s="1" t="s">
-        <x:v>87</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="I11" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="J11" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="K11" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="L11" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="M11" s="4" t="s">
-        <x:v>88</x:v>
-      </x:c>
-      <x:c r="N11" s="4" t="s">
-        <x:v>89</x:v>
+        <x:v>82</x:v>
+      </x:c>
+      <x:c r="N11" s="4" t="str">
+        <x:v>从 {choiceCount} 个强化箱中选择 {requiredPickCount} 个</x:v>
       </x:c>
       <x:c r="O11"/>
     </x:row>
     <x:row r="12" s="3" customFormat="1" ht="17">
       <x:c r="A12" s="1"/>
       <x:c r="B12" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="C12" s="1" t="s">
         <x:v>28</x:v>
       </x:c>
       <x:c r="D12" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="E12" s="1">
         <x:v>5</x:v>
@@ -2216,38 +2156,38 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="H12" s="1" t="s">
-        <x:v>92</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="I12" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="J12" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="K12" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="L12" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="M12" s="4" t="s">
-        <x:v>93</x:v>
-      </x:c>
-      <x:c r="N12" s="4" t="s">
-        <x:v>94</x:v>
+        <x:v>86</x:v>
+      </x:c>
+      <x:c r="N12" s="4" t="str">
+        <x:v>从 {choiceCount} 个调整单中选择 {requiredPickCount} 个</x:v>
       </x:c>
       <x:c r="O12"/>
     </x:row>
     <x:row r="13" s="3" customFormat="1" ht="17">
       <x:c r="A13" s="1"/>
       <x:c r="B13" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C13" s="1" t="s">
-        <x:v>99</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="D13" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="E13" s="1">
         <x:v>3</x:v>
@@ -2259,38 +2199,38 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="H13" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="I13" s="1" t="s">
-        <x:v>100</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="J13" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="K13" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="L13" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="M13" s="4" t="s">
-        <x:v>66</x:v>
-      </x:c>
-      <x:c r="N13" s="4" t="s">
-        <x:v>67</x:v>
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="N13" s="4" t="str">
+        <x:v>从 {choiceCount} 个食物中选择 {requiredPickCount} 个加入食谱</x:v>
       </x:c>
       <x:c r="O13"/>
     </x:row>
     <x:row r="14" s="3" customFormat="1" ht="17">
       <x:c r="A14" s="1"/>
       <x:c r="B14" s="1" t="s">
-        <x:v>101</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="C14" s="1" t="s">
-        <x:v>102</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="D14" s="1" t="s">
-        <x:v>80</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="E14" s="1">
         <x:v>3</x:v>
@@ -2302,38 +2242,38 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="H14" s="1" t="s">
-        <x:v>103</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="I14" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="J14" s="1" t="s">
-        <x:v>104</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="K14" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="L14" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="M14" s="4" t="s">
-        <x:v>83</x:v>
-      </x:c>
-      <x:c r="N14" s="4" t="s">
-        <x:v>84</x:v>
+        <x:v>78</x:v>
+      </x:c>
+      <x:c r="N14" s="4" t="str">
+        <x:v>从 {choiceCount} 个[term]装饰品[/term]中选择 {requiredPickCount} 个</x:v>
       </x:c>
       <x:c r="O14"/>
     </x:row>
     <x:row r="15" s="3" customFormat="1" ht="17">
       <x:c r="A15" s="1"/>
       <x:c r="B15" s="1" t="s">
-        <x:v>105</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C15" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="D15" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="E15" s="1">
         <x:v>3</x:v>
@@ -2345,38 +2285,38 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="H15" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="I15" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="J15" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="K15" s="1" t="s">
-        <x:v>104</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="L15" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="M15" s="4" t="s">
-        <x:v>77</x:v>
-      </x:c>
-      <x:c r="N15" s="4" t="s">
-        <x:v>78</x:v>
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="N15" s="4" t="str">
+        <x:v>从 {choiceCount} 个餐桌格中选择 {requiredPickCount} 个拼入餐桌</x:v>
       </x:c>
       <x:c r="O15"/>
     </x:row>
     <x:row r="16" s="3" customFormat="1" ht="17">
       <x:c r="A16" s="1"/>
       <x:c r="B16" s="1" t="s">
-        <x:v>107</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="C16" s="1" t="s">
-        <x:v>108</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="D16" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="E16" s="1">
         <x:v>1</x:v>
@@ -2389,34 +2329,34 @@
       </x:c>
       <x:c r="H16" s="1"/>
       <x:c r="I16" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="J16" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="K16" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="L16" s="1" t="s">
-        <x:v>109</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="M16" s="4" t="s">
-        <x:v>71</x:v>
-      </x:c>
-      <x:c r="N16" s="4" t="s">
-        <x:v>72</x:v>
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="N16" s="4" t="str">
+        <x:v>[gold]金币+ {requiredPickCount}[/gold]</x:v>
       </x:c>
       <x:c r="O16"/>
     </x:row>
     <x:row r="17" ht="17">
       <x:c r="B17" s="1" t="s">
-        <x:v>110</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="C17" s="1" t="s">
-        <x:v>110</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="D17" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="E17" s="1">
         <x:v>3</x:v>
@@ -2428,37 +2368,37 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="H17" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="I17" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="J17" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="K17" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="L17" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="M17" s="4" t="s">
-        <x:v>66</x:v>
-      </x:c>
-      <x:c r="N17" s="4" t="s">
-        <x:v>67</x:v>
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="N17" s="4" t="str">
+        <x:v>从 {choiceCount} 个食物中选择 {requiredPickCount} 个加入食谱</x:v>
       </x:c>
       <x:c r="O17"/>
     </x:row>
     <x:row r="18" ht="17">
       <x:c r="B18" s="1" t="s">
-        <x:v>111</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="C18" s="1" t="s">
-        <x:v>111</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="D18" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="E18" s="1">
         <x:v>1</x:v>
@@ -2470,37 +2410,37 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="H18" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="I18" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="J18" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="K18" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="L18" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="M18" s="4" t="s">
-        <x:v>66</x:v>
-      </x:c>
-      <x:c r="N18" s="4" t="s">
-        <x:v>112</x:v>
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="N18" s="4" t="str">
+        <x:v>随机获得 {requiredPickCount} 个食物</x:v>
       </x:c>
       <x:c r="O18"/>
     </x:row>
     <x:row r="19" ht="17">
       <x:c r="B19" s="1" t="s">
-        <x:v>113</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="C19" s="1" t="s">
-        <x:v>113</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="D19" s="1" t="s">
-        <x:v>80</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="E19" s="1">
         <x:v>1</x:v>
@@ -2512,37 +2452,37 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="H19" s="1" t="s">
-        <x:v>81</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="I19" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="J19" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="K19" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="L19" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="M19" s="4" t="s">
-        <x:v>83</x:v>
-      </x:c>
-      <x:c r="N19" s="4" t="s">
-        <x:v>114</x:v>
+        <x:v>78</x:v>
+      </x:c>
+      <x:c r="N19" s="4" t="str">
+        <x:v>随机获得 {requiredPickCount} 个[term]装饰品[/term]</x:v>
       </x:c>
       <x:c r="O19"/>
     </x:row>
     <x:row r="20" ht="17">
       <x:c r="B20" s="1" t="s">
-        <x:v>115</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="C20" s="1" t="s">
-        <x:v>115</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="D20" s="1" t="s">
-        <x:v>80</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="E20" s="1">
         <x:v>3</x:v>
@@ -2554,37 +2494,37 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="H20" s="1" t="s">
-        <x:v>81</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="I20" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="J20" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="K20" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="L20" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="M20" s="4" t="s">
-        <x:v>83</x:v>
-      </x:c>
-      <x:c r="N20" s="4" t="s">
-        <x:v>84</x:v>
+        <x:v>78</x:v>
+      </x:c>
+      <x:c r="N20" s="4" t="str">
+        <x:v>从 {choiceCount} 个[term]装饰品[/term]中选择 {requiredPickCount} 个</x:v>
       </x:c>
       <x:c r="O20"/>
     </x:row>
     <x:row r="21" ht="17">
       <x:c r="B21" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="C21" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="D21" s="1" t="s">
-        <x:v>80</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="E21" s="1">
         <x:v>2</x:v>
@@ -2596,37 +2536,37 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="H21" s="1" t="s">
-        <x:v>81</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="I21" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="J21" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="K21" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="L21" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="M21" s="4" t="s">
-        <x:v>83</x:v>
-      </x:c>
-      <x:c r="N21" s="4" t="s">
-        <x:v>117</x:v>
+        <x:v>78</x:v>
+      </x:c>
+      <x:c r="N21" s="4" t="str">
+        <x:v>获得全部 {choiceCount} 个[term]装饰品[/term]</x:v>
       </x:c>
       <x:c r="O21"/>
     </x:row>
     <x:row r="22" ht="17">
       <x:c r="B22" s="1" t="s">
-        <x:v>118</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="C22" s="1" t="s">
-        <x:v>118</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="D22" s="1" t="s">
-        <x:v>119</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="E22" s="1">
         <x:v>1</x:v>
@@ -2638,37 +2578,37 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="H22" s="1" t="s">
-        <x:v>120</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="I22" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="J22" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="K22" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="L22" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="M22" s="4" t="s">
-        <x:v>121</x:v>
-      </x:c>
-      <x:c r="N22" s="4" t="s">
-        <x:v>122</x:v>
+        <x:v>110</x:v>
+      </x:c>
+      <x:c r="N22" s="4" t="str">
+        <x:v>随机获得 {requiredPickCount} 个[term]消耗品[/term]</x:v>
       </x:c>
       <x:c r="O22"/>
     </x:row>
     <x:row r="23" ht="17">
       <x:c r="B23" s="1" t="s">
-        <x:v>123</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="C23" s="1" t="s">
-        <x:v>123</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="D23" s="1" t="s">
-        <x:v>119</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="E23" s="1">
         <x:v>2</x:v>
@@ -2680,37 +2620,37 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="H23" s="1" t="s">
-        <x:v>120</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="I23" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="J23" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="K23" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="L23" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="M23" s="4" t="s">
-        <x:v>121</x:v>
-      </x:c>
-      <x:c r="N23" s="4" t="s">
-        <x:v>124</x:v>
+        <x:v>110</x:v>
+      </x:c>
+      <x:c r="N23" s="4" t="str">
+        <x:v>获得全部 {choiceCount} 个[term]消耗品[/term]</x:v>
       </x:c>
       <x:c r="O23"/>
     </x:row>
     <x:row r="24" ht="17">
       <x:c r="B24" s="1" t="s">
-        <x:v>125</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="C24" s="1" t="s">
-        <x:v>125</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="D24" s="1" t="s">
-        <x:v>119</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="E24" s="1">
         <x:v>3</x:v>
@@ -2722,37 +2662,37 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="H24" s="1" t="s">
-        <x:v>120</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="I24" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="J24" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="K24" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="L24" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="M24" s="4" t="s">
-        <x:v>126</x:v>
-      </x:c>
-      <x:c r="N24" s="4" t="s">
-        <x:v>127</x:v>
+        <x:v>113</x:v>
+      </x:c>
+      <x:c r="N24" s="4" t="str">
+        <x:v>从 {choiceCount} 个[term]消耗品[/term]中选择 {requiredPickCount} 个</x:v>
       </x:c>
       <x:c r="O24"/>
     </x:row>
     <x:row r="25" ht="17">
       <x:c r="B25" s="1" t="s">
-        <x:v>128</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="C25" s="1" t="s">
-        <x:v>128</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="D25" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="E25" s="1">
         <x:v>3</x:v>
@@ -2764,37 +2704,37 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="H25" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="I25" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="J25" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="K25" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="L25" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="M25" s="4" t="s">
-        <x:v>77</x:v>
-      </x:c>
-      <x:c r="N25" s="4" t="s">
-        <x:v>129</x:v>
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="N25" s="4" t="str">
+        <x:v>从 {choiceCount} 个餐桌格中选择 {requiredPickCount} 个</x:v>
       </x:c>
       <x:c r="O25"/>
     </x:row>
     <x:row r="26" ht="17">
       <x:c r="B26" s="1" t="s">
-        <x:v>130</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="C26" s="1" t="s">
-        <x:v>130</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="D26" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="E26" s="1">
         <x:v>3</x:v>
@@ -2806,37 +2746,37 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="H26" s="1" t="s">
-        <x:v>131</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="I26" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="J26" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="K26" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="L26" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="M26" s="4" t="s">
-        <x:v>132</x:v>
-      </x:c>
-      <x:c r="N26" s="4" t="s">
-        <x:v>133</x:v>
+        <x:v>117</x:v>
+      </x:c>
+      <x:c r="N26" s="4" t="str">
+        <x:v>获得全部 {choiceCount} 个风味食物</x:v>
       </x:c>
       <x:c r="O26"/>
     </x:row>
     <x:row r="27" ht="17">
       <x:c r="B27" s="1" t="s">
-        <x:v>134</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="C27" s="1" t="s">
-        <x:v>134</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="D27" s="1" t="s">
-        <x:v>80</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="E27" s="1">
         <x:v>1</x:v>
@@ -2848,37 +2788,37 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="H27" s="1" t="s">
-        <x:v>135</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="I27" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="J27" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="K27" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="L27" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="M27" s="4" t="s">
-        <x:v>136</x:v>
-      </x:c>
-      <x:c r="N27" s="4" t="s">
-        <x:v>137</x:v>
+        <x:v>120</x:v>
+      </x:c>
+      <x:c r="N27" s="4" t="str">
+        <x:v>随机获得 {requiredPickCount} 个传说[term]装饰品[/term]</x:v>
       </x:c>
       <x:c r="O27"/>
     </x:row>
     <x:row r="28" ht="17">
       <x:c r="B28" s="1" t="s">
-        <x:v>138</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="C28" s="1" t="s">
-        <x:v>138</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="D28" s="1" t="s">
-        <x:v>119</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="E28" s="1">
         <x:v>1</x:v>
@@ -2890,37 +2830,37 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="H28" s="1" t="s">
-        <x:v>139</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="I28" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="J28" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="K28" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="L28" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="M28" s="4" t="s">
-        <x:v>140</x:v>
-      </x:c>
-      <x:c r="N28" s="4" t="s">
-        <x:v>141</x:v>
+        <x:v>123</x:v>
+      </x:c>
+      <x:c r="N28" s="4" t="str">
+        <x:v>随机获得 {requiredPickCount} 个木质强化箱</x:v>
       </x:c>
       <x:c r="O28"/>
     </x:row>
     <x:row r="29" ht="17">
       <x:c r="B29" s="1" t="s">
-        <x:v>142</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="C29" s="1" t="s">
-        <x:v>142</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="D29" s="1" t="s">
-        <x:v>119</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="E29" s="1">
         <x:v>1</x:v>
@@ -2932,37 +2872,37 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="H29" s="1" t="s">
-        <x:v>143</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="I29" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="J29" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="K29" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="L29" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="M29" s="4" t="s">
-        <x:v>144</x:v>
-      </x:c>
-      <x:c r="N29" s="4" t="s">
-        <x:v>145</x:v>
+        <x:v>126</x:v>
+      </x:c>
+      <x:c r="N29" s="4" t="str">
+        <x:v>随机获得 {requiredPickCount} 个石质强化箱</x:v>
       </x:c>
       <x:c r="O29"/>
     </x:row>
     <x:row r="30" ht="17">
       <x:c r="B30" s="1" t="s">
-        <x:v>146</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="C30" s="1" t="s">
-        <x:v>146</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="D30" s="1" t="s">
-        <x:v>119</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="E30" s="1">
         <x:v>1</x:v>
@@ -2974,37 +2914,37 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="H30" s="1" t="s">
-        <x:v>147</x:v>
+        <x:v>128</x:v>
       </x:c>
       <x:c r="I30" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="J30" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="K30" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="L30" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="M30" s="4" t="s">
-        <x:v>148</x:v>
-      </x:c>
-      <x:c r="N30" s="4" t="s">
-        <x:v>149</x:v>
+        <x:v>129</x:v>
+      </x:c>
+      <x:c r="N30" s="4" t="str">
+        <x:v>随机获得 {requiredPickCount} 个金属强化箱</x:v>
       </x:c>
       <x:c r="O30"/>
     </x:row>
     <x:row r="31" ht="17">
       <x:c r="B31" s="1" t="s">
-        <x:v>150</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="C31" s="1" t="s">
-        <x:v>151</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="D31" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="E31" s="1">
         <x:v>1</x:v>
@@ -3016,34 +2956,34 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="I31" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="J31" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="K31" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="L31" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="M31" s="4" t="s">
-        <x:v>71</x:v>
-      </x:c>
-      <x:c r="N31" s="4" t="s">
-        <x:v>72</x:v>
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="N31" s="4" t="str">
+        <x:v>[gold]金币+ {requiredPickCount}[/gold]</x:v>
       </x:c>
       <x:c r="O31"/>
     </x:row>
     <x:row r="32" ht="17">
       <x:c r="B32" s="1" t="s">
-        <x:v>152</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="C32" s="1" t="s">
-        <x:v>151</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="D32" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="E32" s="1">
         <x:v>3</x:v>
@@ -3055,37 +2995,37 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="H32" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="I32" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="J32" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="K32" s="1" t="s">
-        <x:v>153</x:v>
+        <x:v>133</x:v>
       </x:c>
       <x:c r="L32" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="M32" s="4" t="s">
-        <x:v>77</x:v>
-      </x:c>
-      <x:c r="N32" s="4" t="s">
-        <x:v>78</x:v>
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="N32" s="4" t="str">
+        <x:v>从 {choiceCount} 个餐桌格中选择 {requiredPickCount} 个拼入餐桌</x:v>
       </x:c>
       <x:c r="O32"/>
     </x:row>
     <x:row r="33" ht="17">
       <x:c r="B33" s="1" t="s">
-        <x:v>154</x:v>
+        <x:v>134</x:v>
       </x:c>
       <x:c r="C33" s="1" t="s">
-        <x:v>151</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="D33" s="1" t="s">
-        <x:v>119</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="E33" s="1">
         <x:v>1</x:v>
@@ -3097,37 +3037,37 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="H33" s="1" t="s">
-        <x:v>120</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="I33" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="J33" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="K33" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="L33" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="M33" s="4" t="s">
-        <x:v>121</x:v>
-      </x:c>
-      <x:c r="N33" s="4" t="s">
-        <x:v>122</x:v>
+        <x:v>110</x:v>
+      </x:c>
+      <x:c r="N33" s="4" t="str">
+        <x:v>随机获得 {requiredPickCount} 个[term]消耗品[/term]</x:v>
       </x:c>
       <x:c r="O33"/>
     </x:row>
     <x:row r="34" ht="17">
       <x:c r="B34" s="1" t="s">
-        <x:v>155</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="C34" s="1" t="s">
-        <x:v>151</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="D34" s="1" t="s">
-        <x:v>80</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="E34" s="1">
         <x:v>2</x:v>
@@ -3139,25 +3079,25 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="H34" s="1" t="s">
-        <x:v>81</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="I34" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="J34" s="1" t="s">
-        <x:v>82</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="K34" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="L34" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="M34" s="4" t="s">
-        <x:v>83</x:v>
-      </x:c>
-      <x:c r="N34" s="4" t="s">
-        <x:v>84</x:v>
+        <x:v>78</x:v>
+      </x:c>
+      <x:c r="N34" s="4" t="str">
+        <x:v>从 {choiceCount} 个[term]装饰品[/term]中选择 {requiredPickCount} 个</x:v>
       </x:c>
       <x:c r="O34"/>
     </x:row>
@@ -3235,10 +3175,10 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="D1" s="1" t="s">
-        <x:v>156</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="E1" s="1" t="s">
-        <x:v>157</x:v>
+        <x:v>137</x:v>
       </x:c>
     </x:row>
     <x:row r="2">
@@ -3246,16 +3186,16 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
-        <x:v>158</x:v>
+        <x:v>138</x:v>
       </x:c>
       <x:c r="C2" s="1" t="s">
-        <x:v>159</x:v>
+        <x:v>139</x:v>
       </x:c>
       <x:c r="D2" s="1" t="s">
-        <x:v>160</x:v>
+        <x:v>140</x:v>
       </x:c>
       <x:c r="E2" s="1" t="s">
-        <x:v>161</x:v>
+        <x:v>141</x:v>
       </x:c>
     </x:row>
     <x:row r="3">
@@ -3266,21 +3206,21 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="C3" s="1" t="s">
-        <x:v>162</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="D3" s="1" t="s">
-        <x:v>163</x:v>
+        <x:v>143</x:v>
       </x:c>
       <x:c r="E3" s="1" t="s">
-        <x:v>164</x:v>
+        <x:v>144</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
       <x:c r="B4" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="C4" s="1" t="s">
-        <x:v>165</x:v>
+        <x:v>145</x:v>
       </x:c>
       <x:c r="D4" s="1" t="b">
         <x:v>1</x:v>
@@ -3288,10 +3228,10 @@
     </x:row>
     <x:row r="5">
       <x:c r="B5" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="C5" s="1" t="s">
-        <x:v>166</x:v>
+        <x:v>146</x:v>
       </x:c>
       <x:c r="D5" s="1" t="b">
         <x:v>1</x:v>
@@ -3299,10 +3239,10 @@
     </x:row>
     <x:row r="6">
       <x:c r="B6" s="1" t="s">
-        <x:v>81</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="C6" s="1" t="s">
-        <x:v>167</x:v>
+        <x:v>147</x:v>
       </x:c>
       <x:c r="D6" s="1" t="b">
         <x:v>1</x:v>
@@ -3310,38 +3250,38 @@
     </x:row>
     <x:row r="7">
       <x:c r="B7" s="1" t="s">
-        <x:v>103</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="C7" s="1" t="s">
-        <x:v>167</x:v>
+        <x:v>147</x:v>
       </x:c>
       <x:c r="D7" s="1" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="E7" s="1" t="s">
-        <x:v>168</x:v>
+        <x:v>148</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="409.5">
       <x:c r="B8" s="2" t="s">
-        <x:v>87</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="C8" s="2" t="s">
-        <x:v>169</x:v>
+        <x:v>149</x:v>
       </x:c>
       <x:c r="D8" s="1" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="E8" s="1" t="s">
-        <x:v>170</x:v>
+        <x:v>150</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
       <x:c r="B9" s="2" t="s">
-        <x:v>92</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="C9" s="2" t="s">
-        <x:v>91</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="D9" s="1" t="b">
         <x:v>1</x:v>
@@ -3349,10 +3289,10 @@
     </x:row>
     <x:row r="10">
       <x:c r="B10" s="1" t="s">
-        <x:v>131</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="C10" s="1" t="s">
-        <x:v>165</x:v>
+        <x:v>145</x:v>
       </x:c>
       <x:c r="D10" s="1" t="b">
         <x:v>1</x:v>
@@ -3360,10 +3300,10 @@
     </x:row>
     <x:row r="11">
       <x:c r="B11" s="1" t="s">
-        <x:v>135</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="C11" s="1" t="s">
-        <x:v>167</x:v>
+        <x:v>147</x:v>
       </x:c>
       <x:c r="D11" s="1" t="b">
         <x:v>1</x:v>
@@ -3371,53 +3311,53 @@
     </x:row>
     <x:row r="12">
       <x:c r="B12" s="1" t="s">
-        <x:v>139</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="C12" s="1" t="s">
-        <x:v>171</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="D12" s="1" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="E12" t="s">
-        <x:v>172</x:v>
+        <x:v>152</x:v>
       </x:c>
     </x:row>
     <x:row r="13">
       <x:c r="B13" s="1" t="s">
-        <x:v>143</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="C13" s="1" t="s">
-        <x:v>171</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="D13" s="1" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="E13" t="s">
-        <x:v>173</x:v>
+        <x:v>153</x:v>
       </x:c>
     </x:row>
     <x:row r="14">
       <x:c r="B14" s="1" t="s">
-        <x:v>147</x:v>
+        <x:v>128</x:v>
       </x:c>
       <x:c r="C14" s="1" t="s">
-        <x:v>171</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="D14" s="1" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="E14" t="s">
-        <x:v>174</x:v>
+        <x:v>154</x:v>
       </x:c>
     </x:row>
     <x:row r="15">
       <x:c r="A15"/>
       <x:c r="B15" t="s">
-        <x:v>120</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="C15" t="s">
-        <x:v>171</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="D15" t="b">
         <x:v>1</x:v>

--- a/GourmetProject/GameConfig/Datas/reward.xlsx
+++ b/GourmetProject/GameConfig/Datas/reward.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="412" uniqueCount="165">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="412" uniqueCount="164">
   <si>
     <t>##var</t>
   </si>
@@ -318,7 +318,7 @@
     <t>boss_dish</t>
   </si>
   <si>
-    <t>10,0</t>
+    <t>4,0</t>
   </si>
   <si>
     <t>slot_boss_passive</t>
@@ -328,9 +328,6 @@
   </si>
   <si>
     <t>pool_passive_boss</t>
-  </si>
-  <si>
-    <t>7,0</t>
   </si>
   <si>
     <t>slot_boss_fragment</t>
@@ -1102,15 +1099,12 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1844,10 +1838,10 @@
       <c r="L1" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="M1" s="4" t="s">
+      <c r="M1" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="N1" s="4" t="s">
+      <c r="N1" s="3" t="s">
         <v>43</v>
       </c>
     </row>
@@ -1888,10 +1882,10 @@
       <c r="L2" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="M2" s="4" t="s">
+      <c r="M2" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="N2" s="4" t="s">
+      <c r="N2" s="3" t="s">
         <v>56</v>
       </c>
     </row>
@@ -1932,10 +1926,10 @@
       <c r="L3" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="M3" s="4" t="s">
+      <c r="M3" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="N3" s="4" t="s">
+      <c r="N3" s="3" t="s">
         <v>9</v>
       </c>
     </row>
@@ -1973,10 +1967,10 @@
       <c r="L4" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="M4" s="4" t="s">
+      <c r="M4" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="N4" s="4" t="s">
+      <c r="N4" s="3" t="s">
         <v>67</v>
       </c>
     </row>
@@ -2011,10 +2005,10 @@
       <c r="L5" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="M5" s="4" t="s">
+      <c r="M5" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="N5" s="4" t="s">
+      <c r="N5" s="3" t="s">
         <v>72</v>
       </c>
     </row>
@@ -2052,10 +2046,10 @@
       <c r="L6" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="M6" s="4" t="s">
+      <c r="M6" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="N6" s="4" t="s">
+      <c r="N6" s="3" t="s">
         <v>78</v>
       </c>
     </row>
@@ -2093,10 +2087,10 @@
       <c r="L7" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="M7" s="4" t="s">
+      <c r="M7" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="N7" s="4" t="s">
+      <c r="N7" s="3" t="s">
         <v>84</v>
       </c>
     </row>
@@ -2134,10 +2128,10 @@
       <c r="L8" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="M8" s="4" t="s">
+      <c r="M8" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="N8" s="4" t="s">
+      <c r="N8" s="3" t="s">
         <v>89</v>
       </c>
     </row>
@@ -2175,10 +2169,10 @@
       <c r="L9" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="M9" s="4" t="s">
+      <c r="M9" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="N9" s="4" t="s">
+      <c r="N9" s="3" t="s">
         <v>94</v>
       </c>
     </row>
@@ -2216,10 +2210,10 @@
       <c r="L10" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="M10" s="4" t="s">
+      <c r="M10" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="N10" s="4" t="s">
+      <c r="N10" s="3" t="s">
         <v>84</v>
       </c>
     </row>
@@ -2257,10 +2251,10 @@
       <c r="L11" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="M11" s="4" t="s">
+      <c r="M11" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="N11" s="4" t="s">
+      <c r="N11" s="3" t="s">
         <v>89</v>
       </c>
     </row>
@@ -2298,10 +2292,10 @@
       <c r="L12" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="M12" s="4" t="s">
+      <c r="M12" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="N12" s="4" t="s">
+      <c r="N12" s="3" t="s">
         <v>94</v>
       </c>
     </row>
@@ -2339,10 +2333,10 @@
       <c r="L13" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="M13" s="4" t="s">
+      <c r="M13" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="N13" s="4" t="s">
+      <c r="N13" s="3" t="s">
         <v>67</v>
       </c>
     </row>
@@ -2372,7 +2366,7 @@
         <v>65</v>
       </c>
       <c r="J14" s="1" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="K14" s="1" t="s">
         <v>65</v>
@@ -2380,19 +2374,19 @@
       <c r="L14" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="M14" s="4" t="s">
+      <c r="M14" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="N14" s="4" t="s">
+      <c r="N14" s="3" t="s">
         <v>84</v>
       </c>
     </row>
     <row r="15" s="1" customFormat="1" ht="17" customHeight="1" spans="2:14">
       <c r="B15" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="C15" s="1" t="s">
         <v>105</v>
-      </c>
-      <c r="C15" s="1" t="s">
-        <v>106</v>
       </c>
       <c r="D15" s="1" t="s">
         <v>74</v>
@@ -2416,24 +2410,24 @@
         <v>65</v>
       </c>
       <c r="K15" s="1" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="L15" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="M15" s="4" t="s">
+      <c r="M15" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="N15" s="4" t="s">
+      <c r="N15" s="3" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="16" s="1" customFormat="1" ht="17" customHeight="1" spans="2:14">
       <c r="B16" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="C16" s="1" t="s">
         <v>107</v>
-      </c>
-      <c r="C16" s="1" t="s">
-        <v>108</v>
       </c>
       <c r="D16" s="1" t="s">
         <v>69</v>
@@ -2457,21 +2451,21 @@
         <v>65</v>
       </c>
       <c r="L16" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="M16" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="M16" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="N16" s="4" t="s">
+      <c r="N16" s="3" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="17" ht="17" customHeight="1" spans="2:14">
       <c r="B17" s="1" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D17" s="1" t="s">
         <v>62</v>
@@ -2500,19 +2494,19 @@
       <c r="L17" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="M17" s="4" t="s">
+      <c r="M17" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="N17" s="4" t="s">
+      <c r="N17" s="3" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="18" ht="17" customHeight="1" spans="2:14">
       <c r="B18" s="1" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D18" s="1" t="s">
         <v>62</v>
@@ -2541,19 +2535,19 @@
       <c r="L18" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="M18" s="4" t="s">
+      <c r="M18" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="N18" s="4" t="s">
-        <v>112</v>
+      <c r="N18" s="3" t="s">
+        <v>111</v>
       </c>
     </row>
     <row r="19" ht="17" customHeight="1" spans="2:14">
       <c r="B19" s="1" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D19" s="1" t="s">
         <v>80</v>
@@ -2582,19 +2576,19 @@
       <c r="L19" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="M19" s="4" t="s">
+      <c r="M19" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="N19" s="4" t="s">
-        <v>114</v>
+      <c r="N19" s="3" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="20" ht="17" customHeight="1" spans="2:14">
       <c r="B20" s="1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D20" s="1" t="s">
         <v>80</v>
@@ -2623,19 +2617,19 @@
       <c r="L20" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="M20" s="4" t="s">
+      <c r="M20" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="N20" s="4" t="s">
+      <c r="N20" s="3" t="s">
         <v>84</v>
       </c>
     </row>
     <row r="21" ht="17" customHeight="1" spans="2:14">
       <c r="B21" s="1" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D21" s="1" t="s">
         <v>80</v>
@@ -2664,63 +2658,63 @@
       <c r="L21" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="M21" s="4" t="s">
+      <c r="M21" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="N21" s="4" t="s">
-        <v>117</v>
+      <c r="N21" s="3" t="s">
+        <v>116</v>
       </c>
     </row>
     <row r="22" ht="17" customHeight="1" spans="2:14">
       <c r="B22" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="D22" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="C22" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="D22" s="1" t="s">
+      <c r="E22" s="1">
+        <v>1</v>
+      </c>
+      <c r="F22" s="1">
+        <v>1</v>
+      </c>
+      <c r="G22" s="1">
+        <v>1</v>
+      </c>
+      <c r="H22" s="1" t="s">
         <v>119</v>
       </c>
-      <c r="E22" s="1">
-        <v>1</v>
-      </c>
-      <c r="F22" s="1">
-        <v>1</v>
-      </c>
-      <c r="G22" s="1">
-        <v>1</v>
-      </c>
-      <c r="H22" s="1" t="s">
+      <c r="I22" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="J22" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="K22" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="L22" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="M22" s="3" t="s">
         <v>120</v>
       </c>
-      <c r="I22" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="J22" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="K22" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="L22" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="M22" s="4" t="s">
+      <c r="N22" s="3" t="s">
         <v>121</v>
-      </c>
-      <c r="N22" s="4" t="s">
-        <v>122</v>
       </c>
     </row>
     <row r="23" ht="17" customHeight="1" spans="2:14">
       <c r="B23" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E23" s="1">
         <v>2</v>
@@ -2732,36 +2726,36 @@
         <v>1</v>
       </c>
       <c r="H23" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="I23" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="J23" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="K23" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="L23" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="M23" s="3" t="s">
         <v>120</v>
       </c>
-      <c r="I23" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="J23" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="K23" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="L23" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="M23" s="4" t="s">
-        <v>121</v>
-      </c>
-      <c r="N23" s="4" t="s">
-        <v>124</v>
+      <c r="N23" s="3" t="s">
+        <v>123</v>
       </c>
     </row>
     <row r="24" ht="17" customHeight="1" spans="2:14">
       <c r="B24" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E24" s="1">
         <v>3</v>
@@ -2773,7 +2767,7 @@
         <v>1</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="I24" s="1" t="s">
         <v>65</v>
@@ -2787,19 +2781,19 @@
       <c r="L24" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="M24" s="4" t="s">
+      <c r="M24" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="N24" s="3" t="s">
         <v>126</v>
-      </c>
-      <c r="N24" s="4" t="s">
-        <v>127</v>
       </c>
     </row>
     <row r="25" ht="17" customHeight="1" spans="2:14">
       <c r="B25" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D25" s="1" t="s">
         <v>74</v>
@@ -2828,19 +2822,19 @@
       <c r="L25" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="M25" s="4" t="s">
+      <c r="M25" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="N25" s="4" t="s">
-        <v>129</v>
+      <c r="N25" s="3" t="s">
+        <v>128</v>
       </c>
     </row>
     <row r="26" ht="17" customHeight="1" spans="2:14">
       <c r="B26" s="1" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D26" s="1" t="s">
         <v>62</v>
@@ -2855,33 +2849,33 @@
         <v>1</v>
       </c>
       <c r="H26" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="I26" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="J26" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="K26" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="L26" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="M26" s="3" t="s">
         <v>131</v>
       </c>
-      <c r="I26" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="J26" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="K26" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="L26" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="M26" s="4" t="s">
+      <c r="N26" s="3" t="s">
         <v>132</v>
-      </c>
-      <c r="N26" s="4" t="s">
-        <v>133</v>
       </c>
     </row>
     <row r="27" ht="17" customHeight="1" spans="2:14">
       <c r="B27" s="1" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="D27" s="1" t="s">
         <v>80</v>
@@ -2896,33 +2890,33 @@
         <v>1</v>
       </c>
       <c r="H27" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="I27" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="J27" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="K27" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="L27" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="M27" s="3" t="s">
         <v>135</v>
       </c>
-      <c r="I27" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="J27" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="K27" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="L27" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="M27" s="4" t="s">
+      <c r="N27" s="3" t="s">
         <v>136</v>
-      </c>
-      <c r="N27" s="4" t="s">
-        <v>137</v>
       </c>
     </row>
     <row r="28" ht="17" customHeight="1" spans="2:14">
       <c r="B28" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="C28" s="1" t="s">
         <v>138</v>
-      </c>
-      <c r="C28" s="1" t="s">
-        <v>139</v>
       </c>
       <c r="D28" s="1" t="s">
         <v>69</v>
@@ -2948,19 +2942,19 @@
       <c r="L28" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="M28" s="4" t="s">
+      <c r="M28" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="N28" s="4" t="s">
+      <c r="N28" s="3" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="29" ht="17" customHeight="1" spans="2:14">
       <c r="B29" s="1" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="D29" s="1" t="s">
         <v>74</v>
@@ -2984,27 +2978,27 @@
         <v>65</v>
       </c>
       <c r="K29" s="1" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="L29" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="M29" s="4" t="s">
+      <c r="M29" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="N29" s="4" t="s">
+      <c r="N29" s="3" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="30" ht="17" customHeight="1" spans="2:14">
       <c r="B30" s="1" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E30" s="1">
         <v>1</v>
@@ -3016,33 +3010,33 @@
         <v>5</v>
       </c>
       <c r="H30" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="I30" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="J30" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="K30" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="L30" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="M30" s="3" t="s">
         <v>120</v>
       </c>
-      <c r="I30" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="J30" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="K30" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="L30" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="M30" s="4" t="s">
+      <c r="N30" s="3" t="s">
         <v>121</v>
-      </c>
-      <c r="N30" s="4" t="s">
-        <v>122</v>
       </c>
     </row>
     <row r="31" ht="17" customHeight="1" spans="2:14">
       <c r="B31" s="1" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="D31" s="1" t="s">
         <v>80</v>
@@ -3063,60 +3057,60 @@
         <v>65</v>
       </c>
       <c r="J31" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="K31" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="L31" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="M31" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="N31" s="3" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="32" ht="17" customHeight="1" spans="2:14">
+      <c r="B32" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="K31" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="L31" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="M31" s="4" t="s">
-        <v>83</v>
-      </c>
-      <c r="N31" s="4" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="32" ht="17" customHeight="1" spans="2:14">
-      <c r="B32" s="3" t="s">
-        <v>145</v>
-      </c>
-      <c r="C32" s="3" t="s">
-        <v>145</v>
-      </c>
-      <c r="D32" s="3" t="s">
+      <c r="C32" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="D32" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="E32" s="3">
+      <c r="E32" s="1">
         <v>2</v>
       </c>
-      <c r="F32" s="3">
+      <c r="F32" s="1">
         <v>2</v>
       </c>
-      <c r="G32" s="3">
-        <v>1</v>
-      </c>
-      <c r="H32" s="3" t="s">
+      <c r="G32" s="1">
+        <v>1</v>
+      </c>
+      <c r="H32" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="I32" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="J32" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="K32" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="L32" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="M32" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="I32" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="J32" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="K32" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="L32" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="M32" s="3" t="s">
+      <c r="N32" s="1" t="s">
         <v>132</v>
-      </c>
-      <c r="N32" s="3" t="s">
-        <v>133</v>
       </c>
     </row>
     <row r="33" ht="17" customHeight="1"/>
@@ -3156,13 +3150,13 @@
         <v>33</v>
       </c>
       <c r="D1" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>146</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" t="s">
         <v>147</v>
-      </c>
-      <c r="F1" t="s">
-        <v>148</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -3170,19 +3164,19 @@
         <v>4</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="C2" s="1" t="s">
         <v>149</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="D2" s="1" t="s">
         <v>150</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="E2" s="1" t="s">
         <v>151</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="F2" t="s">
         <v>152</v>
-      </c>
-      <c r="F2" t="s">
-        <v>153</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -3193,16 +3187,16 @@
         <v>9</v>
       </c>
       <c r="C3" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="D3" s="1" t="s">
         <v>154</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="E3" s="1" t="s">
         <v>155</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="F3" t="s">
         <v>156</v>
-      </c>
-      <c r="F3" t="s">
-        <v>157</v>
       </c>
     </row>
     <row r="4" spans="2:4">
@@ -3210,7 +3204,7 @@
         <v>63</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="D4" s="1" t="b">
         <v>1</v>
@@ -3221,7 +3215,7 @@
         <v>75</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="D5" s="1" t="b">
         <v>1</v>
@@ -3232,7 +3226,7 @@
         <v>81</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="D6" s="1" t="b">
         <v>1</v>
@@ -3243,13 +3237,13 @@
         <v>103</v>
       </c>
       <c r="C7" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="D7" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="E7" s="1" t="s">
         <v>160</v>
-      </c>
-      <c r="D7" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>161</v>
       </c>
     </row>
     <row r="8" ht="409.5" customHeight="1" spans="2:5">
@@ -3263,7 +3257,7 @@
         <v>1</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="9" spans="2:4">
@@ -3279,10 +3273,10 @@
     </row>
     <row r="10" spans="2:4">
       <c r="B10" s="1" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="D10" s="1" t="b">
         <v>1</v>
@@ -3290,24 +3284,24 @@
     </row>
     <row r="11" spans="2:6">
       <c r="B11" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="D11" s="1" t="b">
         <v>1</v>
       </c>
       <c r="F11" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
     <row r="12" spans="2:4">
       <c r="B12" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C12" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="D12" t="b">
         <v>1</v>

--- a/GourmetProject/GameConfig/Datas/reward.xlsx
+++ b/GourmetProject/GameConfig/Datas/reward.xlsx
@@ -228,7 +228,7 @@
     <t>Gold</t>
   </si>
   <si>
-    <t>10,30</t>
+    <t>0,20</t>
   </si>
   <si>
     <t>金币</t>

--- a/GourmetProject/GameConfig/Datas/reward.xlsx
+++ b/GourmetProject/GameConfig/Datas/reward.xlsx
@@ -2928,7 +2928,7 @@
         <v>1</v>
       </c>
       <c r="G28" s="1">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="I28" s="1" t="s">
         <v>65</v>
@@ -2966,7 +2966,7 @@
         <v>1</v>
       </c>
       <c r="G29" s="1">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="H29" s="1" t="s">
         <v>75</v>
@@ -3007,7 +3007,7 @@
         <v>1</v>
       </c>
       <c r="G30" s="1">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="H30" s="1" t="s">
         <v>119</v>
@@ -3048,7 +3048,7 @@
         <v>1</v>
       </c>
       <c r="G31" s="1">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="H31" s="1" t="s">
         <v>81</v>

--- a/GourmetProject/GameConfig/Datas/reward.xlsx
+++ b/GourmetProject/GameConfig/Datas/reward.xlsx
@@ -228,211 +228,211 @@
     <t>Gold</t>
   </si>
   <si>
+    <t>0,10</t>
+  </si>
+  <si>
+    <t>金币</t>
+  </si>
+  <si>
+    <t>[gold]金币+ {requiredPickCount}[/gold]</t>
+  </si>
+  <si>
+    <t>slot_specific_fragment</t>
+  </si>
+  <si>
+    <t>FragmentChoice</t>
+  </si>
+  <si>
+    <t>pool_fragment</t>
+  </si>
+  <si>
+    <t>餐桌格</t>
+  </si>
+  <si>
+    <t>从 {choiceCount} 个餐桌格中选择 {requiredPickCount} 个拼入餐桌</t>
+  </si>
+  <si>
+    <t>slot_specific_passive</t>
+  </si>
+  <si>
+    <t>PassiveItemChoice</t>
+  </si>
+  <si>
+    <t>pool_passive</t>
+  </si>
+  <si>
+    <t>1,4</t>
+  </si>
+  <si>
+    <t>装饰品</t>
+  </si>
+  <si>
+    <t>从 {choiceCount} 个[term]装饰品[/term]中选择 {requiredPickCount} 个</t>
+  </si>
+  <si>
+    <t>slot_specific_active_strengthen</t>
+  </si>
+  <si>
+    <t>ActiveItemStrengthen</t>
+  </si>
+  <si>
+    <t>pool_active_strengthen</t>
+  </si>
+  <si>
+    <t>强化箱</t>
+  </si>
+  <si>
+    <t>从 {choiceCount} 个强化箱中选择 {requiredPickCount} 个</t>
+  </si>
+  <si>
+    <t>slot_specific_active_adjust</t>
+  </si>
+  <si>
+    <t>ActiveItemAdjust</t>
+  </si>
+  <si>
+    <t>pool_active_adjust</t>
+  </si>
+  <si>
+    <t>调整单</t>
+  </si>
+  <si>
+    <t>从 {choiceCount} 个调整单中选择 {requiredPickCount} 个</t>
+  </si>
+  <si>
+    <t>slot_specific_hard_passive</t>
+  </si>
+  <si>
+    <t>slot_specific_hard_active_strengthen</t>
+  </si>
+  <si>
+    <t>slot_specific_hard_active_adjust</t>
+  </si>
+  <si>
+    <t>slot_boss_dish</t>
+  </si>
+  <si>
+    <t>boss_dish</t>
+  </si>
+  <si>
+    <t>4,0</t>
+  </si>
+  <si>
+    <t>slot_boss_passive</t>
+  </si>
+  <si>
+    <t>boss_passive</t>
+  </si>
+  <si>
+    <t>pool_passive_boss</t>
+  </si>
+  <si>
+    <t>slot_boss_fragment</t>
+  </si>
+  <si>
+    <t>boss_fragment</t>
+  </si>
+  <si>
+    <t>slot_boss_gold</t>
+  </si>
+  <si>
+    <t>boss_gold</t>
+  </si>
+  <si>
+    <t>25,0</t>
+  </si>
+  <si>
+    <t>dish_choice_3</t>
+  </si>
+  <si>
+    <t>dish_grant_1</t>
+  </si>
+  <si>
+    <t>随机获得 {requiredPickCount} 个食物</t>
+  </si>
+  <si>
+    <t>passive_choice_1</t>
+  </si>
+  <si>
+    <t>随机获得 {requiredPickCount} 个[term]装饰品[/term]</t>
+  </si>
+  <si>
+    <t>passive_choice_3</t>
+  </si>
+  <si>
+    <t>passive_grant_2</t>
+  </si>
+  <si>
+    <t>获得全部 {choiceCount} 个[term]装饰品[/term]</t>
+  </si>
+  <si>
+    <t>active_grant_1</t>
+  </si>
+  <si>
+    <t>ActiveItemGrant</t>
+  </si>
+  <si>
+    <t>pool_active</t>
+  </si>
+  <si>
+    <t>消耗品</t>
+  </si>
+  <si>
+    <t>随机获得 {requiredPickCount} 个[term]消耗品[/term]</t>
+  </si>
+  <si>
+    <t>active_grant_2</t>
+  </si>
+  <si>
+    <t>获得全部 {choiceCount} 个[term]消耗品[/term]</t>
+  </si>
+  <si>
+    <t>active_choice_3</t>
+  </si>
+  <si>
+    <t>消耗品选择</t>
+  </si>
+  <si>
+    <t>从 {choiceCount} 个[term]消耗品[/term]中选择 {requiredPickCount} 个</t>
+  </si>
+  <si>
+    <t>fragment_choice_3</t>
+  </si>
+  <si>
+    <t>从 {choiceCount} 个餐桌格中选择 {requiredPickCount} 个</t>
+  </si>
+  <si>
+    <t>flavored_dish_3</t>
+  </si>
+  <si>
+    <t>pool_flavored_dish</t>
+  </si>
+  <si>
+    <t>风味食物</t>
+  </si>
+  <si>
+    <t>获得全部 {choiceCount} 个风味食物</t>
+  </si>
+  <si>
+    <t>legendary_choice_1</t>
+  </si>
+  <si>
+    <t>pool_legendary</t>
+  </si>
+  <si>
+    <t>传说装饰品</t>
+  </si>
+  <si>
+    <t>随机获得 {requiredPickCount} 个传说[term]装饰品[/term]</t>
+  </si>
+  <si>
+    <t>slot_machine_gold</t>
+  </si>
+  <si>
+    <t>slot_machine_basic</t>
+  </si>
+  <si>
     <t>0,20</t>
-  </si>
-  <si>
-    <t>金币</t>
-  </si>
-  <si>
-    <t>[gold]金币+ {requiredPickCount}[/gold]</t>
-  </si>
-  <si>
-    <t>slot_specific_fragment</t>
-  </si>
-  <si>
-    <t>FragmentChoice</t>
-  </si>
-  <si>
-    <t>pool_fragment</t>
-  </si>
-  <si>
-    <t>0,10</t>
-  </si>
-  <si>
-    <t>餐桌格</t>
-  </si>
-  <si>
-    <t>从 {choiceCount} 个餐桌格中选择 {requiredPickCount} 个拼入餐桌</t>
-  </si>
-  <si>
-    <t>slot_specific_passive</t>
-  </si>
-  <si>
-    <t>PassiveItemChoice</t>
-  </si>
-  <si>
-    <t>pool_passive</t>
-  </si>
-  <si>
-    <t>1,4</t>
-  </si>
-  <si>
-    <t>装饰品</t>
-  </si>
-  <si>
-    <t>从 {choiceCount} 个[term]装饰品[/term]中选择 {requiredPickCount} 个</t>
-  </si>
-  <si>
-    <t>slot_specific_active_strengthen</t>
-  </si>
-  <si>
-    <t>ActiveItemStrengthen</t>
-  </si>
-  <si>
-    <t>pool_active_strengthen</t>
-  </si>
-  <si>
-    <t>强化箱</t>
-  </si>
-  <si>
-    <t>从 {choiceCount} 个强化箱中选择 {requiredPickCount} 个</t>
-  </si>
-  <si>
-    <t>slot_specific_active_adjust</t>
-  </si>
-  <si>
-    <t>ActiveItemAdjust</t>
-  </si>
-  <si>
-    <t>pool_active_adjust</t>
-  </si>
-  <si>
-    <t>调整单</t>
-  </si>
-  <si>
-    <t>从 {choiceCount} 个调整单中选择 {requiredPickCount} 个</t>
-  </si>
-  <si>
-    <t>slot_specific_hard_passive</t>
-  </si>
-  <si>
-    <t>slot_specific_hard_active_strengthen</t>
-  </si>
-  <si>
-    <t>slot_specific_hard_active_adjust</t>
-  </si>
-  <si>
-    <t>slot_boss_dish</t>
-  </si>
-  <si>
-    <t>boss_dish</t>
-  </si>
-  <si>
-    <t>4,0</t>
-  </si>
-  <si>
-    <t>slot_boss_passive</t>
-  </si>
-  <si>
-    <t>boss_passive</t>
-  </si>
-  <si>
-    <t>pool_passive_boss</t>
-  </si>
-  <si>
-    <t>slot_boss_fragment</t>
-  </si>
-  <si>
-    <t>boss_fragment</t>
-  </si>
-  <si>
-    <t>slot_boss_gold</t>
-  </si>
-  <si>
-    <t>boss_gold</t>
-  </si>
-  <si>
-    <t>50,0</t>
-  </si>
-  <si>
-    <t>dish_choice_3</t>
-  </si>
-  <si>
-    <t>dish_grant_1</t>
-  </si>
-  <si>
-    <t>随机获得 {requiredPickCount} 个食物</t>
-  </si>
-  <si>
-    <t>passive_choice_1</t>
-  </si>
-  <si>
-    <t>随机获得 {requiredPickCount} 个[term]装饰品[/term]</t>
-  </si>
-  <si>
-    <t>passive_choice_3</t>
-  </si>
-  <si>
-    <t>passive_grant_2</t>
-  </si>
-  <si>
-    <t>获得全部 {choiceCount} 个[term]装饰品[/term]</t>
-  </si>
-  <si>
-    <t>active_grant_1</t>
-  </si>
-  <si>
-    <t>ActiveItemGrant</t>
-  </si>
-  <si>
-    <t>pool_active</t>
-  </si>
-  <si>
-    <t>消耗品</t>
-  </si>
-  <si>
-    <t>随机获得 {requiredPickCount} 个[term]消耗品[/term]</t>
-  </si>
-  <si>
-    <t>active_grant_2</t>
-  </si>
-  <si>
-    <t>获得全部 {choiceCount} 个[term]消耗品[/term]</t>
-  </si>
-  <si>
-    <t>active_choice_3</t>
-  </si>
-  <si>
-    <t>消耗品选择</t>
-  </si>
-  <si>
-    <t>从 {choiceCount} 个[term]消耗品[/term]中选择 {requiredPickCount} 个</t>
-  </si>
-  <si>
-    <t>fragment_choice_3</t>
-  </si>
-  <si>
-    <t>从 {choiceCount} 个餐桌格中选择 {requiredPickCount} 个</t>
-  </si>
-  <si>
-    <t>flavored_dish_3</t>
-  </si>
-  <si>
-    <t>pool_flavored_dish</t>
-  </si>
-  <si>
-    <t>风味食物</t>
-  </si>
-  <si>
-    <t>获得全部 {choiceCount} 个风味食物</t>
-  </si>
-  <si>
-    <t>legendary_choice_1</t>
-  </si>
-  <si>
-    <t>pool_legendary</t>
-  </si>
-  <si>
-    <t>传说装饰品</t>
-  </si>
-  <si>
-    <t>随机获得 {requiredPickCount} 个传说[term]装饰品[/term]</t>
-  </si>
-  <si>
-    <t>slot_machine_gold</t>
-  </si>
-  <si>
-    <t>slot_machine_basic</t>
   </si>
   <si>
     <t>slot_machine_fragment</t>
@@ -2023,7 +2023,7 @@
         <v>74</v>
       </c>
       <c r="E6" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F6" s="1">
         <v>1</v>
@@ -2041,27 +2041,27 @@
         <v>65</v>
       </c>
       <c r="K6" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="L6" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="M6" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="L6" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="M6" s="3" t="s">
+      <c r="N6" s="3" t="s">
         <v>77</v>
-      </c>
-      <c r="N6" s="3" t="s">
-        <v>78</v>
       </c>
     </row>
     <row r="7" s="1" customFormat="1" ht="17" customHeight="1" spans="2:14">
       <c r="B7" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E7" s="1">
         <v>2</v>
@@ -2073,36 +2073,36 @@
         <v>1</v>
       </c>
       <c r="H7" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="I7" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="J7" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="I7" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="J7" s="1" t="s">
+      <c r="K7" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="L7" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="M7" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="K7" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="L7" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="M7" s="3" t="s">
+      <c r="N7" s="3" t="s">
         <v>83</v>
-      </c>
-      <c r="N7" s="3" t="s">
-        <v>84</v>
       </c>
     </row>
     <row r="8" s="1" customFormat="1" ht="17" customHeight="1" spans="2:14">
       <c r="B8" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E8" s="1">
         <v>3</v>
@@ -2114,36 +2114,36 @@
         <v>1</v>
       </c>
       <c r="H8" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="I8" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="J8" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="K8" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="L8" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="M8" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="I8" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="J8" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="K8" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="L8" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="M8" s="3" t="s">
+      <c r="N8" s="3" t="s">
         <v>88</v>
-      </c>
-      <c r="N8" s="3" t="s">
-        <v>89</v>
       </c>
     </row>
     <row r="9" s="1" customFormat="1" ht="17" customHeight="1" spans="2:14">
       <c r="B9" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E9" s="1">
         <v>3</v>
@@ -2155,36 +2155,36 @@
         <v>1</v>
       </c>
       <c r="H9" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="I9" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="J9" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="K9" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="L9" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="M9" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="I9" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="J9" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="K9" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="L9" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="M9" s="3" t="s">
+      <c r="N9" s="3" t="s">
         <v>93</v>
-      </c>
-      <c r="N9" s="3" t="s">
-        <v>94</v>
       </c>
     </row>
     <row r="10" s="1" customFormat="1" ht="17" customHeight="1" spans="2:14">
       <c r="B10" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>24</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E10" s="1">
         <v>4</v>
@@ -2196,36 +2196,36 @@
         <v>1</v>
       </c>
       <c r="H10" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="I10" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="J10" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="I10" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="J10" s="1" t="s">
+      <c r="K10" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="L10" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="M10" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="K10" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="L10" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="M10" s="3" t="s">
+      <c r="N10" s="3" t="s">
         <v>83</v>
-      </c>
-      <c r="N10" s="3" t="s">
-        <v>84</v>
       </c>
     </row>
     <row r="11" s="1" customFormat="1" ht="17" customHeight="1" spans="2:14">
       <c r="B11" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>26</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E11" s="1">
         <v>5</v>
@@ -2237,36 +2237,36 @@
         <v>1</v>
       </c>
       <c r="H11" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="I11" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="J11" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="K11" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="L11" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="M11" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="I11" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="J11" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="K11" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="L11" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="M11" s="3" t="s">
+      <c r="N11" s="3" t="s">
         <v>88</v>
-      </c>
-      <c r="N11" s="3" t="s">
-        <v>89</v>
       </c>
     </row>
     <row r="12" s="1" customFormat="1" ht="17" customHeight="1" spans="2:14">
       <c r="B12" s="1" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E12" s="1">
         <v>5</v>
@@ -2278,33 +2278,33 @@
         <v>1</v>
       </c>
       <c r="H12" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="I12" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="J12" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="K12" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="L12" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="M12" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="I12" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="J12" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="K12" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="L12" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="M12" s="3" t="s">
+      <c r="N12" s="3" t="s">
         <v>93</v>
-      </c>
-      <c r="N12" s="3" t="s">
-        <v>94</v>
       </c>
     </row>
     <row r="13" s="1" customFormat="1" ht="17" customHeight="1" spans="2:14">
       <c r="B13" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="C13" s="1" t="s">
         <v>98</v>
-      </c>
-      <c r="C13" s="1" t="s">
-        <v>99</v>
       </c>
       <c r="D13" s="1" t="s">
         <v>62</v>
@@ -2322,7 +2322,7 @@
         <v>63</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="J13" s="1" t="s">
         <v>65</v>
@@ -2342,13 +2342,13 @@
     </row>
     <row r="14" s="1" customFormat="1" ht="17" customHeight="1" spans="2:14">
       <c r="B14" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="C14" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="C14" s="1" t="s">
-        <v>102</v>
-      </c>
       <c r="D14" s="1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E14" s="1">
         <v>3</v>
@@ -2360,13 +2360,13 @@
         <v>1</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="I14" s="1" t="s">
         <v>65</v>
       </c>
       <c r="J14" s="1" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="K14" s="1" t="s">
         <v>65</v>
@@ -2375,24 +2375,24 @@
         <v>65</v>
       </c>
       <c r="M14" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="N14" s="3" t="s">
         <v>83</v>
-      </c>
-      <c r="N14" s="3" t="s">
-        <v>84</v>
       </c>
     </row>
     <row r="15" s="1" customFormat="1" ht="17" customHeight="1" spans="2:14">
       <c r="B15" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="C15" s="1" t="s">
         <v>104</v>
-      </c>
-      <c r="C15" s="1" t="s">
-        <v>105</v>
       </c>
       <c r="D15" s="1" t="s">
         <v>74</v>
       </c>
       <c r="E15" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F15" s="1">
         <v>1</v>
@@ -2410,24 +2410,24 @@
         <v>65</v>
       </c>
       <c r="K15" s="1" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="L15" s="1" t="s">
         <v>65</v>
       </c>
       <c r="M15" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="N15" s="3" t="s">
         <v>77</v>
-      </c>
-      <c r="N15" s="3" t="s">
-        <v>78</v>
       </c>
     </row>
     <row r="16" s="1" customFormat="1" ht="17" customHeight="1" spans="2:14">
       <c r="B16" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="C16" s="1" t="s">
         <v>106</v>
-      </c>
-      <c r="C16" s="1" t="s">
-        <v>107</v>
       </c>
       <c r="D16" s="1" t="s">
         <v>69</v>
@@ -2451,7 +2451,7 @@
         <v>65</v>
       </c>
       <c r="L16" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="M16" s="3" t="s">
         <v>71</v>
@@ -2462,10 +2462,10 @@
     </row>
     <row r="17" ht="17" customHeight="1" spans="2:14">
       <c r="B17" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D17" s="1" t="s">
         <v>62</v>
@@ -2503,10 +2503,10 @@
     </row>
     <row r="18" ht="17" customHeight="1" spans="2:14">
       <c r="B18" s="1" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D18" s="1" t="s">
         <v>62</v>
@@ -2539,59 +2539,59 @@
         <v>66</v>
       </c>
       <c r="N18" s="3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="19" ht="17" customHeight="1" spans="2:14">
       <c r="B19" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="E19" s="1">
+        <v>1</v>
+      </c>
+      <c r="F19" s="1">
+        <v>1</v>
+      </c>
+      <c r="G19" s="1">
+        <v>1</v>
+      </c>
+      <c r="H19" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="I19" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="J19" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="K19" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="L19" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="M19" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="N19" s="3" t="s">
         <v>112</v>
-      </c>
-      <c r="C19" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="D19" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="E19" s="1">
-        <v>1</v>
-      </c>
-      <c r="F19" s="1">
-        <v>1</v>
-      </c>
-      <c r="G19" s="1">
-        <v>1</v>
-      </c>
-      <c r="H19" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="I19" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="J19" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="K19" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="L19" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="M19" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="N19" s="3" t="s">
-        <v>113</v>
       </c>
     </row>
     <row r="20" ht="17" customHeight="1" spans="2:14">
       <c r="B20" s="1" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E20" s="1">
         <v>3</v>
@@ -2603,7 +2603,7 @@
         <v>1</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="I20" s="1" t="s">
         <v>65</v>
@@ -2618,21 +2618,21 @@
         <v>65</v>
       </c>
       <c r="M20" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="N20" s="3" t="s">
         <v>83</v>
-      </c>
-      <c r="N20" s="3" t="s">
-        <v>84</v>
       </c>
     </row>
     <row r="21" ht="17" customHeight="1" spans="2:14">
       <c r="B21" s="1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E21" s="1">
         <v>2</v>
@@ -2644,7 +2644,7 @@
         <v>1</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="I21" s="1" t="s">
         <v>65</v>
@@ -2659,62 +2659,62 @@
         <v>65</v>
       </c>
       <c r="M21" s="3" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="N21" s="3" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="22" ht="17" customHeight="1" spans="2:14">
       <c r="B22" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="D22" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="C22" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="D22" s="1" t="s">
+      <c r="E22" s="1">
+        <v>1</v>
+      </c>
+      <c r="F22" s="1">
+        <v>1</v>
+      </c>
+      <c r="G22" s="1">
+        <v>1</v>
+      </c>
+      <c r="H22" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="E22" s="1">
-        <v>1</v>
-      </c>
-      <c r="F22" s="1">
-        <v>1</v>
-      </c>
-      <c r="G22" s="1">
-        <v>1</v>
-      </c>
-      <c r="H22" s="1" t="s">
+      <c r="I22" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="J22" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="K22" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="L22" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="M22" s="3" t="s">
         <v>119</v>
       </c>
-      <c r="I22" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="J22" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="K22" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="L22" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="M22" s="3" t="s">
+      <c r="N22" s="3" t="s">
         <v>120</v>
-      </c>
-      <c r="N22" s="3" t="s">
-        <v>121</v>
       </c>
     </row>
     <row r="23" ht="17" customHeight="1" spans="2:14">
       <c r="B23" s="1" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E23" s="1">
         <v>2</v>
@@ -2726,36 +2726,36 @@
         <v>1</v>
       </c>
       <c r="H23" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="I23" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="J23" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="K23" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="L23" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="M23" s="3" t="s">
         <v>119</v>
       </c>
-      <c r="I23" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="J23" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="K23" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="L23" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="M23" s="3" t="s">
-        <v>120</v>
-      </c>
       <c r="N23" s="3" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="24" ht="17" customHeight="1" spans="2:14">
       <c r="B24" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E24" s="1">
         <v>3</v>
@@ -2767,7 +2767,7 @@
         <v>1</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="I24" s="1" t="s">
         <v>65</v>
@@ -2782,18 +2782,18 @@
         <v>65</v>
       </c>
       <c r="M24" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="N24" s="3" t="s">
         <v>125</v>
-      </c>
-      <c r="N24" s="3" t="s">
-        <v>126</v>
       </c>
     </row>
     <row r="25" ht="17" customHeight="1" spans="2:14">
       <c r="B25" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D25" s="1" t="s">
         <v>74</v>
@@ -2823,18 +2823,18 @@
         <v>65</v>
       </c>
       <c r="M25" s="3" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="N25" s="3" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="26" ht="17" customHeight="1" spans="2:14">
       <c r="B26" s="1" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D26" s="1" t="s">
         <v>62</v>
@@ -2849,74 +2849,74 @@
         <v>1</v>
       </c>
       <c r="H26" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="I26" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="J26" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="K26" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="L26" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="M26" s="3" t="s">
         <v>130</v>
       </c>
-      <c r="I26" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="J26" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="K26" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="L26" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="M26" s="3" t="s">
+      <c r="N26" s="3" t="s">
         <v>131</v>
-      </c>
-      <c r="N26" s="3" t="s">
-        <v>132</v>
       </c>
     </row>
     <row r="27" ht="17" customHeight="1" spans="2:14">
       <c r="B27" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="E27" s="1">
+        <v>1</v>
+      </c>
+      <c r="F27" s="1">
+        <v>1</v>
+      </c>
+      <c r="G27" s="1">
+        <v>1</v>
+      </c>
+      <c r="H27" s="1" t="s">
         <v>133</v>
       </c>
-      <c r="C27" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="D27" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="E27" s="1">
-        <v>1</v>
-      </c>
-      <c r="F27" s="1">
-        <v>1</v>
-      </c>
-      <c r="G27" s="1">
-        <v>1</v>
-      </c>
-      <c r="H27" s="1" t="s">
+      <c r="I27" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="J27" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="K27" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="L27" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="M27" s="3" t="s">
         <v>134</v>
       </c>
-      <c r="I27" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="J27" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="K27" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="L27" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="M27" s="3" t="s">
+      <c r="N27" s="3" t="s">
         <v>135</v>
-      </c>
-      <c r="N27" s="3" t="s">
-        <v>136</v>
       </c>
     </row>
     <row r="28" ht="17" customHeight="1" spans="2:14">
       <c r="B28" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="C28" s="1" t="s">
         <v>137</v>
-      </c>
-      <c r="C28" s="1" t="s">
-        <v>138</v>
       </c>
       <c r="D28" s="1" t="s">
         <v>69</v>
@@ -2940,7 +2940,7 @@
         <v>65</v>
       </c>
       <c r="L28" s="1" t="s">
-        <v>70</v>
+        <v>138</v>
       </c>
       <c r="M28" s="3" t="s">
         <v>71</v>
@@ -2954,7 +2954,7 @@
         <v>139</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D29" s="1" t="s">
         <v>74</v>
@@ -2984,10 +2984,10 @@
         <v>65</v>
       </c>
       <c r="M29" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="N29" s="3" t="s">
         <v>77</v>
-      </c>
-      <c r="N29" s="3" t="s">
-        <v>78</v>
       </c>
     </row>
     <row r="30" ht="17" customHeight="1" spans="2:14">
@@ -2995,10 +2995,10 @@
         <v>141</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E30" s="1">
         <v>1</v>
@@ -3010,25 +3010,25 @@
         <v>10</v>
       </c>
       <c r="H30" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="I30" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="J30" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="K30" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="L30" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="M30" s="3" t="s">
         <v>119</v>
       </c>
-      <c r="I30" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="J30" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="K30" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="L30" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="M30" s="3" t="s">
+      <c r="N30" s="3" t="s">
         <v>120</v>
-      </c>
-      <c r="N30" s="3" t="s">
-        <v>121</v>
       </c>
     </row>
     <row r="31" ht="17" customHeight="1" spans="2:14">
@@ -3036,10 +3036,10 @@
         <v>142</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E31" s="1">
         <v>2</v>
@@ -3051,7 +3051,7 @@
         <v>10</v>
       </c>
       <c r="H31" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="I31" s="1" t="s">
         <v>65</v>
@@ -3066,10 +3066,10 @@
         <v>65</v>
       </c>
       <c r="M31" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="N31" s="3" t="s">
         <v>83</v>
-      </c>
-      <c r="N31" s="3" t="s">
-        <v>84</v>
       </c>
     </row>
     <row r="32" ht="17" customHeight="1" spans="2:14">
@@ -3092,25 +3092,25 @@
         <v>1</v>
       </c>
       <c r="H32" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="I32" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="J32" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="K32" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="L32" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="M32" s="1" t="s">
         <v>130</v>
       </c>
-      <c r="I32" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="J32" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="K32" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="L32" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="M32" s="1" t="s">
+      <c r="N32" s="1" t="s">
         <v>131</v>
-      </c>
-      <c r="N32" s="1" t="s">
-        <v>132</v>
       </c>
     </row>
     <row r="33" ht="17" customHeight="1"/>
@@ -3223,7 +3223,7 @@
     </row>
     <row r="6" spans="2:4">
       <c r="B6" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>159</v>
@@ -3234,7 +3234,7 @@
     </row>
     <row r="7" spans="2:5">
       <c r="B7" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>159</v>
@@ -3248,10 +3248,10 @@
     </row>
     <row r="8" ht="409.5" customHeight="1" spans="2:5">
       <c r="B8" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D8" s="1" t="b">
         <v>1</v>
@@ -3262,10 +3262,10 @@
     </row>
     <row r="9" spans="2:4">
       <c r="B9" s="2" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D9" s="1" t="b">
         <v>1</v>
@@ -3273,7 +3273,7 @@
     </row>
     <row r="10" spans="2:4">
       <c r="B10" s="1" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>157</v>
@@ -3284,7 +3284,7 @@
     </row>
     <row r="11" spans="2:6">
       <c r="B11" s="1" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>159</v>
@@ -3298,7 +3298,7 @@
     </row>
     <row r="12" spans="2:4">
       <c r="B12" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C12" t="s">
         <v>163</v>
